--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -4526,12 +4526,12 @@
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Ponieważ dokument może pochodzić z EPU/e-Sądu, trzeba odrębnie sprawdzić właściwy tryb i termin reakcji. Ponieważ dokument wskazuje na e-Sąd (EPU), priorytetem jest szybkie zabezpieczenie reakcji w terminie, a pełna strategia i materiał dowodowy mogą zostać dopracowane w kolejnym etapie po przekazaniu sprawy do sądu właściwości ogólnej.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS. Ponieważ dokument wskazuje na e-Sąd (EPU), priorytetem jest szybkie zabezpieczenie reakcji w terminie, a pełna strategia i materiał dowodowy mogą zostać dopracowane w kolejnym etapie po przekazaniu sprawy do sądu właściwości ogólnej.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P28" s="5" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko wynika z połączenia rodzaju dokumentu, potrzeby weryfikacji terminu oraz niepewności danych wymagających sprawdzenia. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy. Ponieważ dokument może pochodzić z EPU/e-Sądu, trzeba odrębnie sprawdzić właściwy tryb i termin reakcji. Możesz zacząć od wstępnej oceny, a dokumenty dosłać później — plan ułożymy etapowo.</t>
+          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P29" s="5" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy. Status rezygnacji lub odwołania oraz aktualność wpisu w KRS wymagają weryfikacji. Ponieważ dokument może pochodzić z EPU/e-Sądu, trzeba odrębnie sprawdzić właściwy tryb i termin reakcji. Ponieważ dokument pochodzi z e-Sądu, zakres czynności na etapie samej reakcji terminowej może być organizacyjnie prostszy, ale równolegle należy przygotować plan dalszej obrony na etap po przekazaniu sprawy do sądu właściwego.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS. Ponieważ dokument pochodzi z e-Sądu, zakres czynności na etapie samej reakcji terminowej może być organizacyjnie prostszy, ale równolegle należy przygotować plan dalszej obrony na etap po przekazaniu sprawy do sądu właściwego.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P30" s="5" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="N31" s="5" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko wynika z połączenia rodzaju dokumentu, potrzeby weryfikacji terminu oraz niepewności danych wymagających sprawdzenia. Ponieważ dokument może pochodzić z EPU/e-Sądu, trzeba odrębnie sprawdzić właściwy tryb i termin reakcji. W przypadku e-Sądu rekomendowany jest Audyt 48h skoncentrowany na prawidłowej organizacji reakcji terminowej oraz przygotowaniu dalszej strategii na etap po ewentualnym przekazaniu sprawy do sądu właściwego.</t>
+          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS. W przypadku e-Sądu rekomendowany jest Audyt 48h skoncentrowany na prawidłowej organizacji reakcji terminowej oraz przygotowaniu dalszej strategii na etap po ewentualnym przekazaniu sprawy do sądu właściwego.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P31" s="5" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono jako średnie, ale wynik nadal wymaga weryfikacji dokumentów i terminów. Ponieważ dokument może pochodzić z EPU/e-Sądu, trzeba odrębnie sprawdzić właściwy tryb i termin reakcji.</t>
+          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie. Ryzyko jest ocenione jako umiarkowane — warto jednak potwierdzić termin i podstawę roszczenia przed podjęciem decyzji o złożeniu sprzeciwu w EPU.</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P32" s="5" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Ponieważ dokument może pochodzić z EPU/e-Sądu, trzeba odrębnie sprawdzić właściwy tryb i termin reakcji. Na tym etapie deklarujesz wstępną ocenę bez wysyłki dokumentów, więc rekomendacja ma charakter organizacyjny i zaczyna od ustalenia braków.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P33" s="5" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko wynika z połączenia rodzaju dokumentu, potrzeby weryfikacji terminu oraz niepewności danych wymagających sprawdzenia. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Ponieważ dokument może pochodzić z EPU/e-Sądu, trzeba odrębnie sprawdzić właściwy tryb i termin reakcji. Masz ponad 2 tygodnie na reakcję — można działać spokojniej, ale warto od razu ustalić plan i checklistę.</t>
+          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P34" s="5" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono jako średnie, ale wynik nadal wymaga weryfikacji dokumentów i terminów. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy. Ponieważ dokument może pochodzić z EPU/e-Sądu, trzeba odrębnie sprawdzić właściwy tryb i termin reakcji. Masz ponad 2 tygodnie na reakcję — można działać spokojniej, ale warto od razu ustalić plan i checklistę.</t>
+          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie. Ryzyko jest ocenione jako umiarkowane — warto jednak potwierdzić termin i podstawę roszczenia przed podjęciem decyzji o złożeniu sprzeciwu w EPU.</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P35" s="5" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Ponieważ dokument może pochodzić z EPU/e-Sądu, trzeba odrębnie sprawdzić właściwy tryb i termin reakcji. Masz ponad 2 tygodnie na reakcję — można działać spokojniej, ale warto od razu ustalić plan i checklistę.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P36" s="5" t="inlineStr">
@@ -5537,12 +5537,12 @@
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko wynika z połączenia rodzaju dokumentu, potrzeby weryfikacji terminu oraz niepewności danych wymagających sprawdzenia. Nieustalony termin zwiększa niepewność i wymaga sprawdzenia przed podjęciem dalszych decyzji. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy. Ponieważ dokument może pochodzić z EPU/e-Sądu, trzeba odrębnie sprawdzić właściwy tryb i termin reakcji. Możesz zacząć od wstępnej oceny, a dokumenty dosłać później — plan ułożymy etapowo.</t>
+          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P37" s="5" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Nieustalony termin zwiększa niepewność i wymaga sprawdzenia przed podjęciem dalszych decyzji. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Ponieważ dokument może pochodzić z EPU/e-Sądu, trzeba odrębnie sprawdzić właściwy tryb i termin reakcji. Na tym etapie deklarujesz wstępną ocenę bez wysyłki dokumentów, więc rekomendacja ma charakter organizacyjny i zaczyna od ustalenia braków.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P38" s="5" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ nakaz EPU może uruchamiać termin na reakcję, a czas może być krótki albo dane mogą wymagać szybkiego potwierdzenia. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce stwarza bezpośrednie ryzyko dla członka zarządu — jeśli spółka nie złoży sprzeciwu w EPU w terminie, nakaz się uprawomocni. Wierzyciel uruchomi egzekucję, a po jej bezskuteczności skieruje roszczenie bezpośrednio do Ciebie z art. 299 KSH. W EPU termin na sprzeciw jest ściśle liczony od doręczenia — pilność wynika z krótkiego czasu i wymogów elektronicznego postępowania.</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P39" s="5" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji. Nakaz przeciwko spółce nie zawsze jest dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny ryzyka odpowiedzialności członka zarządu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P40" s="5" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="N41" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ nakaz EPU może uruchamiać termin na reakcję, a czas może być krótki albo dane mogą wymagać szybkiego potwierdzenia. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce stwarza bezpośrednie ryzyko dla członka zarządu — jeśli spółka nie złoży sprzeciwu w EPU w terminie, nakaz się uprawomocni. Wierzyciel uruchomi egzekucję, a po jej bezskuteczności skieruje roszczenie bezpośrednio do Ciebie z art. 299 KSH. W EPU termin na sprzeciw jest ściśle liczony od doręczenia — pilność wynika z krótkiego czasu i wymogów elektronicznego postępowania.</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P41" s="5" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji. Nakaz przeciwko spółce nie zawsze jest dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny ryzyka odpowiedzialności członka zarządu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P42" s="5" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji. Nakaz EPU przeciwko spółce może być istotny jako dokument pokazujący etap sprawy, ale sam w sobie nie musi jeszcze oznaczać dokumentu bezpośrednio skierowanego do członka zarządu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU przeciwko spółce wymaga sprawdzenia, czy spółka podjęła już działania. W EPU brak sprzeciwu w terminie powoduje uprawomocnienie nakazu i może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla członka zarządu.</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P43" s="5" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ nakaz EPU może uruchamiać termin na reakcję, a czas może być krótki albo dane mogą wymagać szybkiego potwierdzenia. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce stwarza bezpośrednie ryzyko dla członka zarządu — jeśli spółka nie złoży sprzeciwu w EPU w terminie, nakaz się uprawomocni. Wierzyciel uruchomi egzekucję, a po jej bezskuteczności skieruje roszczenie bezpośrednio do Ciebie z art. 299 KSH. W EPU termin na sprzeciw jest ściśle liczony od doręczenia — pilność wynika z krótkiego czasu i wymogów elektronicznego postępowania.</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P44" s="5" t="inlineStr">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji. Nakaz przeciwko spółce nie zawsze jest dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny ryzyka odpowiedzialności członka zarządu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P45" s="5" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>Sprawa ma niższy poziom pilności, ale nadal warto potwierdzić podstawowe dane, zwłaszcza termin i adresata nakazu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU przeciwko spółce jest na tym etapie oceniany jako niskie ryzyko bezpośrednie. Warto jednak potwierdzić, czy spółka złożyła sprzeciw w EPU w terminie — brak reakcji mógłby w przyszłości prowadzić do ryzyka z art. 299 KSH dla członka zarządu.</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P46" s="5" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji. Nakaz EPU przeciwko spółce może być istotny jako dokument pokazujący etap sprawy, ale sam w sobie nie musi jeszcze oznaczać dokumentu bezpośrednio skierowanego do członka zarządu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU przeciwko spółce wymaga sprawdzenia, czy spółka podjęła już działania. W EPU brak sprzeciwu w terminie powoduje uprawomocnienie nakazu i może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla członka zarządu.</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P47" s="5" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="N48" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ nakaz EPU może uruchamiać termin na reakcję, a czas może być krótki albo dane mogą wymagać szybkiego potwierdzenia. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce stwarza bezpośrednie ryzyko dla członka zarządu — jeśli spółka nie złoży sprzeciwu w EPU w terminie, nakaz się uprawomocni. Wierzyciel uruchomi egzekucję, a po jej bezskuteczności skieruje roszczenie bezpośrednio do Ciebie z art. 299 KSH. W EPU termin na sprzeciw jest ściśle liczony od doręczenia — pilność wynika z krótkiego czasu i wymogów elektronicznego postępowania.</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P48" s="5" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="N49" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji. Nakaz przeciwko spółce nie zawsze jest dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny ryzyka odpowiedzialności członka zarządu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P49" s="5" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="N50" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji. Nakaz EPU przeciwko spółce może być istotny jako dokument pokazujący etap sprawy, ale sam w sobie nie musi jeszcze oznaczać dokumentu bezpośrednio skierowanego do członka zarządu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU przeciwko spółce wymaga sprawdzenia, czy spółka podjęła już działania. W EPU brak sprzeciwu w terminie powoduje uprawomocnienie nakazu i może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla członka zarządu.</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P50" s="5" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ nakaz EPU może uruchamiać termin na reakcję, a czas może być krótki albo dane mogą wymagać szybkiego potwierdzenia. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce stwarza bezpośrednie ryzyko dla członka zarządu — jeśli spółka nie złoży sprzeciwu w EPU w terminie, nakaz się uprawomocni. Wierzyciel uruchomi egzekucję, a po jej bezskuteczności skieruje roszczenie bezpośrednio do Ciebie z art. 299 KSH. W EPU termin na sprzeciw jest ściśle liczony od doręczenia — pilność wynika z krótkiego czasu i wymogów elektronicznego postępowania.</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata nakazu, treść pouczenia oraz to, czy dokument dotyczy wyłącznie spółki, czy może mieć znaczenie dla sytuacji obecnego albo byłego członka zarządu.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P51" s="5" t="inlineStr">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P39" s="5" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności byłego członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P40" s="5" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P41" s="5" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności byłego członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P42" s="5" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P43" s="5" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P44" s="5" t="inlineStr">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności byłego członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P45" s="5" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P46" s="5" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P47" s="5" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P48" s="5" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="N49" s="5" t="inlineStr">
         <is>
-          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) wydany przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności byłego członka zarządu z art. 299 KSH — jeśli egzekucja przeciwko spółce okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na sprzeciw spółki w EPU jest ściśle określony i liczony od doręczenia.</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P49" s="5" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P50" s="5" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany do spółki — właściwą reakcją spółki jest sprzeciw złożony w postępowaniu elektronicznym w terminie wynikającym z doręczenia i pouczenia. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej i rozpatrywana jest w trybie zwykłym. Brak sprzeciwu spowoduje uprawomocnienie nakazu i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć sprzeciw w EPU.</t>
         </is>
       </c>
       <c r="P51" s="5" t="inlineStr">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -4526,12 +4526,12 @@
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P28" s="5" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
+          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P29" s="5" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P30" s="5" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="N31" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
+          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P31" s="5" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P32" s="5" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P33" s="5" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
+          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P34" s="5" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P35" s="5" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P36" s="5" t="inlineStr">
@@ -5537,12 +5537,12 @@
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
+          <t>Nakaz z EPU jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu. Masz jeszcze czas na złożenie sprzeciwu w EPU, ale wymaga to weryfikacji: daty doręczenia, treści pouczenia oraz podstawy roszczenia. W EPU sprzeciw może być początkowo uproszczony — ważne jest złożenie go w terminie.</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P37" s="5" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
+          <t>Nakaz zapłaty z EPU (e-Sądu) skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi już Twojej odpowiedzialności osobistej. Termin na sprzeciw w EPU jest ściśle określony od doręczenia i nie podlega przedłużeniu — jego upływ bez reakcji spowoduje uprawomocnienie nakazu.</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
+          <t>Nakaz z EPU (e-Sądu) jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej. Właściwą reakcją jest sprzeciw złożony w postępowaniu elektronicznym w terminie wskazanym w pouczeniu. W EPU sprzeciw może być uproszczony — nie musi od razu zawierać wszystkich zarzutów, ale musi być złożony w terminie. Po skutecznym sprzeciwie sprawa automatycznie trafia do sądu właściwości ogólnej. Kluczowe do ustalenia: data doręczenia, treść pouczenia i termin na sprzeciw.</t>
         </is>
       </c>
       <c r="P38" s="5" t="inlineStr">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -16856,12 +16856,12 @@
       </c>
       <c r="N142" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że sąd wymaga Twojej odpowiedzi lub stawiennictwa. Masz jeszcze czas na weryfikację, ale termin i zakres wymaganej reakcji muszą zostać ustalone natychmiast.</t>
         </is>
       </c>
       <c r="O142" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P142" s="5" t="inlineStr">
@@ -16963,12 +16963,12 @@
       </c>
       <c r="N143" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że postępowanie jest już w toku i sąd wymaga Twojego działania w ściśle określonym terminie. Brak reakcji może skutkować wyrokiem zaocznym lub utratą możliwości obrony.</t>
         </is>
       </c>
       <c r="O143" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P143" s="5" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="N144" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że sąd wymaga Twojej odpowiedzi lub stawiennictwa. Masz jeszcze czas na weryfikację, ale termin i zakres wymaganej reakcji muszą zostać ustalone natychmiast.</t>
         </is>
       </c>
       <c r="O144" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P144" s="5" t="inlineStr">
@@ -17177,12 +17177,12 @@
       </c>
       <c r="N145" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści i terminu. Ryzyko jest umiarkowane, ale brak weryfikacji może spowodować utratę możliwości procesowego działania.</t>
         </is>
       </c>
       <c r="O145" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P145" s="5" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="N146" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że postępowanie jest już w toku i sąd wymaga Twojego działania w ściśle określonym terminie. Brak reakcji może skutkować wyrokiem zaocznym lub utratą możliwości obrony.</t>
         </is>
       </c>
       <c r="O146" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P146" s="5" t="inlineStr">
@@ -17391,12 +17391,12 @@
       </c>
       <c r="N147" s="5" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko wynika z połączenia rodzaju dokumentu, potrzeby weryfikacji terminu oraz niepewności danych wymagających sprawdzenia. To najskuteczniejsza ścieżka realnej obrony — pismo przygotowawcze musi zawierać konkretne zarzuty i dowody, nie ogólne zaprzeczenia.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że sąd wymaga Twojej odpowiedzi lub stawiennictwa. Masz jeszcze czas na weryfikację, ale termin i zakres wymaganej reakcji muszą zostać ustalone natychmiast.</t>
         </is>
       </c>
       <c r="O147" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P147" s="5" t="inlineStr">
@@ -17502,12 +17502,12 @@
       </c>
       <c r="N148" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści i terminu. Ryzyko jest umiarkowane, ale brak weryfikacji może spowodować utratę możliwości procesowego działania.</t>
         </is>
       </c>
       <c r="O148" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P148" s="5" t="inlineStr">
@@ -17609,12 +17609,12 @@
       </c>
       <c r="N149" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Na tym etapie ocena ma charakter wstępny, bo nie widzę treści pisma przygotowawczego strony powodowej.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że postępowanie jest już w toku i sąd wymaga Twojego działania w ściśle określonym terminie. Brak reakcji może skutkować wyrokiem zaocznym lub utratą możliwości obrony.</t>
         </is>
       </c>
       <c r="O149" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P149" s="5" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="N150" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że sąd wymaga Twojej odpowiedzi lub stawiennictwa. Masz jeszcze czas na weryfikację, ale termin i zakres wymaganej reakcji muszą zostać ustalone natychmiast.</t>
         </is>
       </c>
       <c r="O150" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P150" s="5" t="inlineStr">
@@ -17827,12 +17827,12 @@
       </c>
       <c r="N151" s="5" t="inlineStr">
         <is>
-          <t>Sprawa ma niższy poziom pilności, ale nadal warto sprawdzić podstawowe dane i dokumenty. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane do Ciebie jako byłego członka zarządu jest na tym etapie oceniane jako niższe ryzyko. Warto jednak potwierdzić treść wezwania i termin, aby nie przeoczyć wymaganych działań.</t>
         </is>
       </c>
       <c r="O151" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P151" s="5" t="inlineStr">
@@ -17934,12 +17934,12 @@
       </c>
       <c r="N152" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści i terminu. Ryzyko jest umiarkowane, ale brak weryfikacji może spowodować utratę możliwości procesowego działania.</t>
         </is>
       </c>
       <c r="O152" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P152" s="5" t="inlineStr">
@@ -18041,12 +18041,12 @@
       </c>
       <c r="N153" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że postępowanie jest już w toku i sąd wymaga Twojego działania w ściśle określonym terminie. Brak reakcji może skutkować wyrokiem zaocznym lub utratą możliwości obrony.</t>
         </is>
       </c>
       <c r="O153" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P153" s="5" t="inlineStr">
@@ -18148,12 +18148,12 @@
       </c>
       <c r="N154" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że sąd wymaga Twojej odpowiedzi lub stawiennictwa. Masz jeszcze czas na weryfikację, ale termin i zakres wymaganej reakcji muszą zostać ustalone natychmiast.</t>
         </is>
       </c>
       <c r="O154" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P154" s="5" t="inlineStr">
@@ -18255,12 +18255,12 @@
       </c>
       <c r="N155" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści i terminu. Ryzyko jest umiarkowane, ale brak weryfikacji może spowodować utratę możliwości procesowego działania.</t>
         </is>
       </c>
       <c r="O155" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P155" s="5" t="inlineStr">
@@ -18362,12 +18362,12 @@
       </c>
       <c r="N156" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że postępowanie jest już w toku i sąd wymaga Twojego działania w ściśle określonym terminie. Brak reakcji może skutkować wyrokiem zaocznym lub utratą możliwości obrony.</t>
         </is>
       </c>
       <c r="O156" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P156" s="5" t="inlineStr">
@@ -18469,12 +18469,12 @@
       </c>
       <c r="N157" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest istotne z Twojej perspektywy jako byłego członka zarządu — jeśli spółka przegra sprawę lub nie zareaguje, wierzyciel może dochodzić roszczeń bezpośrednio od Ciebie z art. 299 KSH. Masz jeszcze czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O157" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P157" s="5" t="inlineStr">
@@ -18576,12 +18576,12 @@
       </c>
       <c r="N158" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga sprawdzenia, czy spółka podjęła już działania. Brak reakcji spółki może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O158" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P158" s="5" t="inlineStr">
@@ -18683,12 +18683,12 @@
       </c>
       <c r="N159" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga pilnej reakcji — jeśli spółka nie odpowie w terminie, sąd może wydać wyrok zaoczny. Po bezskutecznej egzekucji wobec spółki wierzyciel może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O159" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P159" s="5" t="inlineStr">
@@ -18790,12 +18790,12 @@
       </c>
       <c r="N160" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest istotne z Twojej perspektywy jako byłego członka zarządu — jeśli spółka przegra sprawę lub nie zareaguje, wierzyciel może dochodzić roszczeń bezpośrednio od Ciebie z art. 299 KSH. Masz jeszcze czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O160" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P160" s="5" t="inlineStr">
@@ -18897,12 +18897,12 @@
       </c>
       <c r="N161" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga sprawdzenia, czy spółka podjęła już działania. Brak reakcji spółki może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O161" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P161" s="5" t="inlineStr">
@@ -19004,12 +19004,12 @@
       </c>
       <c r="N162" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga pilnej reakcji — jeśli spółka nie odpowie w terminie, sąd może wydać wyrok zaoczny. Po bezskutecznej egzekucji wobec spółki wierzyciel może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O162" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P162" s="5" t="inlineStr">
@@ -19111,12 +19111,12 @@
       </c>
       <c r="N163" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest istotne z Twojej perspektywy jako byłego członka zarządu — jeśli spółka przegra sprawę lub nie zareaguje, wierzyciel może dochodzić roszczeń bezpośrednio od Ciebie z art. 299 KSH. Masz jeszcze czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O163" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P163" s="5" t="inlineStr">
@@ -19218,12 +19218,12 @@
       </c>
       <c r="N164" s="5" t="inlineStr">
         <is>
-          <t>Sprawa ma niższy poziom pilności, ale nadal warto sprawdzić podstawowe dane i dokumenty. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest na tym etapie oceniane jako niższe ryzyko bezpośrednie. Warto jednak sprawdzić, czy spółka jest aktywnie reprezentowana w postępowaniu — brak reakcji mógłby doprowadzić do wyroku zaocznego.</t>
         </is>
       </c>
       <c r="O164" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P164" s="5" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="N165" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga sprawdzenia, czy spółka podjęła już działania. Brak reakcji spółki może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O165" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P165" s="5" t="inlineStr">
@@ -19432,12 +19432,12 @@
       </c>
       <c r="N166" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga pilnej reakcji — jeśli spółka nie odpowie w terminie, sąd może wydać wyrok zaoczny. Po bezskutecznej egzekucji wobec spółki wierzyciel może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O166" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P166" s="5" t="inlineStr">
@@ -19539,12 +19539,12 @@
       </c>
       <c r="N167" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest istotne z Twojej perspektywy jako byłego członka zarządu — jeśli spółka przegra sprawę lub nie zareaguje, wierzyciel może dochodzić roszczeń bezpośrednio od Ciebie z art. 299 KSH. Masz jeszcze czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O167" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P167" s="5" t="inlineStr">
@@ -19646,12 +19646,12 @@
       </c>
       <c r="N168" s="5" t="inlineStr">
         <is>
-          <t>Sprawa ma niższy poziom pilności, ale nadal warto sprawdzić podstawowe dane i dokumenty. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest na tym etapie oceniane jako niższe ryzyko bezpośrednie. Warto jednak sprawdzić, czy spółka jest aktywnie reprezentowana w postępowaniu — brak reakcji mógłby doprowadzić do wyroku zaocznego.</t>
         </is>
       </c>
       <c r="O168" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P168" s="5" t="inlineStr">
@@ -19753,12 +19753,12 @@
       </c>
       <c r="N169" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga sprawdzenia, czy spółka podjęła już działania. Brak reakcji spółki może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O169" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P169" s="5" t="inlineStr">
@@ -19860,12 +19860,12 @@
       </c>
       <c r="N170" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga pilnej reakcji — jeśli spółka nie odpowie w terminie, sąd może wydać wyrok zaoczny. Po bezskutecznej egzekucji wobec spółki wierzyciel może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O170" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P170" s="5" t="inlineStr">
@@ -19967,12 +19967,12 @@
       </c>
       <c r="N171" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest istotne z Twojej perspektywy jako byłego członka zarządu — jeśli spółka przegra sprawę lub nie zareaguje, wierzyciel może dochodzić roszczeń bezpośrednio od Ciebie z art. 299 KSH. Masz jeszcze czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O171" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P171" s="5" t="inlineStr">
@@ -20074,12 +20074,12 @@
       </c>
       <c r="N172" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga sprawdzenia, czy spółka podjęła już działania. Brak reakcji spółki może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O172" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P172" s="5" t="inlineStr">
@@ -20181,12 +20181,12 @@
       </c>
       <c r="N173" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga pilnej reakcji — jeśli spółka nie odpowie w terminie, sąd może wydać wyrok zaoczny. Po bezskutecznej egzekucji wobec spółki wierzyciel może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O173" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P173" s="5" t="inlineStr">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -1728,12 +1728,12 @@
       </c>
       <c r="N2" s="61" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko wynika z połączenia rodzaju dokumentu, potrzeby weryfikacji terminu oraz niepewności danych wymagających sprawdzenia. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Brak pełnych dokumentów ogranicza pewność wstępnej oceny.</t>
+          <t>Decyzja Urzędu Skarbowego skierowana do Ciebie jako byłego członka zarządu oznacza, że organ podatkowy orzekł o Twojej odpowiedzialności za zaległości podatkowe spółki. Masz jeszcze czas na weryfikację treści i przygotowanie odwołania.</t>
         </is>
       </c>
       <c r="O2" s="61" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS. Ponieważ użytkownik oczekuje planu działania, warto zaakcentować sekwencję kroków i decyzji, a nie jedynie sam wynik punktowy.</t>
+          <t>Decyzja Urzędu Skarbowego jest skierowana bezpośrednio do Ciebie jako byłego członka zarządu — organ podatkowy orzekł o Twojej odpowiedzialności za zaległości podatkowe spółki. Właściwą reakcją jest złożenie odwołania do Dyrektora Izby Administracji Skarbowej za pośrednictwem urzędu, który wydał decyzję, w terminie 14 dni od doręczenia. Kluczowe do ustalenia: termin doręczenia decyzji, okres pełnienia funkcji w zarządzie oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P2" s="61" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy. Rekomendowany jest Audyt 48h w trybie dwustopniowym: najpierw plan działań i kontrola terminów, następnie pogłębiona ocena po dosłaniu decyzji oraz dokumentów dotyczących funkcji i okresu pełnienia obowiązków.</t>
+          <t>Decyzja Urzędu Skarbowego skierowana bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że organ podatkowy orzekł o Twojej odpowiedzialności osobistej za zaległości podatkowe spółki. Od tej decyzji przysługuje odwołanie — termin jest ściśle określony w pouczeniu (zwykle 14 dni od doręczenia).</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Decyzja Urzędu Skarbowego jest skierowana bezpośrednio do Ciebie jako byłego członka zarządu — organ podatkowy orzekł o Twojej odpowiedzialności za zaległości podatkowe spółki. Właściwą reakcją jest złożenie odwołania do Dyrektora Izby Administracji Skarbowej za pośrednictwem urzędu, który wydał decyzję, w terminie 14 dni od doręczenia. Kluczowe do ustalenia: termin doręczenia decyzji, okres pełnienia funkcji w zarządzie oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono niżej, ale podstawowe dane nadal powinny zostać potwierdzone. Posiadanie dokumentacji i umiarkowany termin pozwalają na przeprowadzenie pełnej analizy merytorycznej decyzji US.</t>
+          <t>Decyzja Urzędu Skarbowego dotycząca odpowiedzialności byłego członka zarządu jest na tym etapie oceniana jako niższe ryzyko. Warto jednak potwierdzić termin odwołania.</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Decyzja Urzędu Skarbowego jest skierowana bezpośrednio do Ciebie jako byłego członka zarządu — organ podatkowy orzekł o Twojej odpowiedzialności za zaległości podatkowe spółki. Właściwą reakcją jest złożenie odwołania do Dyrektora Izby Administracji Skarbowej za pośrednictwem urzędu, który wydał decyzję, w terminie 14 dni od doręczenia. Kluczowe do ustalenia: termin doręczenia decyzji, okres pełnienia funkcji w zarządzie oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono jako średnie, ale wynik nadal wymaga weryfikacji dokumentów i terminów. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Rekomendowany jest Audyt 48h ukierunkowany na weryfikację podstaw decyzji ZUS, terminów oraz zgromadzenie dokumentów potrzebnych do oceny dalszej ścieżki obrony.</t>
+          <t>Decyzja Urzędu Skarbowego dotycząca odpowiedzialności byłego członka zarządu za zaległości podatkowe spółki wymaga sprawdzenia treści i terminu odwołania. Ryzyko jest umiarkowane — warto potwierdzić szczegóły.</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Decyzja Urzędu Skarbowego jest skierowana bezpośrednio do Ciebie jako byłego członka zarządu — organ podatkowy orzekł o Twojej odpowiedzialności za zaległości podatkowe spółki. Właściwą reakcją jest złożenie odwołania do Dyrektora Izby Administracji Skarbowej za pośrednictwem urzędu, który wydał decyzję, w terminie 14 dni od doręczenia. Kluczowe do ustalenia: termin doręczenia decyzji, okres pełnienia funkcji w zarządzie oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P5" s="5" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono niżej, ale podstawowe dane nadal powinny zostać potwierdzone. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy.</t>
+          <t>Decyzja Urzędu Skarbowego dotycząca odpowiedzialności byłego członka zarządu jest na tym etapie oceniana jako niższe ryzyko. Warto jednak potwierdzić termin odwołania.</t>
         </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Decyzja Urzędu Skarbowego jest skierowana bezpośrednio do Ciebie jako byłego członka zarządu — organ podatkowy orzekł o Twojej odpowiedzialności za zaległości podatkowe spółki. Właściwą reakcją jest złożenie odwołania do Dyrektora Izby Administracji Skarbowej za pośrednictwem urzędu, który wydał decyzję, w terminie 14 dni od doręczenia. Kluczowe do ustalenia: termin doręczenia decyzji, okres pełnienia funkcji w zarządzie oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P6" s="5" t="inlineStr">
@@ -2271,12 +2271,12 @@
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko wynika z połączenia rodzaju dokumentu, potrzeby weryfikacji terminu oraz niepewności danych wymagających sprawdzenia. Nieustalony termin zwiększa niepewność i wymaga sprawdzenia przed podjęciem dalszych decyzji. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Brak dokumentów i niepewność co do terminu wymuszają natychmiastowe działanie diagnostyczne.</t>
+          <t>Decyzja Urzędu Skarbowego skierowana do Ciebie jako byłego członka zarządu oznacza, że organ podatkowy orzekł o Twojej odpowiedzialności za zaległości podatkowe spółki. Masz jeszcze czas na weryfikację treści i przygotowanie odwołania.</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Decyzja Urzędu Skarbowego jest skierowana bezpośrednio do Ciebie jako byłego członka zarządu — organ podatkowy orzekł o Twojej odpowiedzialności za zaległości podatkowe spółki. Właściwą reakcją jest złożenie odwołania do Dyrektora Izby Administracji Skarbowej za pośrednictwem urzędu, który wydał decyzję, w terminie 14 dni od doręczenia. Kluczowe do ustalenia: termin doręczenia decyzji, okres pełnienia funkcji w zarządzie oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P7" s="5" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono jako średnie, ale wynik nadal wymaga weryfikacji dokumentów i terminów. Nieustalony termin zwiększa niepewność i wymaga sprawdzenia przed podjęciem dalszych decyzji. Posiadanie pełnej dokumentacji umożliwia merytoryczną analizę zasadności decyzji ZUS nawet bez pewności co do terminu.</t>
+          <t>Decyzja Urzędu Skarbowego dotycząca odpowiedzialności byłego członka zarządu za zaległości podatkowe spółki wymaga sprawdzenia treści i terminu odwołania. Ryzyko jest umiarkowane — warto potwierdzić szczegóły.</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Decyzja Urzędu Skarbowego jest skierowana bezpośrednio do Ciebie jako byłego członka zarządu — organ podatkowy orzekł o Twojej odpowiedzialności za zaległości podatkowe spółki. Właściwą reakcją jest złożenie odwołania do Dyrektora Izby Administracji Skarbowej za pośrednictwem urzędu, który wydał decyzję, w terminie 14 dni od doręczenia. Kluczowe do ustalenia: termin doręczenia decyzji, okres pełnienia funkcji w zarządzie oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P8" s="5" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Decyzja ZUS przenosząca odpowiedzialność za zaległości składkowe spółki na członka zarządu (art.</t>
+          <t>Decyzja ZUS skierowana bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że organ orzekł o Twojej odpowiedzialności osobistej za zaległości składkowe spółki. Od tej decyzji przysługuje odwołanie w ściśle określonym terminie wskazanym w pouczeniu.</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Decyzja ZUS jest skierowana bezpośrednio do Ciebie jako byłego członka zarządu — organ orzekł o Twojej odpowiedzialności za zaległości składkowe spółki. Właściwą reakcją jest złożenie odwołania do ZUS (a następnie do sądu pracy i ubezpieczeń społecznych) w terminie wskazanym w pouczeniu. Kluczowe do ustalenia: termin doręczenia decyzji, okres pełnienia funkcji w zarządzie oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P9" s="5" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="N52" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ dokument EPU może uruchamiać krótki termin albo wymagać szybkiego potwierdzenia danych. Pozew EPU przeciwko członkowi zarządu może bezpośrednio dotyczyć odpowiedzialności członka zarządu, dlatego wymaga szczególnie ostrożnej weryfikacji adresata, podstawy roszczenia i terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu w związku z postępowaniem EPU (e-Sąd) oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej. Termin na złożenie odpowiedzi na pozew jest ściśle określony — brak reakcji może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej w związku z postępowaniem EPU (e-Sąd). Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu. Odpowiedź na pozew musi zawierać konkretne zarzuty i dowody — ogólne zaprzeczenie jest niewystarczające. Brak odpowiedzi w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="P52" s="5" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="N53" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Pozew EPU przeciwko członkowi zarządu może bezpośrednio dotyczyć odpowiedzialności członka zarządu, dlatego wymaga szczególnie ostrożnej weryfikacji adresata, podstawy roszczenia i terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu w związku z postępowaniem EPU (e-Sąd) oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej. Masz jeszcze czas na weryfikację dokumentów i przygotowanie odpowiedzi na pozew.</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej w związku z postępowaniem EPU (e-Sąd). Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu. Odpowiedź na pozew musi zawierać konkretne zarzuty i dowody — ogólne zaprzeczenie jest niewystarczające. Brak odpowiedzi w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="P53" s="5" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="N54" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ dokument EPU może uruchamiać krótki termin albo wymagać szybkiego potwierdzenia danych. Pozew EPU przeciwko członkowi zarządu może bezpośrednio dotyczyć odpowiedzialności członka zarządu, dlatego wymaga szczególnie ostrożnej weryfikacji adresata, podstawy roszczenia i terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu w związku z postępowaniem EPU (e-Sąd) oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej. Termin na złożenie odpowiedzi na pozew jest ściśle określony — brak reakcji może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej w związku z postępowaniem EPU (e-Sąd). Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu. Odpowiedź na pozew musi zawierać konkretne zarzuty i dowody — ogólne zaprzeczenie jest niewystarczające. Brak odpowiedzi w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="P54" s="5" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="N55" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Pozew EPU przeciwko członkowi zarządu może bezpośrednio dotyczyć odpowiedzialności członka zarządu, dlatego wymaga szczególnie ostrożnej weryfikacji adresata, podstawy roszczenia i terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu w związku z postępowaniem EPU (e-Sąd) oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej. Masz jeszcze czas na weryfikację dokumentów i przygotowanie odpowiedzi na pozew.</t>
         </is>
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej w związku z postępowaniem EPU (e-Sąd). Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu. Odpowiedź na pozew musi zawierać konkretne zarzuty i dowody — ogólne zaprzeczenie jest niewystarczające. Brak odpowiedzi w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="P55" s="5" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Pozew EPU przeciwko członkowi zarządu może bezpośrednio dotyczyć odpowiedzialności członka zarządu, dlatego wymaga szczególnie ostrożnej weryfikacji adresata, podstawy roszczenia i terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew powiązany z postępowaniem EPU skierowany do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści roszczenia i terminu. Ryzyko jest umiarkowane — warto potwierdzić podstawę odpowiedzialności i termin na reakcję.</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej w związku z postępowaniem EPU (e-Sąd). Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu. Odpowiedź na pozew musi zawierać konkretne zarzuty i dowody — ogólne zaprzeczenie jest niewystarczające. Brak odpowiedzi w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="P56" s="5" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="N57" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ dokument EPU może uruchamiać krótki termin albo wymagać szybkiego potwierdzenia danych. Pozew EPU przeciwko członkowi zarządu może bezpośrednio dotyczyć odpowiedzialności członka zarządu, dlatego wymaga szczególnie ostrożnej weryfikacji adresata, podstawy roszczenia i terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu w związku z postępowaniem EPU (e-Sąd) oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej. Termin na złożenie odpowiedzi na pozew jest ściśle określony — brak reakcji może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej w związku z postępowaniem EPU (e-Sąd). Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu. Odpowiedź na pozew musi zawierać konkretne zarzuty i dowody — ogólne zaprzeczenie jest niewystarczające. Brak odpowiedzi w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="P57" s="5" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Pozew EPU przeciwko członkowi zarządu może bezpośrednio dotyczyć odpowiedzialności członka zarządu, dlatego wymaga szczególnie ostrożnej weryfikacji adresata, podstawy roszczenia i terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu w związku z postępowaniem EPU (e-Sąd) oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej. Masz jeszcze czas na weryfikację dokumentów i przygotowanie odpowiedzi na pozew.</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej w związku z postępowaniem EPU (e-Sąd). Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu. Odpowiedź na pozew musi zawierać konkretne zarzuty i dowody — ogólne zaprzeczenie jest niewystarczające. Brak odpowiedzi w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="P58" s="5" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="N59" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Pozew EPU przeciwko członkowi zarządu może bezpośrednio dotyczyć odpowiedzialności członka zarządu, dlatego wymaga szczególnie ostrożnej weryfikacji adresata, podstawy roszczenia i terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew powiązany z postępowaniem EPU skierowany do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści roszczenia i terminu. Ryzyko jest umiarkowane — warto potwierdzić podstawę odpowiedzialności i termin na reakcję.</t>
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej w związku z postępowaniem EPU (e-Sąd). Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu. Odpowiedź na pozew musi zawierać konkretne zarzuty i dowody — ogólne zaprzeczenie jest niewystarczające. Brak odpowiedzi w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="P59" s="5" t="inlineStr">
@@ -8010,12 +8010,12 @@
       </c>
       <c r="N60" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ dokument EPU może uruchamiać krótki termin albo wymagać szybkiego potwierdzenia danych. Pozew EPU przeciwko członkowi zarządu może bezpośrednio dotyczyć odpowiedzialności członka zarządu, dlatego wymaga szczególnie ostrożnej weryfikacji adresata, podstawy roszczenia i terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu w związku z postępowaniem EPU (e-Sąd) oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej. Termin na złożenie odpowiedzi na pozew jest ściśle określony — brak reakcji może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="O60" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej w związku z postępowaniem EPU (e-Sąd). Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu. Odpowiedź na pozew musi zawierać konkretne zarzuty i dowody — ogólne zaprzeczenie jest niewystarczające. Brak odpowiedzi w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="P60" s="5" t="inlineStr">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="N61" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Pozew EPU przeciwko członkowi zarządu może bezpośrednio dotyczyć odpowiedzialności członka zarządu, dlatego wymaga szczególnie ostrożnej weryfikacji adresata, podstawy roszczenia i terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu w związku z postępowaniem EPU (e-Sąd) oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej. Masz jeszcze czas na weryfikację dokumentów i przygotowanie odpowiedzi na pozew.</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej w związku z postępowaniem EPU (e-Sąd). Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu. Odpowiedź na pozew musi zawierać konkretne zarzuty i dowody — ogólne zaprzeczenie jest niewystarczające. Brak odpowiedzi w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="P61" s="5" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="N62" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ dokument EPU może uruchamiać krótki termin albo wymagać szybkiego potwierdzenia danych. Pozew EPU przeciwko członkowi zarządu może bezpośrednio dotyczyć odpowiedzialności członka zarządu, dlatego wymaga szczególnie ostrożnej weryfikacji adresata, podstawy roszczenia i terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu w związku z postępowaniem EPU (e-Sąd) oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej. Termin na złożenie odpowiedzi na pozew jest ściśle określony — brak reakcji może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej w związku z postępowaniem EPU (e-Sąd). Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu. Odpowiedź na pozew musi zawierać konkretne zarzuty i dowody — ogólne zaprzeczenie jest niewystarczające. Brak odpowiedzi w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="P62" s="5" t="inlineStr">
@@ -8331,12 +8331,12 @@
       </c>
       <c r="N63" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ dokument EPU może uruchamiać krótki termin albo wymagać szybkiego potwierdzenia danych. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu — jeśli spółka nie złoży odpowiedzi w terminie lub przegra, wierzyciel po bezskutecznej egzekucji może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH. Termin jest ściśle określony.</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P63" s="5" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="N64" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu. Jeśli spółka nie zareaguje lub przegra, wierzyciel może po bezskutecznej egzekucji dochodzić roszczeń bezpośrednio od Ciebie jako byłego członka zarządu z art. 299 KSH. Masz czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P64" s="5" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="N65" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ dokument EPU może uruchamiać krótki termin albo wymagać szybkiego potwierdzenia danych. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu — jeśli spółka nie złoży odpowiedzi w terminie lub przegra, wierzyciel po bezskutecznej egzekucji może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH. Termin jest ściśle określony.</t>
         </is>
       </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P65" s="5" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="N66" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu. Jeśli spółka nie zareaguje lub przegra, wierzyciel może po bezskutecznej egzekucji dochodzić roszczeń bezpośrednio od Ciebie jako byłego członka zarządu z art. 299 KSH. Masz czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O66" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P66" s="5" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="N67" s="5" t="inlineStr">
         <is>
-          <t>Sprawa ma niższy poziom pilności, ale nadal warto potwierdzić podstawowe dane, zwłaszcza adresata, termin i treść pouczenia. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU jest na tym etapie oceniana jako niższe ryzyko. Warto jednak potwierdzić, czy spółka jest aktywnie reprezentowana — brak reakcji mógłby doprowadzić do wyroku zaocznego i ryzyka z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P67" s="5" t="inlineStr">
@@ -8866,12 +8866,12 @@
       </c>
       <c r="N68" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU jest na etapie pozwu i wymaga sprawdzenia, czy spółka podjęła działania obronne. Brak reakcji może prowadzić do wyroku zaocznego i w przyszłości do ryzyka z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P68" s="5" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="N69" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ dokument EPU może uruchamiać krótki termin albo wymagać szybkiego potwierdzenia danych. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu — jeśli spółka nie złoży odpowiedzi w terminie lub przegra, wierzyciel po bezskutecznej egzekucji może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH. Termin jest ściśle określony.</t>
         </is>
       </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P69" s="5" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="N70" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu. Jeśli spółka nie zareaguje lub przegra, wierzyciel może po bezskutecznej egzekucji dochodzić roszczeń bezpośrednio od Ciebie jako byłego członka zarządu z art. 299 KSH. Masz czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O70" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P70" s="5" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="N71" s="5" t="inlineStr">
         <is>
-          <t>Sprawa ma niższy poziom pilności, ale nadal warto potwierdzić podstawowe dane, zwłaszcza adresata, termin i treść pouczenia. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU jest na tym etapie oceniana jako niższe ryzyko. Warto jednak potwierdzić, czy spółka jest aktywnie reprezentowana — brak reakcji mógłby doprowadzić do wyroku zaocznego i ryzyka z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O71" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P71" s="5" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="N72" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU jest na etapie pozwu i wymaga sprawdzenia, czy spółka podjęła działania obronne. Brak reakcji może prowadzić do wyroku zaocznego i w przyszłości do ryzyka z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O72" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P72" s="5" t="inlineStr">
@@ -9401,12 +9401,12 @@
       </c>
       <c r="N73" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ dokument EPU może uruchamiać krótki termin albo wymagać szybkiego potwierdzenia danych. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu — jeśli spółka nie złoży odpowiedzi w terminie lub przegra, wierzyciel po bezskutecznej egzekucji może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH. Termin jest ściśle określony.</t>
         </is>
       </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P73" s="5" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="N74" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu. Jeśli spółka nie zareaguje lub przegra, wierzyciel może po bezskutecznej egzekucji dochodzić roszczeń bezpośrednio od Ciebie jako byłego członka zarządu z art. 299 KSH. Masz czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O74" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P74" s="5" t="inlineStr">
@@ -9615,12 +9615,12 @@
       </c>
       <c r="N75" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU jest na etapie pozwu i wymaga sprawdzenia, czy spółka podjęła działania obronne. Brak reakcji może prowadzić do wyroku zaocznego i w przyszłości do ryzyka z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P75" s="5" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="N76" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ dokument EPU może uruchamiać krótki termin albo wymagać szybkiego potwierdzenia danych. Pozew EPU przeciwko spółce nie jest automatycznie dokumentem bezpośrednio skierowanym do członka zarządu, ale może być ważny dla oceny etapu sprawy i dalszego ryzyka. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa dotycząca spółki powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu — jeśli spółka nie złoży odpowiedzi w terminie lub przegra, wierzyciel po bezskutecznej egzekucji może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH. Termin jest ściśle określony.</t>
         </is>
       </c>
       <c r="O76" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pozwu, treść pouczenia, podstawę roszczenia oraz to, czy dokument dotyczy spółki, członka zarządu czy obu tych obszarów.</t>
+          <t>Sprawa powiązana z postępowaniem EPU (e-Sąd) jest na etapie pozwu skierowanego do spółki. Właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd. Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P76" s="5" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="N81" s="5" t="inlineStr">
         <is>
-          <t>Nakaz jest skierowany bezpośrednio do Ciebie. Ryzyko jest ocenione jako umiarkowane — warto jednak potwierdzić termin i podstawę roszczenia, zanim podejmiesz decyzję o reakcji procesowej.</t>
+          <t>Nakaz jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu. Ryzyko jest ocenione jako umiarkowane — warto jednak potwierdzić termin i podstawę roszczenia, zanim podejmiesz decyzję o reakcji procesowej.</t>
         </is>
       </c>
       <c r="O81" s="5" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="N84" s="5" t="inlineStr">
         <is>
-          <t>Nakaz jest skierowany bezpośrednio do Ciebie. Ryzyko jest ocenione jako umiarkowane — warto jednak potwierdzić termin i podstawę roszczenia, zanim podejmiesz decyzję o reakcji procesowej.</t>
+          <t>Nakaz jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu. Ryzyko jest ocenione jako umiarkowane — warto jednak potwierdzić termin i podstawę roszczenia, zanim podejmiesz decyzję o reakcji procesowej.</t>
         </is>
       </c>
       <c r="O84" s="5" t="inlineStr">
@@ -12635,12 +12635,12 @@
       </c>
       <c r="N103" s="5" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko wynika z połączenia rodzaju dokumentu, potrzeby weryfikacji terminu oraz niepewności danych wymagających sprawdzenia. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Dokument wskazuje na czynne postępowanie egzekucyjne wobec spółki na etapie zajęcia.</t>
+          <t>Pismo komornika skierowane do Ciebie jako byłego członka zarządu oznacza, że postępowanie egzekucyjne jest w toku na podstawie tytułu wykonawczego. Twoje zasoby majątkowe mogą zostać zajęte — wymagana jest pilna weryfikacja.</t>
         </is>
       </c>
       <c r="O103" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
         </is>
       </c>
       <c r="P103" s="5" t="inlineStr">
@@ -12746,12 +12746,12 @@
       </c>
       <c r="N104" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Brak pełnych dokumentów ogranicza pewność wstępnej oceny.</t>
+          <t>Pismo komornika skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel wszczął już egzekucję na podstawie tytułu wykonawczego. To jeden z najbardziej zaawansowanych etapów postępowania — wymagana jest natychmiastowa weryfikacja.</t>
         </is>
       </c>
       <c r="O104" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
         </is>
       </c>
       <c r="P104" s="5" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="N105" s="5" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko wynika z połączenia rodzaju dokumentu, potrzeby weryfikacji terminu oraz niepewności danych wymagających sprawdzenia. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy. W pierwszej kolejności należy ustalić, czy dłużnik (spółka) posiada skuteczne zarzuty wobec tytułu wykonawczego lub czy nastąpiły uchybienia proceduralne komornika.</t>
+          <t>Pismo komornika skierowane do Ciebie jako byłego członka zarządu oznacza, że postępowanie egzekucyjne jest w toku na podstawie tytułu wykonawczego. Twoje zasoby majątkowe mogą zostać zajęte — wymagana jest pilna weryfikacja.</t>
         </is>
       </c>
       <c r="O105" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
         </is>
       </c>
       <c r="P105" s="5" t="inlineStr">
@@ -12960,12 +12960,12 @@
       </c>
       <c r="N106" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy. Status rezygnacji lub odwołania oraz aktualność wpisu w KRS wymagają weryfikacji.</t>
+          <t>Pismo komornika skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel wszczął już egzekucję na podstawie tytułu wykonawczego. To jeden z najbardziej zaawansowanych etapów postępowania — wymagana jest natychmiastowa weryfikacja.</t>
         </is>
       </c>
       <c r="O106" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
         </is>
       </c>
       <c r="P106" s="5" t="inlineStr">
@@ -13067,12 +13067,12 @@
       </c>
       <c r="N107" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono niżej, ale podstawowe dane nadal powinny zostać potwierdzone.</t>
+          <t>Pismo komornika skierowane do Ciebie jako byłego członka zarządu jest na tym etapie oceniane jako niższe ryzyko. Warto jednak potwierdzić tytuł wykonawczy i zakres egzekucji.</t>
         </is>
       </c>
       <c r="O107" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
         </is>
       </c>
       <c r="P107" s="5" t="inlineStr">
@@ -13178,12 +13178,12 @@
       </c>
       <c r="N108" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono niżej, ale podstawowe dane nadal powinny zostać potwierdzone.</t>
+          <t>Pismo komornika skierowane do Ciebie jako byłego członka zarządu jest na tym etapie oceniane jako niższe ryzyko. Warto jednak potwierdzić tytuł wykonawczy i zakres egzekucji.</t>
         </is>
       </c>
       <c r="O108" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
         </is>
       </c>
       <c r="P108" s="5" t="inlineStr">
@@ -13404,12 +13404,12 @@
       </c>
       <c r="N110" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Nieustalony termin zwiększa niepewność i wymaga sprawdzenia przed podjęciem dalszych decyzji. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Brak jakichkolwiek informacji o charakterze postępowania egzekucyjnego i własnym statusie w zarządzie spółki uniemożliwia precyzyjną ocenę ryzyka.</t>
+          <t>Pismo komornika skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel wszczął już egzekucję na podstawie tytułu wykonawczego. To jeden z najbardziej zaawansowanych etapów postępowania — wymagana jest natychmiastowa weryfikacja.</t>
         </is>
       </c>
       <c r="O110" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
         </is>
       </c>
       <c r="P110" s="5" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="N111" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Brak pełnych dokumentów ogranicza pewność wstępnej oceny.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Termin na złożenie odpowiedzi na pozew jest ściśle określony przez sąd — brak reakcji w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="O111" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu (zwykle 2 tygodnie od doręczenia). Odpowiedź musi zawierać konkretne zarzuty i dowody — kluczowe do ustalenia: data i dokument rezygnacji lub odwołania z zarządu, aktualność wpisu w KRS w chwili powstania zobowiązania oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P111" s="5" t="inlineStr">
@@ -13630,12 +13630,12 @@
       </c>
       <c r="N112" s="5" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko wynika z połączenia rodzaju dokumentu, potrzeby weryfikacji terminu oraz niepewności danych wymagających sprawdzenia. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy. Głównym zadaniem jest ustalenie: (1) które zobowiązania powstały w czasie kadencji, (2) czy i kiedy zaistniały przesłanki do ogłoszenia upadłości, (3) czy złożono wniosek w terminie lub czy istniały inne podstawy egzoneracji.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Masz jeszcze czas na weryfikację dokumentów i przygotowanie odpowiedzi na pozew — ale termin jest ściśle określony.</t>
         </is>
       </c>
       <c r="O112" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu (zwykle 2 tygodnie od doręczenia). Odpowiedź musi zawierać konkretne zarzuty i dowody — kluczowe do ustalenia: data i dokument rezygnacji lub odwołania z zarządu, aktualność wpisu w KRS w chwili powstania zobowiązania oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P112" s="5" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="N113" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Status rezygnacji lub odwołania oraz aktualność wpisu w KRS wymagają weryfikacji.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Termin na złożenie odpowiedzi na pozew jest ściśle określony przez sąd — brak reakcji w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="O113" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu (zwykle 2 tygodnie od doręczenia). Odpowiedź musi zawierać konkretne zarzuty i dowody — kluczowe do ustalenia: data i dokument rezygnacji lub odwołania z zarządu, aktualność wpisu w KRS w chwili powstania zobowiązania oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P113" s="5" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="N114" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Masz jeszcze czas na weryfikację dokumentów i przygotowanie odpowiedzi na pozew — ale termin jest ściśle określony.</t>
         </is>
       </c>
       <c r="O114" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu (zwykle 2 tygodnie od doręczenia). Odpowiedź musi zawierać konkretne zarzuty i dowody — kluczowe do ustalenia: data i dokument rezygnacji lub odwołania z zarządu, aktualność wpisu w KRS w chwili powstania zobowiązania oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P114" s="5" t="inlineStr">
@@ -13959,12 +13959,12 @@
       </c>
       <c r="N115" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono jako średnie, ale wynik nadal wymaga weryfikacji dokumentów i terminów.</t>
+          <t>Pozew skierowany do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści roszczenia i terminu na odpowiedź. Ryzyko jest umiarkowane — warto jednak potwierdzić podstawę odpowiedzialności i przygotować się do reakcji procesowej.</t>
         </is>
       </c>
       <c r="O115" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu (zwykle 2 tygodnie od doręczenia). Odpowiedź musi zawierać konkretne zarzuty i dowody — kluczowe do ustalenia: data i dokument rezygnacji lub odwołania z zarządu, aktualność wpisu w KRS w chwili powstania zobowiązania oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P115" s="5" t="inlineStr">
@@ -14066,12 +14066,12 @@
       </c>
       <c r="N116" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy. Status rezygnacji lub odwołania oraz aktualność wpisu w KRS wymagają weryfikacji. 299, ustalenie daty powstania zobowiązania i ocena przesłanek egzoneracyjnych.</t>
+          <t>Wysoki poziom ryzyka wynika przede wszystkim z wagi dokumentu — pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi odpowiedzialności osobistej z art. 299 KSH, nie przez spółkę. Sam termin (14 dni) jest jeszcze komfortowy, ale złożoność sprawy — rezygnacja, aktualność wpisu w KRS, data powstania zobowiązania — wymaga szybkiego zebrania dokumentów i oceny możliwych przesłanek obrony.</t>
         </is>
       </c>
       <c r="O116" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel pominął spółkę i dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Aby ocenić możliwość obrony, kluczowe są: data i dokument rezygnacji lub odwołania, aktualność wpisu w KRS, a przede wszystkim to, kiedy powstało dochodzone zobowiązanie i czy w tamtym czasie zachodziły przesłanki do złożenia wniosku o upadłość.</t>
         </is>
       </c>
       <c r="P116" s="5" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="N117" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Masz jeszcze czas na weryfikację dokumentów i przygotowanie odpowiedzi na pozew — ale termin jest ściśle określony.</t>
         </is>
       </c>
       <c r="O117" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu (zwykle 2 tygodnie od doręczenia). Odpowiedź musi zawierać konkretne zarzuty i dowody — kluczowe do ustalenia: data i dokument rezygnacji lub odwołania z zarządu, aktualność wpisu w KRS w chwili powstania zobowiązania oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P117" s="5" t="inlineStr">
@@ -14280,12 +14280,12 @@
       </c>
       <c r="N118" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono jako średnie, ale wynik nadal wymaga weryfikacji dokumentów i terminów. Pomimo że na tym etapie nie ma jeszcze postępowania sądowego, wymagana jest natychmiastowa analiza ekspozycji na ryzyko.</t>
+          <t>Pozew skierowany do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści roszczenia i terminu na odpowiedź. Ryzyko jest umiarkowane — warto jednak potwierdzić podstawę odpowiedzialności i przygotować się do reakcji procesowej.</t>
         </is>
       </c>
       <c r="O118" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu (zwykle 2 tygodnie od doręczenia). Odpowiedź musi zawierać konkretne zarzuty i dowody — kluczowe do ustalenia: data i dokument rezygnacji lub odwołania z zarządu, aktualność wpisu w KRS w chwili powstania zobowiązania oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P118" s="5" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="N119" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Termin na złożenie odpowiedzi na pozew jest ściśle określony przez sąd — brak reakcji w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="O119" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu (zwykle 2 tygodnie od doręczenia). Odpowiedź musi zawierać konkretne zarzuty i dowody — kluczowe do ustalenia: data i dokument rezygnacji lub odwołania z zarządu, aktualność wpisu w KRS w chwili powstania zobowiązania oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P119" s="5" t="inlineStr">
@@ -14494,12 +14494,12 @@
       </c>
       <c r="N120" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Masz jeszcze czas na weryfikację dokumentów i przygotowanie odpowiedzi na pozew — ale termin jest ściśle określony.</t>
         </is>
       </c>
       <c r="O120" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu (zwykle 2 tygodnie od doręczenia). Odpowiedź musi zawierać konkretne zarzuty i dowody — kluczowe do ustalenia: data i dokument rezygnacji lub odwołania z zarządu, aktualność wpisu w KRS w chwili powstania zobowiązania oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P120" s="5" t="inlineStr">
@@ -14605,12 +14605,12 @@
       </c>
       <c r="N121" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Nieustalony termin zwiększa niepewność i wymaga sprawdzenia przed podjęciem dalszych decyzji. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Brak wiedzy o własnym statusie formalnym i naturze pisma przy jednoczesnym otrzymaniu wezwania/pisma sądowego wskazującego na art.</t>
+          <t>Pozew skierowany bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Termin na złożenie odpowiedzi na pozew jest ściśle określony przez sąd — brak reakcji w terminie może skutkować wyrokiem zaocznym.</t>
         </is>
       </c>
       <c r="O121" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany bezpośrednio do Ciebie jako byłego członka zarządu — wierzyciel dochodzi Twojej odpowiedzialności osobistej z art. 299 KSH. Właściwą reakcją jest złożenie odpowiedzi na pozew w terminie wskazanym w pouczeniu (zwykle 2 tygodnie od doręczenia). Odpowiedź musi zawierać konkretne zarzuty i dowody — kluczowe do ustalenia: data i dokument rezygnacji lub odwołania z zarządu, aktualność wpisu w KRS w chwili powstania zobowiązania oraz czy złożono wniosek o upadłość we właściwym czasie.</t>
         </is>
       </c>
       <c r="P121" s="5" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="N122" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew złożony przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności byłego członka zarządu z art. 299 KSH — jeśli wyrok będzie niekorzystny i egzekucja wobec spółki okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na odpowiedź na pozew jest ściśle określony.</t>
         </is>
       </c>
       <c r="O122" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P122" s="5" t="inlineStr">
@@ -14819,12 +14819,12 @@
       </c>
       <c r="N123" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew przeciwko spółce wymaga sprawdzenia, czy spółka podjęła już działania obronne. Brak odpowiedzi na pozew w terminie może doprowadzić do wyroku zaocznego i w przyszłości do ryzyka z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O123" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P123" s="5" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="N124" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew złożony przeciwko spółce stwarza bezpośrednie ryzyko dla byłego członka zarządu — jeśli spółka nie złoży odpowiedzi na pozew w terminie lub przegra, wierzyciel po bezskutecznej egzekucji może skierować roszczenie bezpośrednio do Ciebie z art. 299 KSH. Termin na odpowiedź na pozew jest ściśle określony przez sąd.</t>
         </is>
       </c>
       <c r="O124" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P124" s="5" t="inlineStr">
@@ -15033,12 +15033,12 @@
       </c>
       <c r="N125" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew złożony przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności byłego członka zarządu z art. 299 KSH — jeśli wyrok będzie niekorzystny i egzekucja wobec spółki okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na odpowiedź na pozew jest ściśle określony.</t>
         </is>
       </c>
       <c r="O125" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P125" s="5" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="N126" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew przeciwko spółce wymaga sprawdzenia, czy spółka podjęła już działania obronne. Brak odpowiedzi na pozew w terminie może doprowadzić do wyroku zaocznego i w przyszłości do ryzyka z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O126" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P126" s="5" t="inlineStr">
@@ -15247,12 +15247,12 @@
       </c>
       <c r="N127" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew złożony przeciwko spółce stwarza bezpośrednie ryzyko dla byłego członka zarządu — jeśli spółka nie złoży odpowiedzi na pozew w terminie lub przegra, wierzyciel po bezskutecznej egzekucji może skierować roszczenie bezpośrednio do Ciebie z art. 299 KSH. Termin na odpowiedź na pozew jest ściśle określony przez sąd.</t>
         </is>
       </c>
       <c r="O127" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P127" s="5" t="inlineStr">
@@ -15354,12 +15354,12 @@
       </c>
       <c r="N128" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew złożony przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności byłego członka zarządu z art. 299 KSH — jeśli wyrok będzie niekorzystny i egzekucja wobec spółki okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na odpowiedź na pozew jest ściśle określony.</t>
         </is>
       </c>
       <c r="O128" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P128" s="5" t="inlineStr">
@@ -15461,12 +15461,12 @@
       </c>
       <c r="N129" s="5" t="inlineStr">
         <is>
-          <t>Sprawa ma niższy poziom pilności, ale nadal warto sprawdzić podstawowe dane i dokumenty. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew przeciwko spółce jest na tym etapie oceniany jako niższe ryzyko bezpośrednie. Warto jednak potwierdzić, czy spółka złożyła odpowiedź na pozew — brak reakcji mógłby doprowadzić do wyroku zaocznego i ryzyka z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O129" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P129" s="5" t="inlineStr">
@@ -15568,12 +15568,12 @@
       </c>
       <c r="N130" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew przeciwko spółce wymaga sprawdzenia, czy spółka podjęła już działania obronne. Brak odpowiedzi na pozew w terminie może doprowadzić do wyroku zaocznego i w przyszłości do ryzyka z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O130" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P130" s="5" t="inlineStr">
@@ -15675,12 +15675,12 @@
       </c>
       <c r="N131" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew złożony przeciwko spółce stwarza bezpośrednie ryzyko dla byłego członka zarządu — jeśli spółka nie złoży odpowiedzi na pozew w terminie lub przegra, wierzyciel po bezskutecznej egzekucji może skierować roszczenie bezpośrednio do Ciebie z art. 299 KSH. Termin na odpowiedź na pozew jest ściśle określony przez sąd.</t>
         </is>
       </c>
       <c r="O131" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P131" s="5" t="inlineStr">
@@ -15782,12 +15782,12 @@
       </c>
       <c r="N132" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew złożony przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności byłego członka zarządu z art. 299 KSH — jeśli wyrok będzie niekorzystny i egzekucja wobec spółki okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na odpowiedź na pozew jest ściśle określony.</t>
         </is>
       </c>
       <c r="O132" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P132" s="5" t="inlineStr">
@@ -15889,12 +15889,12 @@
       </c>
       <c r="N133" s="5" t="inlineStr">
         <is>
-          <t>Sprawa ma niższy poziom pilności, ale nadal warto sprawdzić podstawowe dane i dokumenty. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew przeciwko spółce jest na tym etapie oceniany jako niższe ryzyko bezpośrednie. Warto jednak potwierdzić, czy spółka złożyła odpowiedź na pozew — brak reakcji mógłby doprowadzić do wyroku zaocznego i ryzyka z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O133" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P133" s="5" t="inlineStr">
@@ -15996,12 +15996,12 @@
       </c>
       <c r="N134" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew przeciwko spółce wymaga sprawdzenia, czy spółka podjęła już działania obronne. Brak odpowiedzi na pozew w terminie może doprowadzić do wyroku zaocznego i w przyszłości do ryzyka z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O134" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P134" s="5" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="N135" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew złożony przeciwko spółce stwarza bezpośrednie ryzyko dla byłego członka zarządu — jeśli spółka nie złoży odpowiedzi na pozew w terminie lub przegra, wierzyciel po bezskutecznej egzekucji może skierować roszczenie bezpośrednio do Ciebie z art. 299 KSH. Termin na odpowiedź na pozew jest ściśle określony przez sąd.</t>
         </is>
       </c>
       <c r="O135" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P135" s="5" t="inlineStr">
@@ -16210,12 +16210,12 @@
       </c>
       <c r="N136" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew złożony przeciwko spółce może w konsekwencji prowadzić do osobistej odpowiedzialności byłego członka zarządu z art. 299 KSH — jeśli wyrok będzie niekorzystny i egzekucja wobec spółki okaże się bezskuteczna. Masz jeszcze czas na weryfikację, ale termin na odpowiedź na pozew jest ściśle określony.</t>
         </is>
       </c>
       <c r="O136" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P136" s="5" t="inlineStr">
@@ -16317,12 +16317,12 @@
       </c>
       <c r="N137" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew przeciwko spółce wymaga sprawdzenia, czy spółka podjęła już działania obronne. Brak odpowiedzi na pozew w terminie może doprowadzić do wyroku zaocznego i w przyszłości do ryzyka z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O137" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P137" s="5" t="inlineStr">
@@ -16424,12 +16424,12 @@
       </c>
       <c r="N138" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Pozew złożony przeciwko spółce stwarza bezpośrednie ryzyko dla byłego członka zarządu — jeśli spółka nie złoży odpowiedzi na pozew w terminie lub przegra, wierzyciel po bezskutecznej egzekucji może skierować roszczenie bezpośrednio do Ciebie z art. 299 KSH. Termin na odpowiedź na pozew jest ściśle określony przez sąd.</t>
         </is>
       </c>
       <c r="O138" s="5" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Pozew jest skierowany do spółki — właściwą reakcją spółki jest złożenie odpowiedzi na pozew w terminie wskazanym przez sąd (zwykle 2 tygodnie od doręczenia). Brak odpowiedzi spowoduje wyrok zaoczny i otworzy wierzycielowi drogę do egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje złożyć odpowiedź na pozew.</t>
         </is>
       </c>
       <c r="P138" s="5" t="inlineStr">
@@ -16531,12 +16531,12 @@
       </c>
       <c r="N139" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono jako średnie, ale wynik nadal wymaga weryfikacji dokumentów i terminów. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy. Rekomendowany jest Audyt 48h nastawiony na kwalifikację pisma, potwierdzenie terminu reakcji i przygotowanie planu działań odpowiedniego do statusu użytkownika w zarządzie.</t>
+          <t>Wezwanie przedsądowe skierowane do Ciebie jako byłego członka zarządu wymaga sprawdzenia podstawy roszczenia. Ryzyko jest umiarkowane — warto potwierdzić zasadność żądania i dostępne opcje odpowiedzi.</t>
         </is>
       </c>
       <c r="O139" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie przedsądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Wierzyciel domaga się zapłaty lub wyjaśnień przed złożeniem pozwu. Brak reakcji może przyspieszyć skierowanie sprawy do sądu. Kluczowe do ustalenia: termin wyznaczony przez wierzyciela, podstawa roszczenia (art. 299 KSH lub inna), zasadność żądania oraz możliwości odpowiedzi — zapłata, wyjaśnienia lub przygotowanie obrony.</t>
         </is>
       </c>
       <c r="P139" s="5" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="N140" s="5" t="inlineStr">
         <is>
-          <t>Ryzyko oceniono niżej, ale podstawowe dane nadal powinny zostać potwierdzone. Na obecnym etapie sprawa ma charakter prewencyjny — nie widać wysokiej presji czasowej ani istotnych braków formalnych, natomiast potrzebne jest uporządkowanie sytuacji i ocena dalszych scenariuszy.</t>
+          <t>Wezwanie przedsądowe skierowane do Ciebie jako byłego członka zarządu jest na tym etapie oceniane jako niższe ryzyko. Warto jednak potwierdzić treść żądania i termin wyznaczony przez wierzyciela, aby nie przeoczyć koniecznych działań.</t>
         </is>
       </c>
       <c r="O140" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie przedsądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Wierzyciel domaga się zapłaty lub wyjaśnień przed złożeniem pozwu. Brak reakcji może przyspieszyć skierowanie sprawy do sądu. Kluczowe do ustalenia: termin wyznaczony przez wierzyciela, podstawa roszczenia (art. 299 KSH lub inna), zasadność żądania oraz możliwości odpowiedzi — zapłata, wyjaśnienia lub przygotowanie obrony.</t>
         </is>
       </c>
       <c r="P140" s="5" t="inlineStr">
@@ -16749,12 +16749,12 @@
       </c>
       <c r="N141" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Nieustalony termin zwiększa niepewność i wymaga sprawdzenia przed podjęciem dalszych decyzji. Brak pełnych dokumentów ogranicza pewność wstępnej oceny. Wysoki wynik w tej konfiguracji wynika przede wszystkim z kumulacji niepewności: nieustalonego terminu, braku dokumentów i niejasnego statusu w zarządzie.</t>
+          <t>Wezwanie przedsądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel grozi złożeniem pozwu i wyznaczył krótki termin do zapłaty lub wyjaśnień. Brak reakcji może przyspieszyć skierowanie sprawy do sądu.</t>
         </is>
       </c>
       <c r="O141" s="5" t="inlineStr">
         <is>
-          <t>W praktyce najpierw trzeba potwierdzić datę doręczenia, sposób liczenia terminu, adresata pisma, podstawę roszczenia oraz dokumenty dotyczące pełnienia funkcji w zarządzie i aktualności wpisu w KRS.</t>
+          <t>Wezwanie przedsądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Wierzyciel domaga się zapłaty lub wyjaśnień przed złożeniem pozwu. Brak reakcji może przyspieszyć skierowanie sprawy do sądu. Kluczowe do ustalenia: termin wyznaczony przez wierzyciela, podstawa roszczenia (art. 299 KSH lub inna), zasadność żądania oraz możliwości odpowiedzi — zapłata, wyjaśnienia lub przygotowanie obrony.</t>
         </is>
       </c>
       <c r="P141" s="5" t="inlineStr">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -2703,7 +2703,7 @@
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga weryfikacji i uporządkowania danych. Bez ustalenia rodzaju pisma nie można precyzyjnie ocenić charakteru sprawy — czas na reakcję i dane z formularza wskazują, że nie warto zwlekać.</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga ostrożnej weryfikacji. Brak pewności co do rodzaju dokumentu ogranicza precyzję oceny — nie można wykluczyć, że pismo wymaga szybkiej reakcji.</t>
         </is>
       </c>
       <c r="O12" s="5" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga pilnej weryfikacji. Czas na reakcję i dane z formularza wskazują na podwyższoną pilność — jednak bez ustalenia rodzaju pisma nie można określić właściwego kierunku działania.</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga weryfikacji i uporządkowania danych. Bez ustalenia rodzaju pisma nie można precyzyjnie ocenić charakteru sprawy — czas na reakcję i dane z formularza wskazują, że nie warto zwlekać.</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga ostrożnej weryfikacji. Brak pewności co do rodzaju dokumentu ogranicza precyzję oceny — nie można wykluczyć, że pismo wymaga szybkiej reakcji.</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>Podwyższona pilność wynika przede wszystkim z rodzaju dokumentu oraz możliwego biegu terminu na reakcję. Czas na reakcję może być ograniczony, dlatego kluczowe jest potwierdzenie daty doręczenia i treści pouczenia. Dosłanie dokumentów może istotnie zmienić szczegółową ocenę sprawy. Działania równoległe: (1) identyfikacja sygnatury, nadawcy i charakteru żądania, (2) weryfikacja własnego statusu formalnego w KRS i relacji do sprawy, (3) ustalenie czy termin wskazany w piśmie jest terminem procesowym (prekluzja) czy administracyjnym (przywrócalny).</t>
+          <t>Podwyższona pilność wynika z możliwego biegu terminu na reakcję. Czas może być ograniczony — kluczowe jest najpierw ustalenie rodzaju pisma, a następnie potwierdzenie daty doręczenia i treści pouczenia.</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga weryfikacji i uporządkowania danych. Bez ustalenia rodzaju pisma nie można precyzyjnie ocenić charakteru sprawy — czas na reakcję i dane z formularza wskazują, że nie warto zwlekać.</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Sprawa ma niższy poziom pilności, ale nadal warto sprawdzić podstawowe dane i dokumenty. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa ma niższy poziom pilności, ale brak pewności co do rodzaju dokumentu ogranicza pewność tej oceny. Warto potwierdzić podstawowe dane i ustalić, z jakim pismem masz do czynienia.</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga ostrożnej weryfikacji. Brak pewności co do rodzaju dokumentu ogranicza precyzję oceny — nie można wykluczyć, że pismo wymaga szybkiej reakcji.</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga pilnej weryfikacji. Czas na reakcję i dane z formularza wskazują na podwyższoną pilność — jednak bez ustalenia rodzaju pisma nie można określić właściwego kierunku działania.</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga weryfikacji i uporządkowania danych. Bez ustalenia rodzaju pisma nie można precyzyjnie ocenić charakteru sprawy — czas na reakcję i dane z formularza wskazują, że nie warto zwlekać.</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Sprawa ma niższy poziom pilności, ale nadal warto sprawdzić podstawowe dane i dokumenty. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa ma niższy poziom pilności, ale brak pewności co do rodzaju dokumentu ogranicza pewność tej oceny. Warto potwierdzić podstawowe dane i ustalić, z jakim pismem masz do czynienia.</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga ostrożnej weryfikacji. Brak pewności co do rodzaju dokumentu ogranicza precyzję oceny — nie można wykluczyć, że pismo wymaga szybkiej reakcji.</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga pilnej weryfikacji. Czas na reakcję i dane z formularza wskazują na podwyższoną pilność — jednak bez ustalenia rodzaju pisma nie można określić właściwego kierunku działania.</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga uporządkowania i szybkiej weryfikacji, choć nie musi oznaczać krytycznego terminu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga weryfikacji i uporządkowania danych. Bez ustalenia rodzaju pisma nie można precyzyjnie ocenić charakteru sprawy — czas na reakcję i dane z formularza wskazują, że nie warto zwlekać.</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga ostrożnej weryfikacji, zwłaszcza jeżeli brakuje danych o doręczeniu, adresacie albo statusie dokumentu. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga ostrożnej weryfikacji. Brak pewności co do rodzaju dokumentu ogranicza precyzję oceny — nie można wykluczyć, że pismo wymaga szybkiej reakcji.</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji, ponieważ połączenie rodzaju dokumentu, czasu na reakcję albo reguł bezpieczeństwa wskazuje na podwyższoną pilność. Na ocenę wpływają przede wszystkim rodzaj dokumentu, czas na reakcję, informacja o EPU oraz dane wskazane w formularzu.</t>
+          <t>Sprawa wymaga pilnej weryfikacji. Czas na reakcję i dane z formularza wskazują na podwyższoną pilność — jednak bez ustalenia rodzaju pisma nie można określić właściwego kierunku działania.</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -1518,7 +1518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W173"/>
+  <dimension ref="A1:W186"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="8.25" customWidth="1" style="4" min="1" max="1"/>
@@ -20219,6 +20219,1345 @@
       </c>
       <c r="V173" s="5" t="n"/>
       <c r="W173" s="5" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>BASE_173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — pismo organu publicznego ZUS/US, 0-3</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_0_3</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — pilna reakcja wymagana.</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga pilnej reakcji. Termin na złożenie wyjaśnień lub odwołania jest ściśle określony w pouczeniu — jego przekroczenie może zamknąć drogę do obrony.</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Ze względu na krótki termin warto jak najszybciej przejść do Audytu 48h, aby ustalić termin, zakres żądania i właściwy tryb odpowiedzi na pismo organu.</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S174" t="n">
+        <v>1</v>
+      </c>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr"/>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>BASE_174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, 0-3</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_0_3</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — szybka weryfikacja i odpowiedź.</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga przygotowanej odpowiedzi. Właściwą formą jest złożenie wyjaśnień i dokumentów — nie sprzeciw ani pismo do sądu. Czas na reakcję jest ograniczony.</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma, termin i możliwe kierunki odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S175" t="n">
+        <v>1</v>
+      </c>
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr"/>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>BASE_175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — pismo organu publicznego ZUS/US, 4-7</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_4_7</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — pilna reakcja wymagana.</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga pilnej reakcji. Termin na złożenie wyjaśnień lub odwołania jest ściśle określony w pouczeniu — jego przekroczenie może zamknąć drogę do obrony.</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Ze względu na krótki termin warto jak najszybciej przejść do Audytu 48h, aby ustalić termin, zakres żądania i właściwy tryb odpowiedzi na pismo organu.</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S176" t="n">
+        <v>1</v>
+      </c>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr"/>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>BASE_176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, 4-7</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_4_7</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — szybka weryfikacja i odpowiedź.</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga przygotowanej odpowiedzi. Właściwą formą jest złożenie wyjaśnień i dokumentów — nie sprzeciw ani pismo do sądu. Czas na reakcję jest ograniczony.</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma, termin i możliwe kierunki odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr"/>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>BASE_177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, 4-7</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_4_7</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — weryfikacja terminu i zakresu.</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego wymaga weryfikacji i przygotowania właściwej odpowiedzi. Masz jeszcze czas, ale warto bez zwłoki potwierdzić termin określony w pouczeniu i ustalić zakres żądania organu.</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Audyt 48h może pomóc ocenić treść pisma organu, termin i zakres odpowiedzialności — zanim zdecydujesz o formie odpowiedzi.</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S178" t="n">
+        <v>1</v>
+      </c>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr"/>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>BASE_178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, 8-14</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — szybka weryfikacja i odpowiedź.</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga przygotowanej odpowiedzi. Właściwą formą jest złożenie wyjaśnień i dokumentów — nie sprzeciw ani pismo do sądu. Czas na reakcję jest ograniczony.</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma, termin i możliwe kierunki odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S179" t="n">
+        <v>1</v>
+      </c>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr"/>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>BASE_179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, 8-14</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — weryfikacja terminu i zakresu.</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego wymaga weryfikacji i przygotowania właściwej odpowiedzi. Masz jeszcze czas, ale warto bez zwłoki potwierdzić termin określony w pouczeniu i ustalić zakres żądania organu.</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Audyt 48h może pomóc ocenić treść pisma organu, termin i zakres odpowiedzialności — zanim zdecydujesz o formie odpowiedzi.</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S180" t="n">
+        <v>1</v>
+      </c>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr"/>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>BASE_180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko / prewencja — pismo organu publicznego ZUS/US, 8-14</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko / prewencja</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — niższe ryzyko, warto potwierdzić termin.</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej sprawy wskazuje na niższe ryzyko. Właściwa reakcja — wyjaśnienia lub odwołanie — wymaga jednak potwierdzenia terminu, adresata i zakresu żądania.</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Audyt 48h może pomóc ocenić treść pisma organu, termin i zakres odpowiedzialności — zanim zdecydujesz o formie odpowiedzi.</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S181" t="n">
+        <v>1</v>
+      </c>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr"/>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>BASE_181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, above-14</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — szybka weryfikacja i odpowiedź.</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga przygotowanej odpowiedzi. Właściwą formą jest złożenie wyjaśnień i dokumentów — nie sprzeciw ani pismo do sądu. Czas na reakcję jest ograniczony.</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma, termin i możliwe kierunki odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S182" t="n">
+        <v>1</v>
+      </c>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr"/>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>BASE_182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, above-14</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — weryfikacja terminu i zakresu.</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego wymaga weryfikacji i przygotowania właściwej odpowiedzi. Masz jeszcze czas, ale warto bez zwłoki potwierdzić termin określony w pouczeniu i ustalić zakres żądania organu.</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Audyt 48h może pomóc ocenić treść pisma organu, termin i zakres odpowiedzialności — zanim zdecydujesz o formie odpowiedzi.</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S183" t="n">
+        <v>1</v>
+      </c>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr"/>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>BASE_183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko / prewencja — pismo organu publicznego ZUS/US, above-14</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko / prewencja</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — niższe ryzyko, warto potwierdzić termin.</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej sprawy wskazuje na niższe ryzyko. Właściwa reakcja — wyjaśnienia lub odwołanie — wymaga jednak potwierdzenia terminu, adresata i zakresu żądania.</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Audyt 48h może pomóc ocenić treść pisma organu, termin i zakres odpowiedzialności — zanim zdecydujesz o formie odpowiedzi.</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S184" t="n">
+        <v>1</v>
+      </c>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr"/>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>BASE_184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, unknown</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — szybka weryfikacja i odpowiedź.</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga przygotowanej odpowiedzi. Właściwą formą jest złożenie wyjaśnień i dokumentów — nie sprzeciw ani pismo do sądu. Czas na reakcję jest ograniczony.</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma, termin i możliwe kierunki odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S185" t="n">
+        <v>1</v>
+      </c>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr"/>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>BASE_185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, unknown</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu — weryfikacja terminu i zakresu.</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego wymaga weryfikacji i przygotowania właściwej odpowiedzi. Masz jeszcze czas, ale warto bez zwłoki potwierdzić termin określony w pouczeniu i ustalić zakres żądania organu.</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Audyt 48h może pomóc ocenić treść pisma organu, termin i zakres odpowiedzialności — zanim zdecydujesz o formie odpowiedzi.</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S186" t="n">
+        <v>1</v>
+      </c>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr"/>
+      <c r="W186" t="inlineStr">
         <is>
           <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
         </is>

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -1518,7 +1518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W188"/>
+  <dimension ref="A1:W189"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="8.25" customWidth="1" style="4" min="1" max="1"/>
@@ -21414,6 +21414,106 @@
         </is>
       </c>
       <c r="W188" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>BASE_188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Sprawa pilna – pismo organu publicznego ZUS/US, nieznany termin</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu – wysoki ciężar dokumentu, termin nieznany.</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki należy do dokumentów o wysokim ciężarze prawnym. Brak znajomości terminu odpowiedzi dodatkowo zwiększa ryzyko — organ wyznacza termin w pouczeniu, którego przekroczenie może zamknąć drogę do obrony.</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>W pierwszej kolejności ustal termin odpowiedzi wskazany w pouczeniu pisma — Audyt 48h pozwoli ocenić treść dokumentu, termin i właściwy tryb odpowiedzi.</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S189" t="n">
+        <v>1</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>ZATWIERDZONA</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
         <is>
           <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
         </is>

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -4367,7 +4367,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Sprawa wymaga pilnej weryfikacji. Czas na reakcję i dane z formularza wskazują na podwyższoną pilność — jednak bez ustalenia rodzaju pisma nie można określić właściwego kierunku działania.</t>
+          <t>Sprawa oceniana jest jako pilna ze względu na wysoką niepewność — nie wiadomo jakiego rodzaju jest pismo, a termin na reakcję nie jest znany. Brak kluczowych informacji sam w sobie stanowi ryzyko wymagające szybkiego wyjaśnienia.</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
+          <t>Warto bez zbędnej zwłoki ustalić rodzaj dokumentu i termin reakcji — Audyt 48h umożliwia weryfikację treści pisma, terminów i możliwych kierunków działania.</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -19,31 +19,31 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_Instrukcja_działania_AI" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_Kontrola_spojnosci_kodow" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_Instrukcja_dla_AI" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Testy_kontrolne" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Zgodnosc_instrukcji_z_kodem" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Model_hybrydowy" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Uzupelnienie_scenariuszy" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Kontrola_jakosci" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6A_Moduly_K3_K6" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6C_Zasady_uzycia" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6D_Reguly_tekstu_terminu" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6E_Reguly_pilnosci_czlonka_zarz" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6F_Reguly_KRS_next_step" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6G_Reguly_dni_kalendarzowych" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6H_Reguly_EPU_sprzeciw" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6I_Podpowiedz_EPU_dla_klien" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6K_Reguly_EPU_pozew" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6L_Checklista_regresji_v26" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6M_Reguly_CZ_wszystkie_dok" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6N_Reguly_zgodnosci_EPU_dok" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6O_Reguly_dokumentow_spolki" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6P_Nakaz_pozew_spolka_v31" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6Q_Reguly_kwoty_roszczenia" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6R_Kwota_kontekst_v33" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6S_Dokument_nieustalony_v34" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6T_Checklista_regresji_v34" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6U_ZUS_urzad_v35" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6V_Checklista_regresji_v35" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Zgodnosc_instrukcji_z_kodem" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Model_hybrydowy" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Uzupelnienie_scenariuszy" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Kontrola_jakosci" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6A_Moduly_K3_K6" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6C_Zasady_uzycia" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6D_Reguly_tekstu_terminu" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6E_Reguly_pilnosci_czlonka_zarz" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6F_Reguly_KRS_next_step" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6G_Reguly_dni_kalendarzowych" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6H_Reguly_EPU_sprzeciw" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6I_Podpowiedz_EPU_dla_klien" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6K_Reguly_EPU_pozew" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6L_Checklista_regresji_v26" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6M_Reguly_CZ_wszystkie_dok" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6N_Reguly_zgodnosci_EPU_dok" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6O_Reguly_dokumentow_spolki" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6P_Nakaz_pozew_spolka_v31" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6Q_Reguly_kwoty_roszczenia" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6R_Kwota_kontekst_v33" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6S_Dokument_nieustalony_v34" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6T_Checklista_regresji_v34" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6U_ZUS_urzad_v35" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6V_Checklista_regresji_v35" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Testy_kontrolne" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -24157,1059 +24157,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.25" customWidth="1" style="4" min="1" max="1"/>
-    <col width="19.375" customWidth="1" style="4" min="2" max="2"/>
-    <col width="31.625" customWidth="1" style="4" min="3" max="3"/>
-    <col width="29.5" customWidth="1" style="4" min="4" max="4"/>
-    <col width="26.875" customWidth="1" style="4" min="5" max="5"/>
-    <col width="31.625" customWidth="1" style="4" min="6" max="6"/>
-    <col width="27.125" customWidth="1" style="4" min="7" max="7"/>
-    <col width="10" customWidth="1" style="4" min="8" max="8"/>
-    <col width="19.875" customWidth="1" style="4" min="9" max="9"/>
-    <col width="9" customWidth="1" style="4" min="10" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="21.95000076293945" customFormat="1" customHeight="1" s="8">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Testy kontrolne — po uporządkowaniu biblioteki scenariuszy</t>
-        </is>
-      </c>
-      <c r="B1" s="67" t="n"/>
-      <c r="C1" s="67" t="n"/>
-      <c r="D1" s="67" t="n"/>
-      <c r="E1" s="67" t="n"/>
-      <c r="F1" s="67" t="n"/>
-      <c r="G1" s="67" t="n"/>
-      <c r="H1" s="67" t="n"/>
-      <c r="I1" s="68" t="n"/>
-    </row>
-    <row r="2" ht="27.75" customFormat="1" customHeight="1" s="8">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>test_id</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>obszar</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>dane testowe</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>oczekiwany scenariusz bazowy / zachowanie techniczne</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>oczekiwane moduły K3–K6</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>oczekiwany wynik użytkownika</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>czego NIE wolno pokazać użytkownikowi</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>uwagi</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>T01</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Wiele dokumentów</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Pozew przeciwko spółce + pozew przeciwko członkowi zarządu</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Dokument główny: pozew przeciwko członkowi zarządu</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Zależnie od formularza</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Wynik mówi, który dokument wymaga reakcji i jakie dokumenty są pomocnicze</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Nazwy reguł wyboru dokumentu</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>T02</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Wiele dokumentów</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Nakaz przeciwko spółce + nakaz przeciwko członkowi zarządu</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Dokument główny: nakaz przeciwko członkowi zarządu</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Zależnie od formularza</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Wynik wskazuje nakaz jako dokument wymagający reakcji</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Punktacja wyboru dokumentu</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>T03</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>EPU</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Nakaz EPU + pouczenie + potwierdzenie doręczenia</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Typ EPU zgodny z adresatem; dołącz Blok_EPU</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Zależnie od formularza</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Wynik wyjaśnia, że sprawa pochodzi z EPU/e-Sądu</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>EPU jako kod techniczny bez wyjaśnienia</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>T04</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Termin konkretny</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Data doręczenia + termin z pouczenia dają 5 dni</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>K2 technicznie może być 4–7 dni</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Dowolne</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Wynik mówi konkretnie, że zostało ok. 5 dni</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Ogólnik „około 4–7 dni”, gdy znane jest 5 dni</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>T05</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Twarde reguły</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Krótki termin albo termin niepewny</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Poziom ryzyka może zostać podniesiony</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Dowolne</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Użytkownik widzi nietechniczne ostrzeżenie o konieczności potwierdzenia terminu</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>HR01, HR02, HR04 itp.</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>T06</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Brak dokumentów</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Użytkownik chce tylko wstępną ocenę bez dokumentów</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>K3_SUPPORT_BASIC_NO_DOCS</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Wynik jasno mówi, że ocena jest ograniczona bez dokumentów</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Kod K3</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>T07</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Dokumenty później</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Użytkownik chce ocenę teraz i dosłanie dokumentów później</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>K3_SUPPORT_NOW_DOCS_LATER</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Wynik wskazuje, jakie dokumenty trzeba później uzupełnić</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Kod K3</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>T08</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Gotowość do audytu</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Użytkownik gotowy wysłać dokumenty</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>K3_READY_FOR_AUDIT_48H</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Wynik kieruje do listy dokumentów do Audytu 48h</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Kod K3</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>T09</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Status zarządu aktywny</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>K4 = nadal pełnię funkcję</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy nie musi mieć K4</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>MOD_K4_BOARD_ACTIVE</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Wynik mówi o potrzebie sprawdzenia aktualnego statusu i adresata pisma</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>BOARD_ACTIVE</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>T10</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Status zarządu rezygnacja</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>K4 = rezygnacja/odwołanie</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy nie może nadpisać tego statusem aktywnym</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>MOD_K4_BOARD_RESIGNED + właściwy K5</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Wynik mówi o rezygnacji/odwołaniu i dacie skuteczności</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Informacja, że użytkownik nadal pełni funkcję</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>To test problemu ze SCN_002.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>T11</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>KRS nieznany</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>K4=rezygnacja, K5=nie wiem</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>MOD_K4_BOARD_RESIGNED + MOD_K5_KRS_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Wynik zaleca sprawdzenie dokumentu rezygnacji/odwołania i aktualnego odpisu KRS</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>K5_KRS_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Cel: zyskać czas</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>K6 = zyskać czas na przygotowanie obrony</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>MOD_K6_GOAL_BUY_TIME</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Wynik mówi o legalnych środkach procesowych i przygotowaniu obrony, a nie o terminie na reakcję</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Sugestia nadużycia prawa lub działań instrumentalnych</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Rozróżnić od realnej oceny obrony.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>T13</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Cel: ocena podstaw obrony</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>K6 = ocenić realne podstawy obrony</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>MOD_K6_GOAL_DEFENSE</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Wynik koncentruje się na dokumentach, podstawie roszczenia, terminach i możliwych zarzutach</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Kod K6</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>T14</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Cel: pismo procesowe</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>K6 = przygotować odpowiednie pismo procesowe</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>MOD_K6_GOAL_PROCEDURAL_LETTER</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Wynik wskazuje, że rodzaj pisma zależy od dokumentu: sprzeciw przy nakazie, odpowiedź przy pozwie</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Kod K6</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Nowa opcja K6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>T15</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Cel: plan + ocena szans</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>K6 = plan działania i ocena szans</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>MOD_K6_GOAL_PLAN</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Wynik wskazuje potrzebę uporządkowania planu działania i oceny szans</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Kod K6</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>T16</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Cel niepewny</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>K6 = nie wiem / uporządkowanie sytuacji</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>MOD_K6_GOAL_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Wynik pomaga uporządkować możliwe kierunki działania</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Kod K6</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>T31</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Model bazowy + moduły</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Nakaz przeciwko członkowi zarządu, 8–14 dni</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy dla nakazu i terminu</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Z formularza</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Wynik podkreśla znaczenie terminu i treści pouczenia</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>SCN_xxx w wyniku użytkownika</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>T32</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>EPU pilny</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Nakaz EPU przeciwko członkowi zarządu, 0–3 dni</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy EPU + RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Z formularza</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Wynik pilny + blok EPU + ostrzeżenie o terminie</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>HRxx, RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>T33</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Pozew spółka EPU</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Pozew EPU przeciwko spółce</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Typ EPU_POZEW_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Z formularza</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Wynik nie myli pozwu z nakazem i nie myli spółki z członkiem zarządu</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>wewnętrzny typ EPU</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>T34</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Dokument nieustalony</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Niejasny dokument, termin nieznany</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy dokument nieustalony albo fallback</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Z formularza</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Wynik ostrożny, wskazuje potrzebę identyfikacji dokumentu i terminu</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>komunikaty techniczne fallback</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>T35</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>SCN_002 problem</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Nakaz przeciwko członkowi zarządu, 4–7 dni, K4=rezygnacja, K5=nie wiem, K6=kupić czas</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Może wybrać bazę odpowiadającą K1/K2/ryzyku, ale wynik musi wynikać z modułów K4–K6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>K4 rezygnacja + K5 nie wiem + K6 kupić czas</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Wynik NIE zawiera informacji, że użytkownik nadal pełni funkcję</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>BOARD_ACTIVE; 'nadal pełni funkcję' przy K4=resigned</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>Test ze zrzutu użytkownika.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>T36</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Prywatność i technika</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Dowolny przypadek</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Panel testowy może pokazać technikę</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Dowolne</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Wynik użytkownika bez techniki</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>risk_level_code, HRxx, K3/K4/K5/K6 codes, moduły, dynamicznie</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -26234,7 +25181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26643,6 +25590,2153 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G96"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.375" customWidth="1" style="4" min="1" max="1"/>
+    <col width="20.25" customWidth="1" style="4" min="2" max="2"/>
+    <col width="17.625" customWidth="1" style="4" min="3" max="3"/>
+    <col width="22.875" customWidth="1" style="4" min="4" max="4"/>
+    <col width="21.375" customWidth="1" style="4" min="5" max="5"/>
+    <col width="13.5" customWidth="1" style="4" min="6" max="6"/>
+    <col width="37.125" customWidth="1" style="4" min="7" max="7"/>
+    <col width="9" customWidth="1" style="4" min="8" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21.95000076293945" customHeight="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>Raport przebudowy biblioteki scenariuszy (uzupełnienie scenariuszy</t>
+        </is>
+      </c>
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="68" t="n"/>
+    </row>
+    <row r="2" ht="21.95000076293945" customFormat="1" customHeight="1" s="8">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>obszar</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>stan przed zmianą</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>zmiana</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>stan po zmianie</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>uwagi</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Zakładka 6_Biblioteka_scenariuszy</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>366 scenariuszy pełnych/kombinowanych; K3–K6 w tej samej tabeli</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Przebudowano jako bibliotekę scenariuszy bazowych</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>172 scenariusze bazowe</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy nie udaje pełnego opisu sprawy.</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>K3–K6</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Kolumny w bibliotece scenariuszy, powodowały mylące dopasowania</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Przeniesiono do modułów tekstowych</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Nowy arkusz 6A_Moduly_K3_K6</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Odpowiedzi użytkownika są dokładane jako osobne fragmenty.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Stara biblioteka</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Ryzyko utraty danych historycznych</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Zachowano jako archiwum</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>6Z_Archiwum_stara_biblioteka</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Nic nie zostało trwale usunięte.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Opis kolumn</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Niejasne przeznaczenie wielu pól</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Dodano mapę decyzji dla kolumn</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>6B_Porzadek_kolumn</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Pokazuje: zostawiono, przeniesiono, scalono, archiwizowano.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Zasady użycia</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Brak jasnego opisu nowej logiki</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Dodano instrukcję działania bazy i modułów</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>6C_Zasady_uzycia</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Dla testera i osoby rozwijającej kod.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Zakładka 7</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Częściowo opisywała stary model / stare wersje app_professional</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Zaktualizowano instrukcję kroków</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Spójna z bazą + modułami</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Zakładka 9</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Wymagała doprecyzowania zakazu sprzeczności i zakazu techniki w wyniku</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Zaktualizowano instrukcję dla AI</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Spójna z v14 i 6A</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Zakładka 10</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Testy wymagały nowych przypadków jakościowych</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Przebudowano testy kontrolne</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Dodano testy kluczowe dla modułów i SCN_002</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>risk_level_code</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Zakładka 11</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Mapa zgodności odwoływała się do starszych numerów wersji</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Zaktualizowano statusy</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Dodano pozycję: moduły 6A do synchronizacji z kodem</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Zakładka 12</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Model hybrydowy był opisany, ale wymagał urealnienia po przebudowie arkusza 6</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Zaktualizowano opis modelu</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Jasne rozdzielenie pól blokujących i nieblokujących</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Zakładka 14</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Kontrola jakości wymagała nowego zakresu</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Zaktualizowano checklistę</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Dodano ryzyka i dalsze kroki</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: dokument nieustalony prawny, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Dalszy krok</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Kod v14 buduje spójny wynik, ale nowy Excel ma osobny arkusz 6A</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Dostosować app.py do bezpośredniego czytania 6A_Moduly_K3_K6</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Wersja aplikacji v15</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>To najważniejszy kolejny krok techniczny.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko — scenariusz bazowy: dokument nieustalony prawny, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: dokument nieustalony prawny, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: dokument nieustalony prawny, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko — scenariusz bazowy: dokument nieustalony prawny, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: dokument nieustalony prawny, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: dokument nieustalony prawny, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: dokument nieustalony prawny, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: dokument nieustalony prawny, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: dokument nieustalony prawny, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko członkowi zarządu, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko członkowi zarządu, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko członkowi zarządu, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko członkowi zarządu, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko spółce, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko spółce, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko członkowi zarządu, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko członkowi zarządu, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko członkowi zarządu, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko członkowi zarządu, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko spółce, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko spółce, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko — scenariusz bazowy: pozew przeciwko spółce, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko spółce, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko spółce, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko — scenariusz bazowy: pozew przeciwko spółce, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: pozew przeciwko spółce, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko spółce, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko spółce, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="5" t="n"/>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: pozew przeciwko spółce, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko spółce, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="45" customHeight="1">
+      <c r="A69" s="5" t="n"/>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="45" customHeight="1">
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="45" customHeight="1">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="45" customHeight="1">
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="45" customHeight="1">
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="45" customHeight="1">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="45" customHeight="1">
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="45" customHeight="1">
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="45" customHeight="1">
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="45" customHeight="1">
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="45" customHeight="1">
+      <c r="A80" s="5" t="n"/>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="45" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>SCN_313</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_0_3</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>SCN_314</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_0_3</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="45" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>SCN_315</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_4_7</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="45" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>SCN_316</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_4_7</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>SCN_317</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_4_7</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="45" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>SCN_318</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>SCN_319</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="45" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>SCN_320</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>SCN_321</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="45" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>SCN_322</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="45" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>SCN_323</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="45" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>SCN_324</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="45" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>SCN_325</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="45" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>SCN_326</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="45" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>SCN_327</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="45" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>SCN_328</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -27924,2153 +29018,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col width="11.375" customWidth="1" style="4" min="1" max="1"/>
-    <col width="20.25" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17.625" customWidth="1" style="4" min="3" max="3"/>
-    <col width="22.875" customWidth="1" style="4" min="4" max="4"/>
-    <col width="21.375" customWidth="1" style="4" min="5" max="5"/>
-    <col width="13.5" customWidth="1" style="4" min="6" max="6"/>
-    <col width="37.125" customWidth="1" style="4" min="7" max="7"/>
-    <col width="9" customWidth="1" style="4" min="8" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="21.95000076293945" customHeight="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t>Raport przebudowy biblioteki scenariuszy (uzupełnienie scenariuszy</t>
-        </is>
-      </c>
-      <c r="B1" s="67" t="n"/>
-      <c r="C1" s="67" t="n"/>
-      <c r="D1" s="67" t="n"/>
-      <c r="E1" s="67" t="n"/>
-      <c r="F1" s="67" t="n"/>
-      <c r="G1" s="68" t="n"/>
-    </row>
-    <row r="2" ht="21.95000076293945" customFormat="1" customHeight="1" s="8">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>obszar</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>stan przed zmianą</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>zmiana</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>stan po zmianie</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>uwagi</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Zakładka 6_Biblioteka_scenariuszy</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>366 scenariuszy pełnych/kombinowanych; K3–K6 w tej samej tabeli</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Przebudowano jako bibliotekę scenariuszy bazowych</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>172 scenariusze bazowe</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy nie udaje pełnego opisu sprawy.</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>K3–K6</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Kolumny w bibliotece scenariuszy, powodowały mylące dopasowania</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Przeniesiono do modułów tekstowych</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Nowy arkusz 6A_Moduly_K3_K6</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Odpowiedzi użytkownika są dokładane jako osobne fragmenty.</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Stara biblioteka</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Ryzyko utraty danych historycznych</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Zachowano jako archiwum</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>6Z_Archiwum_stara_biblioteka</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Nic nie zostało trwale usunięte.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Opis kolumn</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Niejasne przeznaczenie wielu pól</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Dodano mapę decyzji dla kolumn</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>6B_Porzadek_kolumn</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Pokazuje: zostawiono, przeniesiono, scalono, archiwizowano.</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Zasady użycia</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Brak jasnego opisu nowej logiki</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Dodano instrukcję działania bazy i modułów</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>6C_Zasady_uzycia</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Dla testera i osoby rozwijającej kod.</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Zakładka 7</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Częściowo opisywała stary model / stare wersje app_professional</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Zaktualizowano instrukcję kroków</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Spójna z bazą + modułami</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Zakładka 9</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Wymagała doprecyzowania zakazu sprzeczności i zakazu techniki w wyniku</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Zaktualizowano instrukcję dla AI</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Spójna z v14 i 6A</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Zakładka 10</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Testy wymagały nowych przypadków jakościowych</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Przebudowano testy kontrolne</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Dodano testy kluczowe dla modułów i SCN_002</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>risk_level_code</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Zakładka 11</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Mapa zgodności odwoływała się do starszych numerów wersji</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Zaktualizowano statusy</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Dodano pozycję: moduły 6A do synchronizacji z kodem</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Zakładka 12</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Model hybrydowy był opisany, ale wymagał urealnienia po przebudowie arkusza 6</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Zaktualizowano opis modelu</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Jasne rozdzielenie pól blokujących i nieblokujących</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Zakładka 14</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Kontrola jakości wymagała nowego zakresu</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Zaktualizowano checklistę</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Dodano ryzyka i dalsze kroki</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: dokument nieustalony prawny, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Dalszy krok</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Kod v14 buduje spójny wynik, ale nowy Excel ma osobny arkusz 6A</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Dostosować app.py do bezpośredniego czytania 6A_Moduly_K3_K6</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Wersja aplikacji v15</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>To najważniejszy kolejny krok techniczny.</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>RISK_LOW</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Niższe ryzyko — scenariusz bazowy: dokument nieustalony prawny, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: dokument nieustalony prawny, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: dokument nieustalony prawny, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: dokument nieustalony prawny, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>RISK_LOW</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Niższe ryzyko — scenariusz bazowy: dokument nieustalony prawny, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: dokument nieustalony prawny, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: dokument nieustalony prawny, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: dokument nieustalony prawny, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: dokument nieustalony prawny, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: dokument nieustalony prawny, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko członkowi zarządu, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko członkowi zarządu, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko członkowi zarządu, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko członkowi zarządu, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="5" t="n"/>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko spółce, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1">
-      <c r="A39" s="5" t="n"/>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="45" customHeight="1">
-      <c r="A40" s="5" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>RISK_LOW</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Niższe ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="45" customHeight="1">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
-      <c r="A42" s="5" t="n"/>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko spółce, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="45" customHeight="1">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1">
-      <c r="A44" s="5" t="n"/>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: nakaz zapłaty przeciwko spółce, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customHeight="1">
-      <c r="A45" s="5" t="n"/>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: nakaz zapłaty przeciwko spółce, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="45" customHeight="1">
-      <c r="A46" s="5" t="n"/>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko członkowi zarządu, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="45" customHeight="1">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko członkowi zarządu, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="45" customHeight="1">
-      <c r="A48" s="5" t="n"/>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko członkowi zarządu, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="45" customHeight="1">
-      <c r="A49" s="5" t="n"/>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko członkowi zarządu, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="5" t="n"/>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="5" t="n"/>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="5" t="n"/>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko spółce, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="5" t="n"/>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="5" t="n"/>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="5" t="n"/>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko spółce, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="5" t="n"/>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="5" t="n"/>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="5" t="n"/>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>RISK_LOW</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>Niższe ryzyko — scenariusz bazowy: pozew przeciwko spółce, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="5" t="n"/>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="5" t="n"/>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: pozew przeciwko spółce, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="5" t="n"/>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko spółce, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="5" t="n"/>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko spółce, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="5" t="n"/>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>RISK_LOW</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>Niższe ryzyko — scenariusz bazowy: pozew przeciwko spółce, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="5" t="n"/>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: pozew przeciwko spółce, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="5" t="n"/>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="5" t="n"/>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko spółce, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="5" t="n"/>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: pozew przeciwko spółce, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="5" t="n"/>
-      <c r="B65" s="5" t="n"/>
-      <c r="C65" s="5" t="n"/>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: pozew przeciwko spółce, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="5" t="n"/>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: pozew przeciwko spółce, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="5" t="n"/>
-      <c r="B67" s="5" t="n"/>
-      <c r="C67" s="5" t="n"/>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="5" t="n"/>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="45" customHeight="1">
-      <c r="A69" s="5" t="n"/>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="5" t="n"/>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="45" customHeight="1">
-      <c r="A70" s="5" t="n"/>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="5" t="n"/>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="45" customHeight="1">
-      <c r="A72" s="5" t="n"/>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="5" t="n"/>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="45" customHeight="1">
-      <c r="A73" s="5" t="n"/>
-      <c r="B73" s="5" t="n"/>
-      <c r="C73" s="5" t="n"/>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="45" customHeight="1">
-      <c r="A74" s="5" t="n"/>
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="5" t="n"/>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>RISK_LOW</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="45" customHeight="1">
-      <c r="A75" s="5" t="n"/>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="45" customHeight="1">
-      <c r="A76" s="5" t="n"/>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="5" t="n"/>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="45" customHeight="1">
-      <c r="A77" s="5" t="n"/>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="45" customHeight="1">
-      <c r="A78" s="5" t="n"/>
-      <c r="B78" s="5" t="n"/>
-      <c r="C78" s="5" t="n"/>
-      <c r="D78" s="5" t="n"/>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="45" customHeight="1">
-      <c r="A79" s="5" t="n"/>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="5" t="n"/>
-      <c r="D79" s="5" t="n"/>
-      <c r="E79" s="5" t="n"/>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="45" customHeight="1">
-      <c r="A80" s="5" t="n"/>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="n"/>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="45" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>SCN_313</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_0_3</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>SCN_314</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_0_3</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="45" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>SCN_315</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_4_7</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="45" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>SCN_316</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_4_7</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>SCN_317</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_4_7</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="45" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>SCN_318</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_8_14</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>SCN_319</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_8_14</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>RISK_LOW</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="45" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>SCN_320</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_8_14</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>SCN_321</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_8_14</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="45" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>SCN_322</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="45" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>SCN_323</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>RISK_LOW</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="45" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>SCN_324</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="45" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>SCN_325</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="45" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>SCN_326</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>RISK_HIGH</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="45" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>SCN_327</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>RISK_MEDIUM</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="45" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>SCN_328</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -31483,7 +30430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32449,7 +31396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32684,7 +31631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33038,7 +31985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33360,7 +32307,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33582,7 +32529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33723,7 +32670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33913,7 +32860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34087,6 +33034,165 @@
       <c r="D8" s="64" t="inlineStr">
         <is>
           <t>Warunek do testów UX.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" style="4" min="1" max="1"/>
+    <col width="33.625" customWidth="1" style="4" min="2" max="2"/>
+    <col width="42" customWidth="1" style="4" min="3" max="4"/>
+    <col width="9" customWidth="1" style="4" min="5" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Reguły EPU - pozew</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21.95000076293945" customFormat="1" customHeight="1" s="8">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Zakres</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>Reguła v26</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>Tekst/przykład</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>Uwagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="75" customFormat="1" customHeight="1" s="60">
+      <c r="A3" s="61" t="inlineStr">
+        <is>
+          <t>EPU + nakaz zapłaty</t>
+        </is>
+      </c>
+      <c r="B3" s="61" t="inlineStr">
+        <is>
+          <t>Priorytet: terminowe przygotowanie i złożenie sprzeciwu od nakazu zapłaty w EPU</t>
+        </is>
+      </c>
+      <c r="C3" s="61" t="inlineStr">
+        <is>
+          <t>Najważniejsze jest terminowe przygotowanie i złożenie sprzeciwu od nakazu zapłaty w EPU. Sprzeciw w e-Sądzie ma uproszczony charakter; przy krótkim terminie kluczowe jest zachowanie terminu i prawidłowe oznaczenie nakazu.</t>
+        </is>
+      </c>
+      <c r="D3" s="61" t="inlineStr">
+        <is>
+          <t>KRS/rezygnacja są ważne dla dalszej strategii, ale nie są pierwszym priorytetem przy krótkim terminie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>EPU + pozew / sprawa oznaczona jako EPU</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Priorytet: ustalić właściwy tryb reakcji z pouczenia i przygotować pismo zgodnie z pouczeniem</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Najważniejsze jest szybkie ustalenie właściwego trybu reakcji w EPU / e-Sądzie oraz przygotowanie pisma zgodnie z pouczeniem.</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Nie używać automatycznie formuły: „odpowiedź na pozew w oparciu o faktyczną dokumentację”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>EPU + 0–7 dni</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Nie zaczynać akapitu końcowego od sprawdzania KRS</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Pierwszeństwo ma zachowanie terminu i prawidłowa reakcja na doręczone pismo. Dokumenty KRS/rezygnacja sprawdzić następnie albo równolegle.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Dotyczy nakazu i pozwu, spółki i członka zarządu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>EPU + 8–14 dni</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Można wskazać równoległe porządkowanie dokumentów</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Warto bez zwłoki ustalić właściwy tryb reakcji i przygotować pismo zgodnie z pouczeniem, równolegle porządkując dokumenty do dalszej obrony.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Język spokojniejszy niż 0–7 dni.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Nie-EPU + nakaz/pozew</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Pozostaje zasada dokumentacji faktycznej</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Przy sądzie tradycyjnym można pisać o sprzeciwie/odpowiedzi na pozew w oparciu o faktyczną dokumentację.</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Bez reguły uproszczonego EPU.</t>
         </is>
       </c>
     </row>
@@ -34203,165 +33309,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col width="27" customWidth="1" style="4" min="1" max="1"/>
-    <col width="33.625" customWidth="1" style="4" min="2" max="2"/>
-    <col width="42" customWidth="1" style="4" min="3" max="4"/>
-    <col width="9" customWidth="1" style="4" min="5" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>Reguły EPU - pozew</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="21.95000076293945" customFormat="1" customHeight="1" s="8">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Zakres</t>
-        </is>
-      </c>
-      <c r="B2" s="24" t="inlineStr">
-        <is>
-          <t>Reguła v26</t>
-        </is>
-      </c>
-      <c r="C2" s="24" t="inlineStr">
-        <is>
-          <t>Tekst/przykład</t>
-        </is>
-      </c>
-      <c r="D2" s="24" t="inlineStr">
-        <is>
-          <t>Uwagi</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="75" customFormat="1" customHeight="1" s="60">
-      <c r="A3" s="61" t="inlineStr">
-        <is>
-          <t>EPU + nakaz zapłaty</t>
-        </is>
-      </c>
-      <c r="B3" s="61" t="inlineStr">
-        <is>
-          <t>Priorytet: terminowe przygotowanie i złożenie sprzeciwu od nakazu zapłaty w EPU</t>
-        </is>
-      </c>
-      <c r="C3" s="61" t="inlineStr">
-        <is>
-          <t>Najważniejsze jest terminowe przygotowanie i złożenie sprzeciwu od nakazu zapłaty w EPU. Sprzeciw w e-Sądzie ma uproszczony charakter; przy krótkim terminie kluczowe jest zachowanie terminu i prawidłowe oznaczenie nakazu.</t>
-        </is>
-      </c>
-      <c r="D3" s="61" t="inlineStr">
-        <is>
-          <t>KRS/rezygnacja są ważne dla dalszej strategii, ale nie są pierwszym priorytetem przy krótkim terminie.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>EPU + pozew / sprawa oznaczona jako EPU</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Priorytet: ustalić właściwy tryb reakcji z pouczenia i przygotować pismo zgodnie z pouczeniem</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Najważniejsze jest szybkie ustalenie właściwego trybu reakcji w EPU / e-Sądzie oraz przygotowanie pisma zgodnie z pouczeniem.</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Nie używać automatycznie formuły: „odpowiedź na pozew w oparciu o faktyczną dokumentację”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>EPU + 0–7 dni</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Nie zaczynać akapitu końcowego od sprawdzania KRS</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Pierwszeństwo ma zachowanie terminu i prawidłowa reakcja na doręczone pismo. Dokumenty KRS/rezygnacja sprawdzić następnie albo równolegle.</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Dotyczy nakazu i pozwu, spółki i członka zarządu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>EPU + 8–14 dni</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Można wskazać równoległe porządkowanie dokumentów</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Warto bez zwłoki ustalić właściwy tryb reakcji i przygotować pismo zgodnie z pouczeniem, równolegle porządkując dokumenty do dalszej obrony.</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Język spokojniejszy niż 0–7 dni.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Nie-EPU + nakaz/pozew</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Pozostaje zasada dokumentacji faktycznej</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Przy sądzie tradycyjnym można pisać o sprzeciwie/odpowiedzi na pozew w oparciu o faktyczną dokumentację.</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Bez reguły uproszczonego EPU.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -34582,7 +33529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34807,7 +33754,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35209,7 +34156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35504,7 +34451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35726,7 +34673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36001,7 +34948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36222,7 +35169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36368,7 +35315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36530,6 +35477,300 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col width="17.5" customWidth="1" style="4" min="1" max="1"/>
+    <col width="20.875" customWidth="1" style="4" min="2" max="2"/>
+    <col width="38.375" customWidth="1" style="4" min="3" max="3"/>
+    <col width="30.125" customWidth="1" style="4" min="4" max="4"/>
+    <col width="27.5" customWidth="1" style="4" min="5" max="5"/>
+    <col width="8.625" customWidth="1" style="4" min="6" max="6"/>
+    <col width="9" customWidth="1" style="4" min="7" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21.95000076293945" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Reguły v35 — pisma z ZUS / urzędu dotyczące odpowiedzialności członka zarządu</t>
+        </is>
+      </c>
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="68" t="n"/>
+    </row>
+    <row r="2" ht="21.95000076293945" customFormat="1" customHeight="1" s="8">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>obszar</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>reguła</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>tekst / znaczenie</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>skutek w app.py</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>uwagi testowe</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>wersja</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Nowy typ dokumentu</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu dotyczące odpowiedzialności członka zarządu za zobowiązania spółki.</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Nowa opcja na liście dokumentów.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Testować na przykładach: ZUS, US, zawiadomienie, wezwanie, decyzja.</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>v35</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Charakter sprawy</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Nie jest pozwem ani nakazem zapłaty</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Nie generować tekstów o sprzeciwie od nakazu zapłaty ani odpowiedzi na pozew.</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>build_public_authority_next_step_sentence()</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Sprawdzić brak słów: sprzeciw od nakazu, odpowiedź na pozew.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>v35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Priorytet</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Wyjaśnienia i dowody</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Najpierw ustalić termin odpowiedzi, okres zaległości, okres pełnienia funkcji i dokumenty wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>public_authority_risk_explanation()</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>ZUS/US wymaga innego języka niż sąd cywilny.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>v35</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>EPU</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Niedozwolone</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Pisma ZUS/US nie są dokumentami z EPU / e-Sądu.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>epu_compatibility_status() zwraca NIE.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Checkbox EPU ma być wyłączony.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>v35</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Punktacja</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>C=3, H=1</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Wysoki ciężar gatunkowy z uwagi na możliwą osobistą odpowiedzialność członka zarządu oraz administracyjny/publicznoprawny charakter sprawy.</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>fallback_points() i Excel 5_Punktacja_formularza.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Termin i kwota nadal wpływają na wynik.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>v35</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Kwota</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>K7 używać kontekstowo</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Kwota oznacza kwotę zaległości/roszczenia; przy wysokiej kwocie akcentować osobistą odpowiedzialność majątkową, nie skutki dla spółki.</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>claim_amount_text()</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Regresja dla kwoty nieznanej, 150–500 tys. i &gt;500 tys.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>v35</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Audyt 48h</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Celem Audytu jest identyfikacja pisma, terminu, zakresu żądania organu i dokumentów potrzebnych do odpowiedzi.</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>build_client_audit_cta()</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Nie tworzyć instrukcji procesowej.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>v35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -36709,300 +35950,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col width="17.5" customWidth="1" style="4" min="1" max="1"/>
-    <col width="20.875" customWidth="1" style="4" min="2" max="2"/>
-    <col width="38.375" customWidth="1" style="4" min="3" max="3"/>
-    <col width="30.125" customWidth="1" style="4" min="4" max="4"/>
-    <col width="27.5" customWidth="1" style="4" min="5" max="5"/>
-    <col width="8.625" customWidth="1" style="4" min="6" max="6"/>
-    <col width="9" customWidth="1" style="4" min="7" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="21.95000076293945" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Reguły v35 — pisma z ZUS / urzędu dotyczące odpowiedzialności członka zarządu</t>
-        </is>
-      </c>
-      <c r="B1" s="67" t="n"/>
-      <c r="C1" s="67" t="n"/>
-      <c r="D1" s="67" t="n"/>
-      <c r="E1" s="67" t="n"/>
-      <c r="F1" s="68" t="n"/>
-    </row>
-    <row r="2" ht="21.95000076293945" customFormat="1" customHeight="1" s="8">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>obszar</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>reguła</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>tekst / znaczenie</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>skutek w app.py</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>uwagi testowe</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>wersja</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Nowy typ dokumentu</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Pismo z ZUS / urzędu dotyczące odpowiedzialności członka zarządu za zobowiązania spółki.</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Nowa opcja na liście dokumentów.</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Testować na przykładach: ZUS, US, zawiadomienie, wezwanie, decyzja.</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>v35</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Charakter sprawy</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Nie jest pozwem ani nakazem zapłaty</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Nie generować tekstów o sprzeciwie od nakazu zapłaty ani odpowiedzi na pozew.</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>build_public_authority_next_step_sentence()</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Sprawdzić brak słów: sprzeciw od nakazu, odpowiedź na pozew.</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>v35</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Priorytet</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Wyjaśnienia i dowody</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Najpierw ustalić termin odpowiedzi, okres zaległości, okres pełnienia funkcji i dokumenty wyłączające odpowiedzialność.</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>public_authority_risk_explanation()</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>ZUS/US wymaga innego języka niż sąd cywilny.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>v35</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>EPU</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Niedozwolone</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Pisma ZUS/US nie są dokumentami z EPU / e-Sądu.</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>epu_compatibility_status() zwraca NIE.</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Checkbox EPU ma być wyłączony.</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>v35</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Punktacja</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>C=3, H=1</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Wysoki ciężar gatunkowy z uwagi na możliwą osobistą odpowiedzialność członka zarządu oraz administracyjny/publicznoprawny charakter sprawy.</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>fallback_points() i Excel 5_Punktacja_formularza.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Termin i kwota nadal wpływają na wynik.</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>v35</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Kwota</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>K7 używać kontekstowo</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Kwota oznacza kwotę zaległości/roszczenia; przy wysokiej kwocie akcentować osobistą odpowiedzialność majątkową, nie skutki dla spółki.</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>claim_amount_text()</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Regresja dla kwoty nieznanej, 150–500 tys. i &gt;500 tys.</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>v35</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>CTA</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Audyt 48h</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Celem Audytu jest identyfikacja pisma, terminu, zakresu żądania organu i dokumentów potrzebnych do odpowiedzi.</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>build_client_audit_cta()</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Nie tworzyć instrukcji procesowej.</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>v35</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -37233,6 +36180,1362 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>test_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>obszar</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>dane testowe</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>oczekiwany scenariusz bazowy / zachowanie techniczne</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>oczekiwane moduły K3–K6</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>oczekiwany wynik użytkownika</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>czego NIE wolno pokazać użytkownikowi</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>uwagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Wiele dokumentów</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pozew przeciwko spółce + pozew przeciwko członkowi zarządu</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dokument główny: pozew przeciwko członkowi zarządu</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Zależnie od formularza</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Wynik mówi, który dokument wymaga reakcji i jakie dokumenty są pomocnicze</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Nazwy reguł wyboru dokumentu</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ODŁOŻONY – poza MVP</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Wielodokumentowość nie jest zaimplementowana w app.py (MVP). Odłożyć do kolejnego etapu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Wiele dokumentów</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nakaz przeciwko spółce + nakaz przeciwko członkowi zarządu</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Dokument główny: nakaz przeciwko członkowi zarządu</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Zależnie od formularza</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Wynik wskazuje nakaz jako dokument wymagający reakcji</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Punktacja wyboru dokumentu</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ODŁOŻONY – poza MVP</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Wielodokumentowość nie jest zaimplementowana w app.py (MVP). Odłożyć do kolejnego etapu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EPU</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Nakaz EPU + pouczenie + potwierdzenie doręczenia</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Typ EPU zgodny z adresatem; dołącz Blok_EPU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zależnie od formularza</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Wynik wyjaśnia, że sprawa pochodzi z EPU/e-Sądu</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>EPU jako kod techniczny bez wyjaśnienia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Termin konkretny</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Data doręczenia + termin z pouczenia dają 5 dni</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>K2 technicznie może być 4–7 dni</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dowolne</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Wynik mówi konkretnie, że zostało ok. 5 dni</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ogólnik „około 4–7 dni”, gdy znane jest 5 dni</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Twarde reguły</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Krótki termin albo termin niepewny</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Poziom ryzyka może zostać podniesiony</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Dowolne</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Użytkownik widzi nietechniczne ostrzeżenie o konieczności potwierdzenia terminu</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HR01, HR02, HR04 itp.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brak dokumentów</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Użytkownik chce tylko wstępną ocenę bez dokumentów</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>K3_SUPPORT_BASIC_NO_DOCS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Wynik jasno mówi, że ocena jest ograniczona bez dokumentów</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Kod K3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dokumenty później</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Użytkownik chce ocenę teraz i dosłanie dokumentów później</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>K3_SUPPORT_NOW_DOCS_LATER</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Wynik wskazuje, jakie dokumenty trzeba później uzupełnić</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Kod K3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gotowość do audytu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Użytkownik gotowy wysłać dokumenty</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>K3_READY_FOR_AUDIT_48H</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Wynik kieruje do listy dokumentów do Audytu 48h</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Kod K3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Status zarządu aktywny</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>K4 = nadal pełnię funkcję</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy nie musi mieć K4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MOD_K4_BOARD_ACTIVE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Wynik mówi o potrzebie sprawdzenia aktualnego statusu i adresata pisma</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BOARD_ACTIVE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Status zarządu rezygnacja</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>K4 = rezygnacja/odwołanie</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy nie może nadpisać tego statusem aktywnym</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MOD_K4_BOARD_RESIGNED + właściwy K5</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Wynik mówi o rezygnacji/odwołaniu i dacie skuteczności</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Informacja, że użytkownik nadal pełni funkcję</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>To test problemu ze SCN_002.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KRS nieznany</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>K4=rezygnacja, K5=nie wiem</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MOD_K4_BOARD_RESIGNED + MOD_K5_KRS_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Wynik zaleca sprawdzenie dokumentu rezygnacji/odwołania i aktualnego odpisu KRS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>K5_KRS_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cel: zyskać czas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>K6 = zyskać czas na przygotowanie obrony</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MOD_K6_GOAL_BUY_TIME</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Wynik mówi o legalnych środkach procesowych i przygotowaniu obrony, a nie o terminie na reakcję</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sugestia nadużycia prawa lub działań instrumentalnych</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Rozróżnić od realnej oceny obrony.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cel: ocena podstaw obrony</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>K6 = ocenić realne podstawy obrony</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MOD_K6_GOAL_DEFENSE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Wynik koncentruje się na dokumentach, podstawie roszczenia, terminach i możliwych zarzutach</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Kod K6</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cel: pismo procesowe</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>K6 = przygotować odpowiednie pismo procesowe</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MOD_K6_GOAL_PROCEDURAL_LETTER</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Wynik wskazuje, że rodzaj pisma zależy od dokumentu: sprzeciw przy nakazie, odpowiedź przy pozwie</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Kod K6</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nowa opcja K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cel: plan + ocena szans</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>K6 = plan działania i ocena szans</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MOD_K6_GOAL_PLAN</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Wynik wskazuje potrzebę uporządkowania planu działania i oceny szans</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Kod K6</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cel niepewny</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>K6 = nie wiem / uporządkowanie sytuacji</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MOD_K6_GOAL_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Wynik pomaga uporządkować możliwe kierunki działania</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Kod K6</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Model bazowy + moduły</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nakaz przeciwko członkowi zarządu, 8–14 dni</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy dla nakazu i terminu</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Z formularza</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Wynik podkreśla znaczenie terminu i treści pouczenia</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SCN_xxx w wyniku użytkownika</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T32</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EPU pilny</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Nakaz EPU przeciwko członkowi zarządu, 0–3 dni</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy EPU + RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Z formularza</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Wynik pilny + blok EPU + ostrzeżenie o terminie</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HRxx, RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T33</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pozew spółka — brak EPU</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>K1=K1_POZEW_SPOLKA — sprawdzić, że checkbox EPU jest wyłączony (szary) i epu=False</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Typ POZEW_SPOLKA (nie EPU_POZEW_SPOLKA) — EPU_COMPATIBLE[K1_POZEW_SPOLKA]=NIE wymusza epu=False</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Z formularza</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Wynik standardowy dla POZEW_SPOLKA; nie myli pozwu z nakazem i spółki z członkiem zarządu</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>EPU_POZEW_SPOLKA jako typ; blok EPU w wyniku; wewnętrzny typ EPU</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EPU jest niedostępne dla K1_POZEW_SPOLKA — checkbox jest wyłączony przez UI. Scenariusze EPU_POZEW_SPOLKA celowo nieosiągalne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T34</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dokument nieustalony</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Niejasny dokument, termin nieznany</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Scenariusz bazowy dokument nieustalony albo fallback</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Z formularza</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Wynik ostrożny, wskazuje potrzebę identyfikacji dokumentu i terminu</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>komunikaty techniczne fallback</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T35</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SCN_002 problem</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>K1=K1_NAKAZ_CZLONEK_ZARZADU, K2=K2_DAYS_LEFT_4_7, K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_RESIGNED, K5=K5_KRS_UNKNOWN, K6=K6_GOAL_BUY_TIME, K7=K7_AMOUNT_10K_50K, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Może wybrać bazę odpowiadającą K1/K2/ryzyku, ale wynik musi wynikać z modułów K4–K6</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>K4 rezygnacja + K5 nie wiem + K6 kupić czas</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Wynik NIE zawiera informacji, że użytkownik nadal pełni funkcję</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>BOARD_ACTIVE; 'nadal pełni funkcję' przy K4=resigned</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Test ze zrzutu użytkownika.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T36</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Prywatność i technika</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Dowolny przypadek</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Panel testowy może pokazać technikę</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Dowolne</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Wynik użytkownika bez techniki</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>risk_level_code, HRxx, K3/K4/K5/K6 codes, moduły, dynamicznie</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T37</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pismo ZUS / urząd — krótki termin</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>K1=K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU, K2=K2_DAYS_LEFT_0_3, K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_ACTIVE, K5=K5_NOT_APPLICABLE, K6=K6_GOAL_DEFENSE, K7=K7_AMOUNT_10K_50K, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BASE_173 (RISK_URGENT)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>K3, K4_BOARD_ACTIVE, zus_note (nie urgency_note)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lead: "Na pismo z ZUS lub urzędu skarbowego masz X dni"; treść mówi o piśmie ZUS; CTA o wyjaśnieniach — nie sprzeciwie</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>"bez ustalenia rodzaju pisma"; "sprzeciw"; "odpowiedź na pozew"; kody techniczne</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T38</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pismo ZUS — 14 dni, RISK_URGENT przez ciężar dokumentu</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>K1=K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU, K2=K2_DAYS_LEFT_8_14 (use_dates=TAK, znana data), K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_ACTIVE, K5=K5_NOT_APPLICABLE, K6=K6_GOAL_DEFENSE, K7=K7_AMOUNT_10K_50K, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BASE_186 (RISK_URGENT — C=3+P=1+H=3+W=1=8)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>K3, K4_BOARD_ACTIVE, zus_note</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>"wysoki ciężar prawny — niezależnie od długości terminu"; wynik NIE mówi że czas wskazuje na pilność</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>"bez ustalenia rodzaju pisma"; "czas na reakcję wskazuje na podwyższoną pilność"; "sprzeciw"</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Weryfikuje poprawność BASE_186 — główny błąd zgłoszony przez użytkownika.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T39</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pismo ZUS — nieznany termin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>K1=K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU, K2=K2_DAYS_LEFT_UNKNOWN, K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_ACTIVE, K5=K5_NOT_APPLICABLE, K6=K6_GOAL_DEFENSE, K7=K7_AMOUNT_10K_50K, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BASE_188 (RISK_URGENT) lub BASE_184 (RISK_HIGH) — zależnie od S z K2A</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>K3, K4_BOARD_ACTIVE, zus_note</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mówi o piśmie ZUS; zaleca potwierdzenie terminu z pouczenia; NIE zawiera "bez ustalenia rodzaju pisma"</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>"bez ustalenia rodzaju pisma"; "sprzeciw"; kody techniczne</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T40</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Inne/nie wiem + wiele opcji "nie wiem" — RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>K1=K1_INNE_NIE_WIEM, K2=K2_DAYS_LEFT_UNKNOWN, K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_UNKNOWN, K5=K5_KRS_UNKNOWN, K6=K6_GOAL_UNKNOWN, K7=K7_AMOUNT_UNKNOWN, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BASE_026 (K2_UNKNOWN + RISK_URGENT)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>K3, K4_BOARD_UNKNOWN, K5_KRS_UNKNOWN, K6_GOAL_UNKNOWN, unknown_doc_note</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>"pilna ze względu na wysoką niepewność"; wynik NIE mówi że czas wskazuje na pilność</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>"Czas na reakcję wskazuje na podwyższoną pilność"; kody techniczne</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Weryfikuje poprawność BASE_026 po naprawie tekstu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T41</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pismo ZUS — cel: pismo procesowe</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>K1=K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU, K2=K2_DAYS_LEFT_8_14, K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_ACTIVE, K5=K5_NOT_APPLICABLE, K6=K6_GOAL_PROCEDURAL_LETTER, K7=K7_AMOUNT_10K_50K, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BASE_186 lub BASE_178</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>K6_GOAL_PROCEDURAL_LETTER (wyjaśnienia, nie sprzeciw)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>K6 text: "wyjaśnienia i dokumenty potwierdzające stanowisko — nie sprzeciw ani odpowiedź na pozew"</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>"sprzeciw"; "odpowiedź na pozew"; kody techniczne</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Kluczowa reguła komunikacyjna dla ZUS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T42</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Punktacja K2A — ręczny wybór K2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>K1=K1_INNE_NIE_WIEM, K2=K2_DAYS_LEFT_UNKNOWN (bez zaznaczenia checkboxa daty), K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_ACTIVE, K5=K5_NOT_APPLICABLE, K6=K6_GOAL_DEFENSE, K7=K7_AMOUNT_10K_50K</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Panel testowy: answers zawiera K2A=K2A_DELIVERY_DATE_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Brak widocznego modułu K2A w wyniku</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Panel testowy pokazuje H wyższe o 1 niż bez K2A; klient nie widzi K2A w tekście wyniku</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>K2A_DELIVERY_DATE_UNKNOWN jako widoczny tekst; kody techniczne</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Weryfikacja przez panel testowy — klient widzi tylko wynik S i poziom ryzyka.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T43</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Walidacja formularza</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kalkulator po starcie lub po wyczyszczeniu — kliknij "Oblicz ryzyko →" bez zaznaczenia żadnych opcji</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Brak obliczeń — walidacja blokuje wykonanie</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Brak</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pojawia się ostrzeżenie z listą brakujących kroków (np. "Krok 1 — Rodzaj pisma, Krok 3 — Czas na reakcję..."); sekcja "Twoja ocena ryzyka" NIE pojawia się</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Wynik ryzyka bez wypełnionego formularza</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Testuje nową funkcję walidacji dodaną w app.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -36189,51 +36189,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>test_id</t>
+          <t>nr</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>obszar</t>
+          <t>priorytet</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>dane testowe</t>
+          <t>temat</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>oczekiwany scenariusz bazowy / zachowanie techniczne</t>
+          <t>dane do kalkulatora</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>oczekiwane moduły K3–K6</t>
+          <t>co powinien pokazać wynik</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>oczekiwany wynik użytkownika</t>
+          <t>czego NIE wolno w wyniku</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>czego NIE wolno pokazać użytkownikowi</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>uwagi</t>
         </is>
@@ -36247,42 +36237,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>ODŁOŻONY – poza MVP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Wiele dokumentów</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Pozew przeciwko spółce + pozew przeciwko członkowi zarządu</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Dokument główny: pozew przeciwko członkowi zarządu</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Zależnie od formularza</t>
+          <t>Wynik mówi, który dokument wymaga reakcji i jakie dokumenty są pomocnicze</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wynik mówi, który dokument wymaga reakcji i jakie dokumenty są pomocnicze</t>
+          <t>Nazwy reguł wyboru dokumentu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nazwy reguł wyboru dokumentu</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ODŁOŻONY – poza MVP</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Wielodokumentowość nie jest zaimplementowana w app.py (MVP). Odłożyć do kolejnego etapu.</t>
+          <t>Wielodokumentowość nie jest zaimplementowana w app.py (MVP). Odłożyć do kolejnego etapu. | Scenariusz: Dokument główny: pozew przeciwko członkowi zarządu</t>
         </is>
       </c>
     </row>
@@ -36294,42 +36274,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>ODŁOŻONY – poza MVP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Wiele dokumentów</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Nakaz przeciwko spółce + nakaz przeciwko członkowi zarządu</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Dokument główny: nakaz przeciwko członkowi zarządu</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zależnie od formularza</t>
+          <t>Wynik wskazuje nakaz jako dokument wymagający reakcji</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wynik wskazuje nakaz jako dokument wymagający reakcji</t>
+          <t>Punktacja wyboru dokumentu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Punktacja wyboru dokumentu</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ODŁOŻONY – poza MVP</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Wielodokumentowość nie jest zaimplementowana w app.py (MVP). Odłożyć do kolejnego etapu.</t>
+          <t>Wielodokumentowość nie jest zaimplementowana w app.py (MVP). Odłożyć do kolejnego etapu. | Scenariusz: Dokument główny: nakaz przeciwko członkowi zarządu</t>
         </is>
       </c>
     </row>
@@ -36341,40 +36311,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>EPU</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Nakaz EPU + pouczenie + potwierdzenie doręczenia</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Typ EPU zgodny z adresatem; dołącz Blok_EPU</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zależnie od formularza</t>
+          <t>Wynik wyjaśnia, że sprawa pochodzi z EPU/e-Sądu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wynik wyjaśnia, że sprawa pochodzi z EPU/e-Sądu</t>
+          <t>EPU jako kod techniczny bez wyjaśnienia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EPU jako kod techniczny bez wyjaśnienia</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Scenariusz: Typ EPU zgodny z adresatem; dołącz Blok_EPU</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36384,40 +36348,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Termin konkretny</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Data doręczenia + termin z pouczenia dają 5 dni</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>K2 technicznie może być 4–7 dni</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dowolne</t>
+          <t>Wynik mówi konkretnie, że zostało ok. 5 dni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wynik mówi konkretnie, że zostało ok. 5 dni</t>
+          <t>Ogólnik „około 4–7 dni”, gdy znane jest 5 dni</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ogólnik „około 4–7 dni”, gdy znane jest 5 dni</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Scenariusz: K2 technicznie może być 4–7 dni</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36427,40 +36385,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Twarde reguły</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Krótki termin albo termin niepewny</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Poziom ryzyka może zostać podniesiony</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dowolne</t>
+          <t>Użytkownik widzi nietechniczne ostrzeżenie o konieczności potwierdzenia terminu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Użytkownik widzi nietechniczne ostrzeżenie o konieczności potwierdzenia terminu</t>
+          <t>HR01, HR02, HR04 itp.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HR01, HR02, HR04 itp.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Scenariusz: Poziom ryzyka może zostać podniesiony</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36470,40 +36422,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Brak dokumentów</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Użytkownik chce tylko wstępną ocenę bez dokumentów</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>K3_SUPPORT_BASIC_NO_DOCS</t>
+          <t>Wynik jasno mówi, że ocena jest ograniczona bez dokumentów</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wynik jasno mówi, że ocena jest ograniczona bez dokumentów</t>
+          <t>Kod K3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kod K3</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Scenariusz: Scenariusz bazowy po K1/K2/ryzyku; Moduły: K3_SUPPORT_BASIC_NO_DOCS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36513,40 +36459,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Dokumenty później</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Użytkownik chce ocenę teraz i dosłanie dokumentów później</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>K3_SUPPORT_NOW_DOCS_LATER</t>
+          <t>Wynik wskazuje, jakie dokumenty trzeba później uzupełnić</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wynik wskazuje, jakie dokumenty trzeba później uzupełnić</t>
+          <t>Kod K3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kod K3</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Scenariusz: Scenariusz bazowy po K1/K2/ryzyku; Moduły: K3_SUPPORT_NOW_DOCS_LATER</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36556,40 +36496,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Gotowość do audytu</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Użytkownik gotowy wysłać dokumenty</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>K3_READY_FOR_AUDIT_48H</t>
+          <t>Wynik kieruje do listy dokumentów do Audytu 48h</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wynik kieruje do listy dokumentów do Audytu 48h</t>
+          <t>Kod K3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kod K3</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Scenariusz: Scenariusz bazowy po K1/K2/ryzyku; Moduły: K3_READY_FOR_AUDIT_48H</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36599,40 +36533,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Status zarządu aktywny</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>K4 = nadal pełnię funkcję</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy nie musi mieć K4</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MOD_K4_BOARD_ACTIVE</t>
+          <t>Wynik mówi o potrzebie sprawdzenia aktualnego statusu i adresata pisma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wynik mówi o potrzebie sprawdzenia aktualnego statusu i adresata pisma</t>
+          <t>BOARD_ACTIVE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BOARD_ACTIVE</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Scenariusz: Scenariusz bazowy nie musi mieć K4; Moduły: MOD_K4_BOARD_ACTIVE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -36642,42 +36570,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Status zarządu rezygnacja</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>K4 = rezygnacja/odwołanie</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy nie może nadpisać tego statusem aktywnym</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MOD_K4_BOARD_RESIGNED + właściwy K5</t>
+          <t>Wynik mówi o rezygnacji/odwołaniu i dacie skuteczności</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wynik mówi o rezygnacji/odwołaniu i dacie skuteczności</t>
+          <t>Informacja, że użytkownik nadal pełni funkcję</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Informacja, że użytkownik nadal pełni funkcję</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>To test problemu ze SCN_002.</t>
+          <t>To test problemu ze SCN_002. | Scenariusz: Scenariusz bazowy nie może nadpisać tego statusem aktywnym; Moduły: MOD_K4_BOARD_RESIGNED + właściwy K5</t>
         </is>
       </c>
     </row>
@@ -36689,40 +36607,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>KRS nieznany</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>K4=rezygnacja, K5=nie wiem</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MOD_K4_BOARD_RESIGNED + MOD_K5_KRS_UNKNOWN</t>
+          <t>Wynik zaleca sprawdzenie dokumentu rezygnacji/odwołania i aktualnego odpisu KRS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wynik zaleca sprawdzenie dokumentu rezygnacji/odwołania i aktualnego odpisu KRS</t>
+          <t>K5_KRS_UNKNOWN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>K5_KRS_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Scenariusz: Scenariusz bazowy po K1/K2/ryzyku; Moduły: MOD_K4_BOARD_RESIGNED + MOD_K5_KRS_UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -36732,42 +36644,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Cel: zyskać czas</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>K6 = zyskać czas na przygotowanie obrony</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MOD_K6_GOAL_BUY_TIME</t>
+          <t>Wynik mówi o legalnych środkach procesowych i przygotowaniu obrony, a nie o terminie na reakcję</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wynik mówi o legalnych środkach procesowych i przygotowaniu obrony, a nie o terminie na reakcję</t>
+          <t>Sugestia nadużycia prawa lub działań instrumentalnych</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sugestia nadużycia prawa lub działań instrumentalnych</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Rozróżnić od realnej oceny obrony.</t>
+          <t>Rozróżnić od realnej oceny obrony. | Scenariusz: Scenariusz bazowy po K1/K2/ryzyku; Moduły: MOD_K6_GOAL_BUY_TIME</t>
         </is>
       </c>
     </row>
@@ -36779,40 +36681,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Cel: ocena podstaw obrony</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>K6 = ocenić realne podstawy obrony</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MOD_K6_GOAL_DEFENSE</t>
+          <t>Wynik koncentruje się na dokumentach, podstawie roszczenia, terminach i możliwych zarzutach</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wynik koncentruje się na dokumentach, podstawie roszczenia, terminach i możliwych zarzutach</t>
+          <t>Kod K6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kod K6</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Scenariusz: Scenariusz bazowy po K1/K2/ryzyku; Moduły: MOD_K6_GOAL_DEFENSE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36822,42 +36718,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Cel: pismo procesowe</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>K6 = przygotować odpowiednie pismo procesowe</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MOD_K6_GOAL_PROCEDURAL_LETTER</t>
+          <t>Wynik wskazuje, że rodzaj pisma zależy od dokumentu: sprzeciw przy nakazie, odpowiedź przy pozwie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wynik wskazuje, że rodzaj pisma zależy od dokumentu: sprzeciw przy nakazie, odpowiedź przy pozwie</t>
+          <t>Kod K6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kod K6</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Nowa opcja K6.</t>
+          <t>Nowa opcja K6. | Scenariusz: Scenariusz bazowy po K1/K2/ryzyku; Moduły: MOD_K6_GOAL_PROCEDURAL_LETTER</t>
         </is>
       </c>
     </row>
@@ -36869,40 +36755,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Cel: plan + ocena szans</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>K6 = plan działania i ocena szans</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MOD_K6_GOAL_PLAN</t>
+          <t>Wynik wskazuje potrzebę uporządkowania planu działania i oceny szans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wynik wskazuje potrzebę uporządkowania planu działania i oceny szans</t>
+          <t>Kod K6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kod K6</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Scenariusz: Scenariusz bazowy po K1/K2/ryzyku; Moduły: MOD_K6_GOAL_PLAN</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36912,40 +36792,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Cel niepewny</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>K6 = nie wiem / uporządkowanie sytuacji</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy po K1/K2/ryzyku</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MOD_K6_GOAL_UNKNOWN</t>
+          <t>Wynik pomaga uporządkować możliwe kierunki działania</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wynik pomaga uporządkować możliwe kierunki działania</t>
+          <t>Kod K6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kod K6</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Scenariusz: Scenariusz bazowy po K1/K2/ryzyku; Moduły: MOD_K6_GOAL_UNKNOWN</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36955,40 +36829,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Model bazowy + moduły</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Nakaz przeciwko członkowi zarządu, 8–14 dni</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy dla nakazu i terminu</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Z formularza</t>
+          <t>Wynik podkreśla znaczenie terminu i treści pouczenia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wynik podkreśla znaczenie terminu i treści pouczenia</t>
+          <t>SCN_xxx w wyniku użytkownika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SCN_xxx w wyniku użytkownika</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Scenariusz: Scenariusz bazowy dla nakazu i terminu; Moduły: Z formularza</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36998,40 +36866,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>EPU pilny</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Nakaz EPU przeciwko członkowi zarządu, 0–3 dni</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy EPU + RISK_URGENT</t>
-        </is>
-      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Z formularza</t>
+          <t>Wynik pilny + blok EPU + ostrzeżenie o terminie</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wynik pilny + blok EPU + ostrzeżenie o terminie</t>
+          <t>HRxx, RISK_URGENT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HRxx, RISK_URGENT</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Scenariusz: Scenariusz bazowy EPU + RISK_URGENT; Moduły: Z formularza</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -37041,42 +36903,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Pozew spółka — brak EPU</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>K1=K1_POZEW_SPOLKA — sprawdzić, że checkbox EPU jest wyłączony (szary) i epu=False</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Typ POZEW_SPOLKA (nie EPU_POZEW_SPOLKA) — EPU_COMPATIBLE[K1_POZEW_SPOLKA]=NIE wymusza epu=False</t>
-        </is>
-      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Z formularza</t>
+          <t>Wynik standardowy dla POZEW_SPOLKA; nie myli pozwu z nakazem i spółki z członkiem zarządu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wynik standardowy dla POZEW_SPOLKA; nie myli pozwu z nakazem i spółki z członkiem zarządu</t>
+          <t>EPU_POZEW_SPOLKA jako typ; blok EPU w wyniku; wewnętrzny typ EPU</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>EPU_POZEW_SPOLKA jako typ; blok EPU w wyniku; wewnętrzny typ EPU</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>EPU jest niedostępne dla K1_POZEW_SPOLKA — checkbox jest wyłączony przez UI. Scenariusze EPU_POZEW_SPOLKA celowo nieosiągalne.</t>
+          <t>EPU jest niedostępne dla K1_POZEW_SPOLKA — checkbox jest wyłączony przez UI. Scenariusze EPU_POZEW_SPOLKA celowo nieosiągalne. | Scenariusz: Typ POZEW_SPOLKA (nie EPU_POZEW_SPOLKA) — EPU_COMPATIBLE[K1_POZEW_SPOLKA]=NIE wymusza epu=False; Moduły: Z formularza</t>
         </is>
       </c>
     </row>
@@ -37088,40 +36940,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Dokument nieustalony</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Niejasny dokument, termin nieznany</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Scenariusz bazowy dokument nieustalony albo fallback</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Z formularza</t>
+          <t>Wynik ostrożny, wskazuje potrzebę identyfikacji dokumentu i terminu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wynik ostrożny, wskazuje potrzebę identyfikacji dokumentu i terminu</t>
+          <t>komunikaty techniczne fallback</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>komunikaty techniczne fallback</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Scenariusz: Scenariusz bazowy dokument nieustalony albo fallback; Moduły: Z formularza</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -37131,42 +36977,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>SCN_002 problem</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>K1=K1_NAKAZ_CZLONEK_ZARZADU, K2=K2_DAYS_LEFT_4_7, K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_RESIGNED, K5=K5_KRS_UNKNOWN, K6=K6_GOAL_BUY_TIME, K7=K7_AMOUNT_10K_50K, EPU=NIE</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Może wybrać bazę odpowiadającą K1/K2/ryzyku, ale wynik musi wynikać z modułów K4–K6</t>
-        </is>
-      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>K4 rezygnacja + K5 nie wiem + K6 kupić czas</t>
+          <t>Wynik NIE zawiera informacji, że użytkownik nadal pełni funkcję</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wynik NIE zawiera informacji, że użytkownik nadal pełni funkcję</t>
+          <t>BOARD_ACTIVE; 'nadal pełni funkcję' przy K4=resigned</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BOARD_ACTIVE; 'nadal pełni funkcję' przy K4=resigned</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Test ze zrzutu użytkownika.</t>
+          <t>Test ze zrzutu użytkownika. | Scenariusz: Może wybrać bazę odpowiadającą K1/K2/ryzyku, ale wynik musi wynikać z modułów K4–K6; Moduły: K4 rezygnacja + K5 nie wiem + K6 kupić czas</t>
         </is>
       </c>
     </row>
@@ -37178,40 +37014,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Prywatność i technika</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Dowolny przypadek</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Panel testowy może pokazać technikę</t>
-        </is>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dowolne</t>
+          <t>Wynik użytkownika bez techniki</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wynik użytkownika bez techniki</t>
+          <t>risk_level_code, HRxx, K3/K4/K5/K6 codes, moduły, dynamicznie</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>risk_level_code, HRxx, K3/K4/K5/K6 codes, moduły, dynamicznie</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Scenariusz: Panel testowy może pokazać technikę</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -37221,40 +37051,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Pismo ZUS / urząd — krótki termin</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>K1=K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU, K2=K2_DAYS_LEFT_0_3, K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_ACTIVE, K5=K5_NOT_APPLICABLE, K6=K6_GOAL_DEFENSE, K7=K7_AMOUNT_10K_50K, EPU=NIE</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>BASE_173 (RISK_URGENT)</t>
-        </is>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>K3, K4_BOARD_ACTIVE, zus_note (nie urgency_note)</t>
+          <t>Lead: "Na pismo z ZUS lub urzędu skarbowego masz X dni"; treść mówi o piśmie ZUS; CTA o wyjaśnieniach — nie sprzeciwie</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lead: "Na pismo z ZUS lub urzędu skarbowego masz X dni"; treść mówi o piśmie ZUS; CTA o wyjaśnieniach — nie sprzeciwie</t>
+          <t>"bez ustalenia rodzaju pisma"; "sprzeciw"; "odpowiedź na pozew"; kody techniczne</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>"bez ustalenia rodzaju pisma"; "sprzeciw"; "odpowiedź na pozew"; kody techniczne</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Scenariusz: BASE_173 (RISK_URGENT); Moduły: K3, K4_BOARD_ACTIVE, zus_note (nie urgency_note)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -37264,42 +37088,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Pismo ZUS — 14 dni, RISK_URGENT przez ciężar dokumentu</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>K1=K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU, K2=K2_DAYS_LEFT_8_14 (use_dates=TAK, znana data), K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_ACTIVE, K5=K5_NOT_APPLICABLE, K6=K6_GOAL_DEFENSE, K7=K7_AMOUNT_10K_50K, EPU=NIE</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>BASE_186 (RISK_URGENT — C=3+P=1+H=3+W=1=8)</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>K3, K4_BOARD_ACTIVE, zus_note</t>
+          <t>"wysoki ciężar prawny — niezależnie od długości terminu"; wynik NIE mówi że czas wskazuje na pilność</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>"wysoki ciężar prawny — niezależnie od długości terminu"; wynik NIE mówi że czas wskazuje na pilność</t>
+          <t>"bez ustalenia rodzaju pisma"; "czas na reakcję wskazuje na podwyższoną pilność"; "sprzeciw"</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>"bez ustalenia rodzaju pisma"; "czas na reakcję wskazuje na podwyższoną pilność"; "sprzeciw"</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Weryfikuje poprawność BASE_186 — główny błąd zgłoszony przez użytkownika.</t>
+          <t>Weryfikuje poprawność BASE_186 — główny błąd zgłoszony przez użytkownika. | Scenariusz: BASE_186 (RISK_URGENT — C=3+P=1+H=3+W=1=8); Moduły: K3, K4_BOARD_ACTIVE, zus_note</t>
         </is>
       </c>
     </row>
@@ -37311,40 +37125,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>Pismo ZUS — nieznany termin</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>K1=K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU, K2=K2_DAYS_LEFT_UNKNOWN, K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_ACTIVE, K5=K5_NOT_APPLICABLE, K6=K6_GOAL_DEFENSE, K7=K7_AMOUNT_10K_50K, EPU=NIE</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>BASE_188 (RISK_URGENT) lub BASE_184 (RISK_HIGH) — zależnie od S z K2A</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>K3, K4_BOARD_ACTIVE, zus_note</t>
+          <t>Mówi o piśmie ZUS; zaleca potwierdzenie terminu z pouczenia; NIE zawiera "bez ustalenia rodzaju pisma"</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mówi o piśmie ZUS; zaleca potwierdzenie terminu z pouczenia; NIE zawiera "bez ustalenia rodzaju pisma"</t>
+          <t>"bez ustalenia rodzaju pisma"; "sprzeciw"; kody techniczne</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>"bez ustalenia rodzaju pisma"; "sprzeciw"; kody techniczne</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Scenariusz: BASE_188 (RISK_URGENT) lub BASE_184 (RISK_HIGH) — zależnie od S z K2A; Moduły: K3, K4_BOARD_ACTIVE, zus_note</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -37354,42 +37162,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Inne/nie wiem + wiele opcji "nie wiem" — RISK_URGENT</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>K1=K1_INNE_NIE_WIEM, K2=K2_DAYS_LEFT_UNKNOWN, K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_UNKNOWN, K5=K5_KRS_UNKNOWN, K6=K6_GOAL_UNKNOWN, K7=K7_AMOUNT_UNKNOWN, EPU=NIE</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>BASE_026 (K2_UNKNOWN + RISK_URGENT)</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>K3, K4_BOARD_UNKNOWN, K5_KRS_UNKNOWN, K6_GOAL_UNKNOWN, unknown_doc_note</t>
+          <t>"pilna ze względu na wysoką niepewność"; wynik NIE mówi że czas wskazuje na pilność</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>"pilna ze względu na wysoką niepewność"; wynik NIE mówi że czas wskazuje na pilność</t>
+          <t>"Czas na reakcję wskazuje na podwyższoną pilność"; kody techniczne</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>"Czas na reakcję wskazuje na podwyższoną pilność"; kody techniczne</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Weryfikuje poprawność BASE_026 po naprawie tekstu.</t>
+          <t>Weryfikuje poprawność BASE_026 po naprawie tekstu. | Scenariusz: BASE_026 (K2_UNKNOWN + RISK_URGENT); Moduły: K3, K4_BOARD_UNKNOWN, K5_KRS_UNKNOWN, K6_GOAL_UNKNOWN, unknown_doc_note</t>
         </is>
       </c>
     </row>
@@ -37401,42 +37199,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Pismo ZUS — cel: pismo procesowe</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>K1=K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU, K2=K2_DAYS_LEFT_8_14, K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_ACTIVE, K5=K5_NOT_APPLICABLE, K6=K6_GOAL_PROCEDURAL_LETTER, K7=K7_AMOUNT_10K_50K, EPU=NIE</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>BASE_186 lub BASE_178</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>K6_GOAL_PROCEDURAL_LETTER (wyjaśnienia, nie sprzeciw)</t>
+          <t>K6 text: "wyjaśnienia i dokumenty potwierdzające stanowisko — nie sprzeciw ani odpowiedź na pozew"</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>K6 text: "wyjaśnienia i dokumenty potwierdzające stanowisko — nie sprzeciw ani odpowiedź na pozew"</t>
+          <t>"sprzeciw"; "odpowiedź na pozew"; kody techniczne</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>"sprzeciw"; "odpowiedź na pozew"; kody techniczne</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Kluczowa reguła komunikacyjna dla ZUS.</t>
+          <t>Kluczowa reguła komunikacyjna dla ZUS. | Scenariusz: BASE_186 lub BASE_178; Moduły: K6_GOAL_PROCEDURAL_LETTER (wyjaśnienia, nie sprzeciw)</t>
         </is>
       </c>
     </row>
@@ -37448,42 +37236,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>DO TESTU</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>Punktacja K2A — ręczny wybór K2</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>K1=K1_INNE_NIE_WIEM, K2=K2_DAYS_LEFT_UNKNOWN (bez zaznaczenia checkboxa daty), K3=K3_SUPPORT_BASIC_NO_DOCS, K4=K4_BOARD_ACTIVE, K5=K5_NOT_APPLICABLE, K6=K6_GOAL_DEFENSE, K7=K7_AMOUNT_10K_50K</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Panel testowy: answers zawiera K2A=K2A_DELIVERY_DATE_UNKNOWN</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brak widocznego modułu K2A w wyniku</t>
+          <t>Panel testowy pokazuje H wyższe o 1 niż bez K2A; klient nie widzi K2A w tekście wyniku</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Panel testowy pokazuje H wyższe o 1 niż bez K2A; klient nie widzi K2A w tekście wyniku</t>
+          <t>K2A_DELIVERY_DATE_UNKNOWN jako widoczny tekst; kody techniczne</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>K2A_DELIVERY_DATE_UNKNOWN jako widoczny tekst; kody techniczne</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>DO TESTU</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Weryfikacja przez panel testowy — klient widzi tylko wynik S i poziom ryzyka.</t>
+          <t>Weryfikacja przez panel testowy — klient widzi tylko wynik S i poziom ryzyka. | Scenariusz: Panel testowy: answers zawiera K2A=K2A_DELIVERY_DATE_UNKNOWN; Moduły: Brak widocznego modułu K2A w wyniku</t>
         </is>
       </c>
     </row>
@@ -37495,42 +37273,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>KLUCZOWY</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>Walidacja formularza</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Kalkulator po starcie lub po wyczyszczeniu — kliknij "Oblicz ryzyko →" bez zaznaczenia żadnych opcji</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Brak obliczeń — walidacja blokuje wykonanie</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brak</t>
+          <t>Pojawia się ostrzeżenie z listą brakujących kroków (np. "Krok 1 — Rodzaj pisma, Krok 3 — Czas na reakcję..."); sekcja "Twoja ocena ryzyka" NIE pojawia się</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pojawia się ostrzeżenie z listą brakujących kroków (np. "Krok 1 — Rodzaj pisma, Krok 3 — Czas na reakcję..."); sekcja "Twoja ocena ryzyka" NIE pojawia się</t>
+          <t>Wynik ryzyka bez wypełnionego formularza</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Wynik ryzyka bez wypełnionego formularza</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>KLUCZOWY</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Testuje nową funkcję walidacji dodaną w app.py.</t>
+          <t>Testuje nową funkcję walidacji dodaną w app.py. | Scenariusz: Brak obliczeń — walidacja blokuje wykonanie; Moduły: Brak</t>
         </is>
       </c>
     </row>

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -37554,7 +37554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="23.5" customWidth="1" style="4" min="1" max="1"/>
@@ -38713,47 +38713,94 @@
       </c>
     </row>
     <row r="26" ht="140.4499969482422" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PISMO_PROCESOWE_SADOWE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pismo procesowe w toczącym się postępowaniu sądowym</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sąd</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>członek zarządu / spółka</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>pismo przygotowawcze; odpowiedź na sprzeciw; w odpowiedzi na sprzeciw; replika; podtrzymuję; wnoszę o oddalenie; postępowanie w toku; sprawa w toku; dalsze pisma</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>pismo przygotowawcze; odpowiedź na sprzeciw; w odpowiedzi na sprzeciw</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>termin wskazany w wezwaniu sądu jeśli dotyczy</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>WARUNKOWO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Dokument wskazuje na kontynuację sporu sądowego. Bez kompletnej dokumentacji (pozwu, sprzeciwu, wcześniejszych pism) rzetelna ocena jest niemożliwa. Jeżeli jest dokumentem głównym — przekierować do Audytu 48h z pełną dokumentacją.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Pismo z ZUS / urzędu dotyczące odpowiedzialności członka zarządu</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>organ publiczny</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>członek zarządu</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>ZUS; Zakład Ubezpieczeń Społecznych; urząd skarbowy; naczelnik urzędu skarbowego; odpowiedzialność osoby trzeciej; odpowiedzialność członka zarządu; zaległości składkowe; zaległości podatkowe; Ordynacja podatkowa; ustawa o systemie ubezpieczeń społecznych; wezwanie do wyjaśnień; zawiadomienie o wszczęciu postępowania; decyzja</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>organ publiczny informuje o wszczęciu postępowania albo wzywa członka zarządu do wyjaśnień w sprawie odpowiedzialności za zobowiązania spółki</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>termin wskazany w piśmie organu, często na złożenie wyjaśnień albo dokumentów</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>TAK</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Odrębna ścieżka od pozwu/nakazu. Nie generować sprzeciwu ani odpowiedzi na pozew; priorytetem są wyjaśnienia, dowody, okres pełnienia funkcji i przesłanki wyłączające odpowiedzialność.</t>
         </is>

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -27748,7 +27748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="6.25" customWidth="1" style="4" min="1" max="1"/>
@@ -27985,39 +27985,41 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>R07</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R06a</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Typ dokumentu</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Wezwanie sądowe skierowane do członka zarządu</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Bardzo silny kandydat</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Może oznaczać konieczność reakcji lub udziału w postępowaniu</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pozew w elektronicznym postepowaniu upominawczym (EPU) przeciwko czlonkowi zarzadu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Dokument glowny - wysoki priorytet</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jezeli sygnatura zawiera Nc-e albo wystepuje Sad Rejonowy Lublin-Zachod, dodaj flage EPU. Pozew jest wczesniejszym etapem niz nakaz - nie musi zawierac formuly nakazowej.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>R08</t>
+          <t>R07</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -28027,7 +28029,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Pismo komornicze skierowane do członka zarządu</t>
+          <t>Wezwanie sądowe skierowane do członka zarządu</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
@@ -28040,14 +28042,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Wskazuje na etap egzekucyjny albo ryzyko majątkowe</t>
+          <t>Może oznaczać konieczność reakcji lub udziału w postępowaniu</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>R09</t>
+          <t>R08</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -28057,27 +28059,27 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Pozew przeciwko spółce</t>
+          <t>Pismo komornicze skierowane do członka zarządu</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Dokument główny tylko wtedy, gdy brak dokumentu przeciwko członkowi zarządu</t>
+          <t>Bardzo silny kandydat</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Ważny jako kontekst, ale nie zawsze bezpośrednio dotyczy odpowiedzialności osobistej</t>
+          <t>Wskazuje na etap egzekucyjny albo ryzyko majątkowe</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R09</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -28087,11 +28089,11 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Nakaz zapłaty przeciwko spółce</t>
+          <t>Pozew przeciwko spółce</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -28100,14 +28102,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Może być ważny dla późniejszej odpowiedzialności z art. 299 KSH</t>
+          <t>Ważny jako kontekst, ale nie zawsze bezpośrednio dotyczy odpowiedzialności osobistej</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -28117,27 +28119,27 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Pismo komornicze dotyczące egzekucji przeciwko spółce</t>
+          <t>Nakaz zapłaty przeciwko spółce</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Ważny dokument kontekstowy, czasem główny</t>
+          <t>Dokument główny tylko wtedy, gdy brak dokumentu przeciwko członkowi zarządu</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Szczególnie ważny, jeżeli wskazuje na bezskuteczność egzekucji</t>
+          <t>Może być ważny dla późniejszej odpowiedzialności z art. 299 KSH</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -28147,27 +28149,27 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Postanowienie o umorzeniu egzekucji przeciwko spółce z powodu bezskuteczności</t>
+          <t>Pismo komornicze dotyczące egzekucji przeciwko spółce</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Bardzo ważny dokument kontekstowy</t>
+          <t>Ważny dokument kontekstowy, czasem główny</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Może być kluczowy dla sprawy z art. 299 KSH, ale nie zawsze wymaga natychmiastowej reakcji</t>
+          <t>Szczególnie ważny, jeżeli wskazuje na bezskuteczność egzekucji</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -28177,27 +28179,27 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Przedsądowe wezwanie do zapłaty skierowane do członka zarządu</t>
+          <t>Postanowienie o umorzeniu egzekucji przeciwko spółce z powodu bezskuteczności</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Kandydat na dokument główny</t>
+          <t>Bardzo ważny dokument kontekstowy</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Ważne, ale zwykle mniej pilne niż pozew lub nakaz</t>
+          <t>Może być kluczowy dla sprawy z art. 299 KSH, ale nie zawsze wymaga natychmiastowej reakcji</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -28207,27 +28209,27 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Przedsądowe wezwanie do zapłaty skierowane do spółki</t>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do członka zarządu</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Dokument pomocniczy</t>
+          <t>Kandydat na dokument główny</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Nie powinien wygrywać z dokumentem sądowym</t>
+          <t>Ważne, ale zwykle mniej pilne niż pozew lub nakaz</t>
         </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -28237,27 +28239,27 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Decyzja ZUS lub decyzja podatkowa dotycząca odpowiedzialności osoby zarządzającej</t>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do spółki</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Silny kandydat na dokument główny</t>
+          <t>Dokument pomocniczy</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Dotyczy odpowiedzialności osobistej, ale może należeć do ścieżki Audyt 48h, nie tylko art. 299 KSH</t>
+          <t>Nie powinien wygrywać z dokumentem sądowym</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -28267,57 +28269,57 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Decyzja ZUS lub US skierowana wyłącznie do spółki</t>
+          <t>Decyzja ZUS lub decyzja podatkowa dotycząca odpowiedzialności osoby zarządzającej</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Dokument pomocniczy albo kandydat drugiego rzędu</t>
+          <t>Silny kandydat na dokument główny</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Ważny kontekst, ale niższy priorytet niż decyzja wobec osoby fizycznej</t>
+          <t>Dotyczy odpowiedzialności osobistej, ale może należeć do ścieżki Audyt 48h, nie tylko art. 299 KSH</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Termin</t>
+          <t>Typ dokumentu</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Dokument zawiera wyraźny termin reakcji: sprzeciw, zarzuty, odpowiedź, odwołanie, skarga, zażalenie</t>
+          <t>Decyzja ZUS lub US skierowana wyłącznie do spółki</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Silny kandydat na dokument główny</t>
+          <t>Dokument pomocniczy albo kandydat drugiego rzędu</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Termin reakcji bardzo zwiększa priorytet dokumentu</t>
+          <t>Ważny kontekst, ale niższy priorytet niż decyzja wobec osoby fizycznej</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -28327,27 +28329,27 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Dokument wskazuje termin 0–3 dni pozostałe na reakcję</t>
+          <t>Dokument zawiera wyraźny termin reakcji: sprzeciw, zarzuty, odpowiedź, odwołanie, skarga, zażalenie</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Dokument krytyczny</t>
+          <t>Silny kandydat na dokument główny</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Jeżeli termin jest tak krótki, dokument prawie zawsze powinien być główny</t>
+          <t>Termin reakcji bardzo zwiększa priorytet dokumentu</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -28357,27 +28359,27 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Dokument wskazuje termin 4–7 dni pozostałe na reakcję</t>
+          <t>Dokument wskazuje termin 0–3 dni pozostałe na reakcję</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Dokument bardzo pilny</t>
+          <t>Dokument krytyczny</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Wysoki priorytet</t>
+          <t>Jeżeli termin jest tak krótki, dokument prawie zawsze powinien być główny</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -28387,27 +28389,27 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Dokument wskazuje termin 8–14 dni pozostałe na reakcję</t>
+          <t>Dokument wskazuje termin 4–7 dni pozostałe na reakcję</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Dokument pilny</t>
+          <t>Dokument bardzo pilny</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Średnio-wysoki priorytet</t>
+          <t>Wysoki priorytet</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -28417,27 +28419,27 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Dokument wskazuje termin powyżej 14 dni</t>
+          <t>Dokument wskazuje termin 8–14 dni pozostałe na reakcję</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Dokument mniej pilny</t>
+          <t>Dokument pilny</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Priorytet zależy od typu dokumentu</t>
+          <t>Średnio-wysoki priorytet</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -28447,7 +28449,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Nie udało się ustalić terminu reakcji</t>
+          <t>Dokument wskazuje termin powyżej 14 dni</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -28455,49 +28457,49 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Kandydat niepewny</t>
+          <t>Dokument mniej pilny</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>AI powinno oznaczyć brak pewności i wskazać konieczność weryfikacji w Audycie 48h</t>
+          <t>Priorytet zależy od typu dokumentu</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Etap sprawy</t>
+          <t>Termin</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Dokument pochodzi z sądu</t>
+          <t>Nie udało się ustalić terminu reakcji</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Wysoki priorytet</t>
+          <t>Kandydat niepewny</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Sądowe dokumenty mają wyższy priorytet niż korespondencja prywatna</t>
+          <t>AI powinno oznaczyć brak pewności i wskazać konieczność weryfikacji w Audycie 48h</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>R24</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -28507,7 +28509,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Dokument pochodzi od komornika</t>
+          <t>Dokument pochodzi z sądu</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -28520,14 +28522,14 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Może wskazywać na etap egzekucji lub bezskuteczność egzekucji</t>
+          <t>Sądowe dokumenty mają wyższy priorytet niż korespondencja prywatna</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>R25</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -28537,7 +28539,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Dokument pochodzi od ZUS, US albo innego organu</t>
+          <t>Dokument pochodzi od komornika</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -28550,14 +28552,14 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Szczególnie gdy dotyczy osoby fizycznej</t>
+          <t>Może wskazywać na etap egzekucji lub bezskuteczność egzekucji</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>R26</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -28567,147 +28569,147 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Dokument pochodzi od wierzyciela albo kancelarii wierzyciela</t>
+          <t>Dokument pochodzi od ZUS, US albo innego organu</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Średni priorytet</t>
+          <t>Wysoki priorytet</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Ważne, ale niżej niż sąd/organ/komornik</t>
+          <t>Szczególnie gdy dotyczy osoby fizycznej</t>
         </is>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>R27</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Art. 299 KSH</t>
+          <t>Etap sprawy</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Dokument zawiera frazy: „art. 299 KSH”, „odpowiedzialność członków zarządu”, „bezskuteczność egzekucji”, „zobowiązania spółki”</t>
+          <t>Dokument pochodzi od wierzyciela albo kancelarii wierzyciela</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Bardzo silny sygnał zgodności z celem kalkulatora</t>
+          <t>Średni priorytet</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>AI powinno podnieść priorytet dokumentu</t>
+          <t>Ważne, ale niżej niż sąd/organ/komornik</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>R28</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>EPU</t>
+          <t>Art. 299 KSH</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Dokument zawiera sygnaturę „Nc-e” albo wskazuje Sąd Rejonowy Lublin-Zachód w Lublinie</t>
+          <t>Dokument zawiera frazy: „art. 299 KSH”, „odpowiedzialność członków zarządu”, „bezskuteczność egzekucji”, „zobowiązania spółki”</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Dodaj flagę EPU</t>
+          <t>Bardzo silny sygnał zgodności z celem kalkulatora</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Nie musi samodzielnie przesądzać wyboru, ale podnosi pilność</t>
+          <t>AI powinno podnieść priorytet dokumentu</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>R29</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Data dokumentu</t>
+          <t>EPU</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Dokument jest najnowszy spośród dokumentów o podobnym priorytecie</t>
+          <t>Dokument zawiera sygnaturę „Nc-e” albo wskazuje Sąd Rejonowy Lublin-Zachód w Lublinie</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Reguła pomocnicza</t>
+          <t>Dodaj flagę EPU</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Stosować tylko przy remisie albo bardzo zbliżonym wyniku</t>
+          <t>Nie musi samodzielnie przesądzać wyboru, ale podnosi pilność</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>R29</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Jakość odczytu</t>
+          <t>Data dokumentu</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Dokument został odczytany z wysoką pewnością OCR/tekstu</t>
+          <t>Dokument jest najnowszy spośród dokumentów o podobnym priorytecie</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Podnosi pewność wyboru</t>
+          <t>Reguła pomocnicza</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Nie powinno decydować samo w sobie</t>
+          <t>Stosować tylko przy remisie albo bardzo zbliżonym wyniku</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -28717,103 +28719,121 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Dokument został odczytany z niską pewnością OCR/tekstu</t>
+          <t>Dokument został odczytany z wysoką pewnością OCR/tekstu</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Obniża pewność wyboru</t>
+          <t>Podnosi pewność wyboru</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>AI powinno pokazać ostrzeżenie o konieczności weryfikacji</t>
+          <t>Nie powinno decydować samo w sobie</t>
         </is>
       </c>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Dokument pomocniczy</t>
+          <t>Jakość odczytu</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Dokument jest fakturą, umową, odpisem KRS, korespondencją handlową, potwierdzeniem przelewu albo dokumentem księgowym</t>
+          <t>Dokument został odczytany z niską pewnością OCR/tekstu</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Zwykle nie wybierać jako główny</t>
+          <t>Obniża pewność wyboru</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Może być ważny dla Audytu 48h, ale nie jako dokument wymagający reakcji</t>
+          <t>AI powinno pokazać ostrzeżenie o konieczności weryfikacji</t>
         </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Dokument pomocniczy</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Dokument jest fakturą, umową, odpisem KRS, korespondencją handlową, potwierdzeniem przelewu albo dokumentem księgowym</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>-20</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Zwykle nie wybierać jako główny</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Może być ważny dla Audytu 48h, ale nie jako dokument wymagający reakcji</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>R33</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Dokument obcy tematycznie</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Dokument nie jest dokumentem prawnym albo nie dotyczy odpowiedzialności zarządu/spółki</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D36" s="5" t="n">
         <v>-100</v>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Nie wybierać jako dokument główny</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Pokazać komunikat: „Wczytany dokument wydaje się nie być właściwy dla kalkulatora”</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="25" t="n"/>
-      <c r="B36" s="26" t="inlineStr">
-        <is>
-          <t>Kolejność oceny powinna być następująca:</t>
-        </is>
-      </c>
-      <c r="C36" s="69" t="n"/>
-      <c r="D36" s="25" t="n"/>
-      <c r="E36" s="25" t="n"/>
-      <c r="F36" s="25" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="25" t="n"/>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>1. Czy dokument dotyczy członka zarządu?</t>
-        </is>
-      </c>
-      <c r="C37" s="37" t="n"/>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>Kolejność oceny powinna być następująca:</t>
+        </is>
+      </c>
+      <c r="C37" s="69" t="n"/>
       <c r="D37" s="25" t="n"/>
       <c r="E37" s="25" t="n"/>
       <c r="F37" s="25" t="n"/>
@@ -28822,7 +28842,7 @@
       <c r="A38" s="25" t="n"/>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>2. Czy dokument uruchamia termin na reakcję?</t>
+          <t>1. Czy dokument dotyczy członka zarządu?</t>
         </is>
       </c>
       <c r="C38" s="37" t="n"/>
@@ -28834,7 +28854,7 @@
       <c r="A39" s="25" t="n"/>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>3. Czy dokument dotyczy odpowiedzialności z art. 299 KSH albo podobnego ryzyka osobistego?</t>
+          <t>2. Czy dokument uruchamia termin na reakcję?</t>
         </is>
       </c>
       <c r="C39" s="37" t="n"/>
@@ -28846,7 +28866,7 @@
       <c r="A40" s="25" t="n"/>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>4. Czy dokument pochodzi z sądu, komornika, organu lub wierzyciela?</t>
+          <t>3. Czy dokument dotyczy odpowiedzialności z art. 299 KSH albo podobnego ryzyka osobistego?</t>
         </is>
       </c>
       <c r="C40" s="37" t="n"/>
@@ -28858,7 +28878,7 @@
       <c r="A41" s="25" t="n"/>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>5. Czy dokument jest aktualny i ma biegnący termin?</t>
+          <t>4. Czy dokument pochodzi z sądu, komornika, organu lub wierzyciela?</t>
         </is>
       </c>
       <c r="C41" s="37" t="n"/>
@@ -28870,7 +28890,7 @@
       <c r="A42" s="25" t="n"/>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>6. Dopiero na końcu — jaka jest data dokumentu.</t>
+          <t>5. Czy dokument jest aktualny i ma biegnący termin?</t>
         </is>
       </c>
       <c r="C42" s="37" t="n"/>
@@ -28878,37 +28898,33 @@
       <c r="E42" s="25" t="n"/>
       <c r="F42" s="25" t="n"/>
     </row>
-    <row r="44" ht="72" customFormat="1" customHeight="1" s="37">
-      <c r="C44" s="38" t="inlineStr">
-        <is>
-          <t>Doprecyzowanie po uwagach</t>
-        </is>
-      </c>
-      <c r="D44" s="39" t="inlineStr">
-        <is>
-          <t>Relacja między punktacją a kolejnością oceny</t>
-        </is>
-      </c>
-      <c r="E44" s="38" t="inlineStr">
-        <is>
-          <t>Kolejność oceny jest hierarchią merytoryczną, a punktacja jest jej technicznym odwzorowaniem. Data dokumentu jest kryterium pomocniczym stosowanym na końcu, zwłaszcza przy remisie.</t>
-        </is>
-      </c>
-    </row>
+    <row r="43">
+      <c r="A43" s="25" t="n"/>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>6. Dopiero na końcu — jaka jest data dokumentu.</t>
+        </is>
+      </c>
+      <c r="C43" s="37" t="n"/>
+      <c r="D43" s="25" t="n"/>
+      <c r="E43" s="25" t="n"/>
+      <c r="F43" s="25" t="n"/>
+    </row>
+    <row r="44" ht="72" customFormat="1" customHeight="1" s="37"/>
     <row r="45" customFormat="1" s="37">
       <c r="C45" s="38" t="inlineStr">
         <is>
-          <t>Kolejność oceny</t>
-        </is>
-      </c>
-      <c r="D45" s="38" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Doprecyzowanie po uwagach</t>
+        </is>
+      </c>
+      <c r="D45" s="39" t="inlineStr">
+        <is>
+          <t>Relacja między punktacją a kolejnością oceny</t>
         </is>
       </c>
       <c r="E45" s="38" t="inlineStr">
         <is>
-          <t>Czy dokument dotyczy członka zarządu?</t>
+          <t>Kolejność oceny jest hierarchią merytoryczną, a punktacja jest jej technicznym odwzorowaniem. Data dokumentu jest kryterium pomocniczym stosowanym na końcu, zwłaszcza przy remisie.</t>
         </is>
       </c>
     </row>
@@ -28920,12 +28936,12 @@
       </c>
       <c r="D46" s="38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" s="38" t="inlineStr">
         <is>
-          <t>Czy dokument uruchamia termin na reakcję?</t>
+          <t>Czy dokument dotyczy członka zarządu?</t>
         </is>
       </c>
     </row>
@@ -28937,12 +28953,12 @@
       </c>
       <c r="D47" s="38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" s="38" t="inlineStr">
         <is>
-          <t>Czy dokument dotyczy odpowiedzialności z art. 299 k.s.h. albo podobnej odpowiedzialności osoby zarządzającej?</t>
+          <t>Czy dokument uruchamia termin na reakcję?</t>
         </is>
       </c>
     </row>
@@ -28954,12 +28970,12 @@
       </c>
       <c r="D48" s="38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E48" s="38" t="inlineStr">
         <is>
-          <t>Czy dokument pochodzi z sądu, komornika albo organu publicznego?</t>
+          <t>Czy dokument dotyczy odpowiedzialności z art. 299 k.s.h. albo podobnej odpowiedzialności osoby zarządzającej?</t>
         </is>
       </c>
     </row>
@@ -28971,12 +28987,12 @@
       </c>
       <c r="D49" s="38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E49" s="38" t="inlineStr">
         <is>
-          <t>Czy dokument jest aktualny i ma bieżący termin?</t>
+          <t>Czy dokument pochodzi z sądu, komornika albo organu publicznego?</t>
         </is>
       </c>
     </row>
@@ -28988,10 +29004,27 @@
       </c>
       <c r="D50" s="38" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E50" s="38" t="inlineStr">
+        <is>
+          <t>Czy dokument jest aktualny i ma bieżący termin?</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="38" t="inlineStr">
+        <is>
+          <t>Kolejność oceny</t>
+        </is>
+      </c>
+      <c r="D51" s="38" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E50" s="38" t="inlineStr">
+      <c r="E51" s="38" t="inlineStr">
         <is>
           <t>Dopiero na końcu — jaka jest data dokumentu.</t>
         </is>
@@ -37936,12 +37969,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>pozew; e-sąd; EPU; Nc-e; Sąd Rejonowy Lublin-Zachód; pozwany: członek zarządu; art. 299 ksh</t>
+          <t>pozew; P O Z E W; e-sad; EPU; Sad Rejonowy Lublin-Zachod; wartosc przedmiotu sporu; uzasadnienie; wnosimy o; wnosze o</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>pozew w elektronicznym postępowaniu upominawczym przeciwko członkowi zarządu</t>
+          <t>pozew o zaplate; powod wnosi o</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -28807,11 +28807,7 @@
           <t>Dokument obcy tematycznie</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Dokument nie jest dokumentem prawnym albo nie dotyczy odpowiedzialności zarządu/spółki</t>
-        </is>
-      </c>
+      <c r="C36" s="68" t="n"/>
       <c r="D36" s="5" t="n">
         <v>-100</v>
       </c>
@@ -35815,7 +35811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="9.75" customWidth="1" style="4" min="1" max="1"/>
@@ -35880,90 +35876,107 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Jeden dokument to nakaz zapłaty, drugi to pozew</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Wybrać nakaz zapłaty, jeżeli termin na sprzeciw/zarzuty jeszcze biegnie</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2a</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Oba dokumenty to nakazy tego samego rodzaju (EPU lub zwykły); jeden zawiera instrukcję terminu reakcji (np. "w ciągu dwóch tygodni"), drugi nie</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Wybrać nakaz z instrukcją terminu — strona uzasadnienia błędnie sklasyfikowana jako nakaz nie powinna wyprzedzać faktycznego nakazu EPU</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Jeden dokument pochodzi z EPU</t>
+          <t>Jeden dokument to nakaz zapłaty, drugi to pozew</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Wybrać dokument EPU, jeżeli jest skierowany do członka zarządu albo termin nadal biegnie</t>
+          <t>Wybrać nakaz zapłaty — nakaz ma bezwzględnie wyższy priorytet niż pozew niezależnie od biegnącego terminu</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Jeden dokument pochodzi od sądu, drugi od wierzyciela</t>
+          <t>Jeden dokument pochodzi z EPU</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Wybrać dokument sądowy</t>
+          <t>Wybrać dokument EPU, jeżeli jest skierowany do członka zarządu albo termin nadal biegnie</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Jeden dokument pochodzi od komornika, drugi jest wcześniejszym dokumentem wierzyciela</t>
+          <t>Jeden dokument pochodzi od sądu, drugi od wierzyciela</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Wybrać dokument komorniczy</t>
+          <t>Wybrać dokument sądowy</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Dokumenty są tego samego typu i mają podobny priorytet</t>
+          <t>Jeden dokument pochodzi od komornika, drugi jest wcześniejszym dokumentem wierzyciela</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Wybrać dokument najnowszy</t>
+          <t>Wybrać dokument komorniczy</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Dokumenty są tego samego typu i mają podobny priorytet</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Wybrać dokument najnowszy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Nadal nie można ustalić dokumentu głównego</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Poprosić użytkownika o ręczny wybór dokumentu głównego</t>
         </is>

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -38311,7 +38311,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>przedsądowe wezwanie do zapłaty; wezwanie do zapłaty; ostateczne wezwanie; art. 299 KSH; odpowiedzialność członka zarządu</t>
+          <t>przedsądowe wezwanie do zapłaty; wezwanie do zapłaty; ostateczne wezwanie; art. 299 KSH; odpowiedzialność członka zarządu; przedsądowe</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -38358,7 +38358,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>wezwanie do zapłaty; przedsądowe wezwanie; należność; faktura; zaległość</t>
+          <t>wezwanie do zapłaty; przedsądowe wezwanie; należność; faktura; zaległość; przedsądowe</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -37600,7 +37600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="23.5" customWidth="1" style="4" min="1" max="1"/>
@@ -37935,7 +37935,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>pozew; e-sąd; EPU; Nc-e; Sąd Rejonowy Lublin-Zachód; powód; pozwany: spółka</t>
+          <t>pozew; e-sąd; EPU; Sąd Rejonowy Lublin-Zachód; powód; pozwany: spółka</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -37982,12 +37982,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>pozew; P O Z E W; e-sad; EPU; Sad Rejonowy Lublin-Zachod; wartosc przedmiotu sporu; uzasadnienie; wnosimy o; wnosze o</t>
+          <t>pozew; P O Z E W; e-sąd; EPU; Sąd Rejonowy Lublin-Zachód; wartość przedmiotu sporu; uzasadnienie; wnosimy o; wnoszę o</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>pozew o zaplate; powod wnosi o</t>
+          <t>pozew o zapłatę; powód wnosi o</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -38264,12 +38264,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>umorzyć postępowanie egzekucyjne; bezskuteczność egzekucji; egzekucja okazała się bezskuteczna; komornik</t>
+          <t>umorzyć postępowanie egzekucyjne; umorzyć z urzędu postępowanie egzekucyjne; bezskutecz; brak majątku; art. 824; komornik; postanowił</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>wyraźne wskazanie bezskuteczności egzekucji przeciwko spółce</t>
+          <t>umorzyć z urzędu postępowanie egzekucyjne</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -38289,61 +38289,61 @@
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Przedsądowe wezwanie do zapłaty skierowane do członka zarządu</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WNIOSEK_EGZEKUCYJNY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wniosek wierzyciela o wszczęcie postępowania egzekucyjnego</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>wierzyciel</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>członek zarządu</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>przedsądowe wezwanie do zapłaty; wezwanie do zapłaty; ostateczne wezwanie; art. 299 KSH; odpowiedzialność członka zarządu; przedsądowe</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>wierzyciel żąda zapłaty od członka zarządu</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>termin z wezwania, często 3/7/14 dni</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Może być dokumentem głównym, jeżeli brak pozwu albo nakazu.</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>komornik</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>wniosek o wszczęcie postępowania egzekucyjnego; tytuł wykonawczy; wierzyciel; dłużnik; komornik sądowy</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>wniosek o wszczęcie postępowania egzekucyjnego</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>pismo nie jest skierowane do dłużnika, brak terminu obrony</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Dokument czysto informacyjny/tła sprawy — pismo wierzyciela DO komornika, nigdy nie powinien być dokumentem głównym.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>WEZWANIE_PRZEDSADOWE_SPOLKA</t>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Przedsądowe wezwanie do zapłaty skierowane do spółki</t>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do członka zarządu</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -38353,91 +38353,91 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>spółka</t>
+          <t>członek zarządu</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>wezwanie do zapłaty; przedsądowe wezwanie; należność; faktura; zaległość; przedsądowe</t>
+          <t>przedsądowe wezwanie do zapłaty; wezwanie do zapłaty; ostateczne wezwanie; art. 299 KSH; odpowiedzialność członka zarządu; przedsądowe</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>wezwanie skierowane tylko do spółki</t>
+          <t>wierzyciel żąda zapłaty od członka zarządu</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>termin z wezwania</t>
+          <t>termin z wezwania, często 3/7/14 dni</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>WARUNKOWO</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Zwykle dokument pomocniczy. Nie powinien wygrać z dokumentem sądowym.</t>
+          <t>Może być dokumentem głównym, jeżeli brak pozwu albo nakazu.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>DECYZJA_ZUS_CZLONEK_ZARZADU</t>
+          <t>WEZWANIE_PRZEDSADOWE_SPOLKA</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Decyzja ZUS dotycząca odpowiedzialności członka zarządu</t>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do spółki</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>organ</t>
+          <t>wierzyciel</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>członek zarządu</t>
+          <t>spółka</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Zakład Ubezpieczeń Społecznych; decyzja; odpowiedzialność; członek zarządu; zaległości składkowe; odwołanie</t>
+          <t>wezwanie do zapłaty; przedsądowe wezwanie; należność; faktura; zaległość; przedsądowe</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>decyzja kierowana do osoby fizycznej jako członka zarządu</t>
+          <t>wezwanie skierowane tylko do spółki</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>termin odwołania z decyzji</t>
+          <t>termin z wezwania</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>WARUNKOWO</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Może należeć bardziej do Audytu 48h niż klasycznego art. 299 KSH, ale jest ważna dla KRS Guard.</t>
+          <t>Zwykle dokument pomocniczy. Nie powinien wygrać z dokumentem sądowym.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>DECYZJA_US_CZLONEK_ZARZADU</t>
+          <t>DECYZJA_ZUS_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Decyzja podatkowa dotycząca odpowiedzialności członka zarządu</t>
+          <t>Decyzja ZUS dotycząca odpowiedzialności członka zarządu</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -38452,12 +38452,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>urząd skarbowy; naczelnik urzędu skarbowego; decyzja; odpowiedzialność osoby trzeciej; zaległości podatkowe; odwołanie</t>
+          <t>Zakład Ubezpieczeń Społecznych; decyzja; odpowiedzialność; członek zarządu; zaległości składkowe; odwołanie</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>decyzja kierowana do osoby fizycznej/członka zarządu</t>
+          <t>decyzja kierowana do osoby fizycznej jako członka zarządu</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -38472,19 +38472,19 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Wysoki priorytet, zwłaszcza gdy biegnie termin odwołania.</t>
+          <t>Może należeć bardziej do Audytu 48h niż klasycznego art. 299 KSH, ale jest ważna dla KRS Guard.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>DECYZJA_ZUS_US_SPOLKA</t>
+          <t>DECYZJA_US_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Decyzja ZUS/US skierowana do spółki</t>
+          <t>Decyzja podatkowa dotycząca odpowiedzialności członka zarządu</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -38494,91 +38494,91 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>spółka</t>
+          <t>członek zarządu</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>decyzja; ZUS; urząd skarbowy; zaległości; spółka; płatnik; podatnik</t>
+          <t>urząd skarbowy; naczelnik urzędu skarbowego; decyzja; odpowiedzialność osoby trzeciej; zaległości podatkowe; odwołanie</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>decyzja dotyczy spółki, nie członka zarządu</t>
+          <t>decyzja kierowana do osoby fizycznej/członka zarządu</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>termin wskazany w decyzji</t>
+          <t>termin odwołania z decyzji</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>WARUNKOWO</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Dokument pomocniczy lub główny tylko wtedy, gdy brak dokumentu wobec członka zarządu.</t>
+          <t>Wysoki priorytet, zwłaszcza gdy biegnie termin odwołania.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>POTWIERDZENIE_DORECZENIA</t>
+          <t>DECYZJA_ZUS_US_SPOLKA</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Potwierdzenie doręczenia</t>
+          <t>Decyzja ZUS/US skierowana do spółki</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>pomocniczy</t>
+          <t>organ</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>nieustalony</t>
+          <t>spółka</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>koperta; UPP; e-doręczenie; potwierdzenie odbioru; data doręczenia; awizo; przesyłka</t>
+          <t>decyzja; ZUS; urząd skarbowy; zaległości; spółka; płatnik; podatnik</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>zawiera datę doręczenia pisma</t>
+          <t>decyzja dotyczy spółki, nie członka zarządu</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>nie dotyczy</t>
+          <t>termin wskazany w decyzji</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>WARUNKOWO</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Nigdy nie powinno być dokumentem głównym, ale jest kluczowe do obliczenia terminu.</t>
+          <t>Dokument pomocniczy lub główny tylko wtedy, gdy brak dokumentu wobec członka zarządu.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>ODPIS_KRS</t>
+          <t>POTWIERDZENIE_DORECZENIA</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Odpis KRS</t>
+          <t>Potwierdzenie doręczenia</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -38588,17 +38588,17 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>spółka</t>
+          <t>nieustalony</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Krajowy Rejestr Sądowy; odpis aktualny; odpis pełny; reprezentacja; zarząd; wspólnicy</t>
+          <t>koperta; UPP; e-doręczenie; potwierdzenie odbioru; data doręczenia; awizo; przesyłka</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>dane rejestrowe spółki i zarządu</t>
+          <t>zawiera datę doręczenia pisma</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -38613,19 +38613,19 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Dokument tła. Pomaga ustalić status zarządu, ale nie jest dokumentem głównym.</t>
+          <t>Nigdy nie powinno być dokumentem głównym, ale jest kluczowe do obliczenia terminu.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>UMOWA_FAKTURA_KORESPONDENCJA</t>
+          <t>ODPIS_KRS</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Umowa, faktura lub korespondencja handlowa</t>
+          <t>Odpis KRS</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -38635,17 +38635,17 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>nieustalony</t>
+          <t>spółka</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>faktura; umowa; zamówienie; protokół; e-mail; nota księgowa; potwierdzenie przelewu</t>
+          <t>Krajowy Rejestr Sądowy; odpis aktualny; odpis pełny; reprezentacja; zarząd; wspólnicy</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>dokument gospodarczy, nie procesowy</t>
+          <t>dane rejestrowe spółki i zarządu</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -38660,24 +38660,24 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Dokument pomocniczy. Może mieć znaczenie w Audycie 48h, ale nie powinien być dokumentem głównym.</t>
+          <t>Dokument tła. Pomaga ustalić status zarządu, ale nie jest dokumentem głównym.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>DOKUMENT_NIEPRAWNY</t>
+          <t>UMOWA_FAKTURA_KORESPONDENCJA</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Dokument nieprawny albo obcy tematycznie</t>
+          <t>Umowa, faktura lub korespondencja handlowa</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>nieistotny</t>
+          <t>pomocniczy</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -38687,12 +38687,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>bilet; paragon; reklama; artykuł; notatka; dokument niezwiązany ze sprawą</t>
+          <t>faktura; umowa; zamówienie; protokół; e-mail; nota księgowa; potwierdzenie przelewu</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>brak cech dokumentu prawnego lub sprawy zarządu/spółki</t>
+          <t>dokument gospodarczy, nie procesowy</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -38705,148 +38705,195 @@
           <t>NIE</t>
         </is>
       </c>
-      <c r="I24" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Dokument pomocniczy. Może mieć znaczenie w Audycie 48h, ale nie powinien być dokumentem głównym.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>DOKUMENT_NIEPRAWNY</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Dokument nieprawny albo obcy tematycznie</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>nieistotny</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>nieustalony</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>bilet; paragon; reklama; artykuł; notatka; dokument niezwiązany ze sprawą</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>brak cech dokumentu prawnego lub sprawy zarządu/spółki</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nie dotyczy</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="I25" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="140.4499969482422" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t>DOKUMENT_NIECZYTELNY</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Dokument nieczytelny</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>techniczny</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>nieustalony</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>brak odczytu; OCR niepewny; tekst nieczytelny; skan bardzo słabej jakości</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>bardzo niska jakość odczytu</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>nieustalony</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>NIE</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Kalkulator powinien poprosić o lepszy skan albo umożliwić ręczne uzupełnienie danych.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="140.4499969482422" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>PISMO_PROCESOWE_SADOWE</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Pismo procesowe w toczącym się postępowaniu sądowym</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>sąd</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>członek zarządu / spółka</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>pismo przygotowawcze; odpowiedź na sprzeciw; w odpowiedzi na sprzeciw; replika; podtrzymuję; wnoszę o oddalenie; postępowanie w toku; sprawa w toku; dalsze pisma</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>pismo przygotowawcze; odpowiedź na sprzeciw; w odpowiedzi na sprzeciw</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>termin wskazany w wezwaniu sądu jeśli dotyczy</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>WARUNKOWO</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Dokument wskazuje na kontynuację sporu sądowego. Bez kompletnej dokumentacji (pozwu, sprzeciwu, wcześniejszych pism) rzetelna ocena jest niemożliwa. Jeżeli jest dokumentem głównym — przekierować do Audytu 48h z pełną dokumentacją.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Pismo z ZUS / urzędu dotyczące odpowiedzialności członka zarządu</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>organ publiczny</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>członek zarządu</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>ZUS; Zakład Ubezpieczeń Społecznych; urząd skarbowy; naczelnik urzędu skarbowego; odpowiedzialność osoby trzeciej; odpowiedzialność członka zarządu; zaległości składkowe; zaległości podatkowe; Ordynacja podatkowa; ustawa o systemie ubezpieczeń społecznych; wezwanie do wyjaśnień; zawiadomienie o wszczęciu postępowania; decyzja</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>organ publiczny informuje o wszczęciu postępowania albo wzywa członka zarządu do wyjaśnień w sprawie odpowiedzialności za zobowiązania spółki</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>termin wskazany w piśmie organu, często na złożenie wyjaśnień albo dokumentów</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>TAK</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Odrębna ścieżka od pozwu/nakazu. Nie generować sprzeciwu ani odpowiedzi na pozew; priorytetem są wyjaśnienia, dowody, okres pełnienia funkcji i przesłanki wyłączające odpowiedzialność.</t>
         </is>

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -35903,7 +35903,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Wybrać nakaz zapłaty — nakaz ma bezwzględnie wyższy priorytet niż pozew niezależnie od biegnącego terminu</t>
+          <t>Wybrać nakaz zapłaty — nakaz ma wyższy priorytet niż pozew niezależnie od biegnącego terminu, CHYBA ŻE nakaz dotyczy spółki, a pozew członka zarządu (sekwencja art. 299 KSH: po bezskutecznej egzekucji przeciwko spółce dokumentem wymagającym reakcji jest pozew przeciwko członkowi zarządu — nakaz jest wtedy prawomocnym dokumentem historycznym; zob. R10 w arkuszu 2). Sygnały sekwencji art. 299: w paczce jest wniosek egzekucyjny lub postanowienie o umorzeniu egzekucji, albo nakaz i pozew mają różnych pozwanych (spółka vs osoba fizyczna)</t>
         </is>
       </c>
     </row>

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -27997,22 +27997,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pozew w elektronicznym postepowaniu upominawczym (EPU) przeciwko czlonkowi zarzadu</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+          <t>Pozew w elektronicznym postępowaniu upominawczym (EPU) przeciwko członkowi zarządu</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>52</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dokument glowny - wysoki priorytet</t>
+          <t>Dokument główny — wysoki priorytet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jezeli sygnatura zawiera Nc-e albo wystepuje Sad Rejonowy Lublin-Zachod, dodaj flage EPU. Pozew jest wczesniejszym etapem niz nakaz - nie musi zawierac formuly nakazowej.</t>
+          <t>Jeżeli sygnatura zawiera „Nc-e" albo występuje Sąd Rejonowy Lublin-Zachód, dodaj flagę EPU. Pozew jest wcześniejszym etapem niż nakaz — nie musi zawierać formuły nakazowej.</t>
         </is>
       </c>
     </row>
@@ -28807,7 +28805,11 @@
           <t>Dokument obcy tematycznie</t>
         </is>
       </c>
-      <c r="C36" s="68" t="n"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Dokument nie jest dokumentem prawnym albo nie dotyczy odpowiedzialności zarządu/spółki</t>
+        </is>
+      </c>
       <c r="D36" s="5" t="n">
         <v>-100</v>
       </c>
@@ -29027,13 +29029,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B41:C41"/>
   </mergeCells>
@@ -35883,7 +35884,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oba dokumenty to nakazy tego samego rodzaju (EPU lub zwykły); jeden zawiera instrukcję terminu reakcji (np. "w ciągu dwóch tygodni"), drugi nie</t>
+          <t>Oba dokumenty to nakazy tego samego rodzaju (EPU lub zwykły), jeden zawiera instrukcję terminu reakcji (np. "w ciągu dwóch tygodni"), drugi nie</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -35903,7 +35904,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Wybrać nakaz zapłaty — nakaz ma wyższy priorytet niż pozew niezależnie od biegnącego terminu, CHYBA ŻE nakaz dotyczy spółki, a pozew członka zarządu (sekwencja art. 299 KSH: po bezskutecznej egzekucji przeciwko spółce dokumentem wymagającym reakcji jest pozew przeciwko członkowi zarządu — nakaz jest wtedy prawomocnym dokumentem historycznym; zob. R10 w arkuszu 2). Sygnały sekwencji art. 299: w paczce jest wniosek egzekucyjny lub postanowienie o umorzeniu egzekucji, albo nakaz i pozew mają różnych pozwanych (spółka vs osoba fizyczna)</t>
+          <t>Wybrać nakaz zapłaty — nakaz ma wyższy priorytet niż pozew niezależnie od biegnącego terminu, CHYBA ŻE nakaz dotyczy spółki, a pozew członka zarządu (sekwencja art. 299 KSH: po bezskutecznej egzekucji przeciwko spółce dokumentem wymagającym reakcji jest pozew przeciwko członkowi zarządu — nakaz jest wtedy prawomocnym dokumentem historycznym — zob. R10 w arkuszu 2). Sygnały sekwencji art. 299: w paczce jest wniosek egzekucyjny lub postanowienie o umorzeniu egzekucji, albo nakaz i pozew mają różnych pozwanych (spółka vs osoba fizyczna)</t>
         </is>
       </c>
     </row>
@@ -41673,7 +41674,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -38171,12 +38171,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>komornik sądowy; zajęcie; wezwanie; dłużnik; wierzyciel; egzekucja; opłata egzekucyjna</t>
+          <t>komornik sądowy; kancelaria komornicza; zajęcie; wezwanie; dłużnik; wierzyciel; egzekucja; opłata egzekucyjna; postępowanie egzekucyjne; tytuł wykonawczy; wykaz majątku</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>komornik kieruje pismo do osoby fizycznej/członka zarządu</t>
+          <t>zawiadomienie o wszczęciu postępowania egzekucyjnego; zajęciu rachunku bankowego; wezwanie do złożenia wykazu majątku; zajęcie wierzytelności</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -38218,12 +38218,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>komornik sądowy; egzekucja; dłużnik; wierzyciel; zajęcie; umorzenie; bezskuteczność</t>
+          <t>komornik sądowy; kancelaria komornicza; egzekucja; dłużnik; wierzyciel; zajęcie; umorzenie; bezskuteczność; postępowanie egzekucyjne; tytuł wykonawczy; zajęcie rachunku bankowego; wykaz majątku; zajęcie wierzytelności</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>egzekucja przeciwko spółce</t>
+          <t>egzekucja przeciwko spółce; zawiadomienie o wszczęciu postępowania egzekucyjnego; zajęciu rachunku bankowego; wezwanie do złożenia wykazu majątku</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -1518,7 +1518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W189"/>
+  <dimension ref="A1:W210"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="8.25" customWidth="1" style="4" min="1" max="1"/>
@@ -12427,7 +12427,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -21514,6 +21514,2265 @@
         </is>
       </c>
       <c r="W189" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>BASE_189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, 0–3 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_0_3</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: bardzo krótki czas pozostały na reakcję, wymagana ostrożna weryfikacja terminu</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało bardzo mało czasu na reakcję — około 0–3 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście — ale bezskuteczność egzekucji otwiera wierzycielowi drogę do roszczeń wobec członków zarządu (art. 299 KSH). Wymagana jest pilna weryfikacja stanu egzekucji i majątku spółki.</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BASE_190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, 0–3 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_0_3</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: bardzo krótki czas pozostały na reakcję, wymagana ostrożna weryfikacja terminu</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało bardzo mało czasu na reakcję — około 0–3 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się już postępowanie egzekucyjne na podstawie tytułu wykonawczego — to jeden z najbardziej zaawansowanych etapów sprawy. Jeżeli egzekucja z majątku spółki okaże się bezskuteczna, wierzyciel może następnie dochodzić zapłaty od członków zarządu (art. 299 KSH). Sprawa wymaga natychmiastowej weryfikacji dokumentów i terminów.</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, zakres egzekucji i możliwe kierunki reakcji — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S191" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>BASE_191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, 4–7 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_4_7</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: krótki czas pozostały na reakcję, termin należy potwierdzić z dokumentu i daty doręczenia</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało niewiele czasu na reakcję — około 4–7 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny. Warto zweryfikować stan egzekucji i majątku spółki — bezskuteczność egzekucji jest podstawową przesłanką późniejszej odpowiedzialności członków zarządu (art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>BASE_192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, 4–7 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_4_7</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: krótki czas pozostały na reakcję, termin należy potwierdzić z dokumentu i daty doręczenia</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało niewiele czasu na reakcję — około 4–7 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście — ale bezskuteczność egzekucji otwiera wierzycielowi drogę do roszczeń wobec członków zarządu (art. 299 KSH). Wymagana jest pilna weryfikacja stanu egzekucji i majątku spółki.</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>BASE_193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, 4–7 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_4_7</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: krótki czas pozostały na reakcję, termin należy potwierdzić z dokumentu i daty doręczenia</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało niewiele czasu na reakcję — około 4–7 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się już postępowanie egzekucyjne na podstawie tytułu wykonawczego — to jeden z najbardziej zaawansowanych etapów sprawy. Jeżeli egzekucja z majątku spółki okaże się bezskuteczna, wierzyciel może następnie dochodzić zapłaty od członków zarządu (art. 299 KSH). Sprawa wymaga natychmiastowej weryfikacji dokumentów i terminów.</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, zakres egzekucji i możliwe kierunki reakcji — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>BASE_194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, 8–14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny. Warto zweryfikować stan egzekucji i majątku spółki — bezskuteczność egzekucji jest podstawową przesłanką późniejszej odpowiedzialności członków zarządu (art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S195" t="n">
+        <v>0</v>
+      </c>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>BASE_195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, 8–14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście — ale bezskuteczność egzekucji otwiera wierzycielowi drogę do roszczeń wobec członków zarządu (art. 299 KSH). Wymagana jest pilna weryfikacja stanu egzekucji i majątku spółki.</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S196" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>BASE_196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, 8–14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się już postępowanie egzekucyjne na podstawie tytułu wykonawczego — to jeden z najbardziej zaawansowanych etapów sprawy. Jeżeli egzekucja z majątku spółki okaże się bezskuteczna, wierzyciel może następnie dochodzić zapłaty od członków zarządu (art. 299 KSH). Sprawa wymaga natychmiastowej weryfikacji dokumentów i terminów.</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, zakres egzekucji i możliwe kierunki reakcji — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S197" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>BASE_197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko / prewencja — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko / prewencja</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Niższe ryzyko / prewencja. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Pismo komornika dotyczy egzekucji z majątku spółki i na tym etapie jest oceniane jako niższe ryzyko osobiste. Warto jednak monitorować przebieg egzekucji — jeżeli okaże się bezskuteczna, wierzyciel może dochodzić zapłaty od członków zarządu (art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Warto uporządkować dokumenty i monitorować przebieg egzekucji. Audyt 48h może pomóc ocenić, czy sprawa nie zmierza w stronę odpowiedzialności osobistej członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S198" t="n">
+        <v>0</v>
+      </c>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>BASE_198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny. Warto zweryfikować stan egzekucji i majątku spółki — bezskuteczność egzekucji jest podstawową przesłanką późniejszej odpowiedzialności członków zarządu (art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S199" t="n">
+        <v>0</v>
+      </c>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>BASE_199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście — ale bezskuteczność egzekucji otwiera wierzycielowi drogę do roszczeń wobec członków zarządu (art. 299 KSH). Wymagana jest pilna weryfikacja stanu egzekucji i majątku spółki.</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S200" t="n">
+        <v>0</v>
+      </c>
+      <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>BASE_200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się już postępowanie egzekucyjne na podstawie tytułu wykonawczego — to jeden z najbardziej zaawansowanych etapów sprawy. Jeżeli egzekucja z majątku spółki okaże się bezskuteczna, wierzyciel może następnie dochodzić zapłaty od członków zarządu (art. 299 KSH). Sprawa wymaga natychmiastowej weryfikacji dokumentów i terminów.</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, zakres egzekucji i możliwe kierunki reakcji — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S201" t="n">
+        <v>0</v>
+      </c>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>BASE_201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>BAZOWY+REGUŁA_TWARDA</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, termin nieustalony, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>HR05</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: nieustalona, brak pewności co do terminu powinien zwiększać ostrożność oceny</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych nie udało się jednoznacznie ustalić, ile czasu pozostało na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny. Warto zweryfikować stan egzekucji i majątku spółki — bezskuteczność egzekucji jest podstawową przesłanką późniejszej odpowiedzialności członków zarządu (art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S202" t="n">
+        <v>0</v>
+      </c>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>BASE_202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>BAZOWY+REGUŁA_TWARDA</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, termin nieustalony, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>HR05</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: nieustalona, brak pewności co do terminu powinien zwiększać ostrożność oceny</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych nie udało się jednoznacznie ustalić, ile czasu pozostało na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście — ale bezskuteczność egzekucji otwiera wierzycielowi drogę do roszczeń wobec członków zarządu (art. 299 KSH). Wymagana jest pilna weryfikacja stanu egzekucji i majątku spółki.</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>BASE_203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>BAZOWY+REGUŁA_TWARDA</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, termin nieustalony, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>HR05</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: nieustalona, brak pewności co do terminu powinien zwiększać ostrożność oceny</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych nie udało się jednoznacznie ustalić, ile czasu pozostało na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się już postępowanie egzekucyjne na podstawie tytułu wykonawczego — to jeden z najbardziej zaawansowanych etapów sprawy. Jeżeli egzekucja z majątku spółki okaże się bezskuteczna, wierzyciel może następnie dochodzić zapłaty od członków zarządu (art. 299 KSH). Sprawa wymaga natychmiastowej weryfikacji dokumentów i terminów.</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, zakres egzekucji i możliwe kierunki reakcji — w tym ocenę ryzyka osobistego członków zarządu.</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S204" t="n">
+        <v>0</v>
+      </c>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>BASE_204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_CZLONEK_ZARZADU, 8–14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Pismo komornika skierowane do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że postępowanie egzekucyjne jest w toku na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny — kluczowa jest weryfikacja tytułu wykonawczego i zakresu egzekucji.</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, status KRS i możliwe kierunki dalszego działania.</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S205" t="n">
+        <v>0</v>
+      </c>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>BASE_205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_CZLONEK_ZARZADU, 8–14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Pismo komornika skierowane do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że postępowanie egzekucyjne jest w toku na podstawie tytułu wykonawczego. Twoje zasoby majątkowe mogą zostać zajęte — wymagana jest pilna weryfikacja.</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, status KRS i możliwe kierunki dalszego działania.</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S206" t="n">
+        <v>0</v>
+      </c>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>BASE_206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — PISMO_KOMORNIK_CZLONEK_ZARZADU, 8–14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Pismo komornika skierowane bezpośrednio do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że wierzyciel wszczął już egzekucję na podstawie tytułu wykonawczego. To jeden z najbardziej zaawansowanych etapów postępowania — wymagana jest natychmiastowa weryfikacja.</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, adresata pisma i możliwe kierunki reakcji.</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S207" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>BASE_207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_CZLONEK_ZARZADU, ponad 14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Pismo komornika skierowane do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że postępowanie egzekucyjne jest w toku na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny — kluczowa jest weryfikacja tytułu wykonawczego i zakresu egzekucji.</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, status KRS i możliwe kierunki dalszego działania.</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>BASE_208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_CZLONEK_ZARZADU, ponad 14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Pismo komornika skierowane do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że postępowanie egzekucyjne jest w toku na podstawie tytułu wykonawczego. Twoje zasoby majątkowe mogą zostać zajęte — wymagana jest pilna weryfikacja.</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, status KRS i możliwe kierunki dalszego działania.</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>BASE_209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — PISMO_KOMORNIK_CZLONEK_ZARZADU, ponad 14 dni, wstępna ocena bez dokumentów</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Pismo komornika skierowane bezpośrednio do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że wierzyciel wszczął już egzekucję na podstawie tytułu wykonawczego. To jeden z najbardziej zaawansowanych etapów postępowania — wymagana jest natychmiastowa weryfikacja.</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, adresata pisma i możliwe kierunki reakcji.</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
         <is>
           <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
         </is>
@@ -38914,7 +41173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="5.625" customWidth="1" style="4" min="1" max="1"/>
@@ -40683,6 +42942,100 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rodzaj pisma</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pismo komornicze (spółka)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Brak</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Nowa kategoria 05.07.2026: pismo komornika w egzekucji przeciwko spółce (zawiadomienie o wszczęciu egzekucji, zajęcie rachunku, wezwanie do wykazu majątku itp.). Egzekucja przeciwko spółce to przedpole odpowiedzialności z art. 299 KSH — jeżeli okaże się bezskuteczna, wierzyciel może dochodzić zapłaty od członków zarządu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rodzaj pisma</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pismo komornicze (członek zarządu)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Brak</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Nowa kategoria 05.07.2026: pismo komornika w egzekucji z majątku osobistego członka zarządu — najpóźniejszy etap sprawy, istnieje tytuł wykonawczy przeciwko osobie fizycznej. Jeden z najwyższych ciężarów gatunkowych.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
@@ -40697,7 +43050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" style="4" min="1" max="1"/>
@@ -41040,82 +43393,82 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_0_3</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>0–3 dni kalendarzowe</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>K2_urgency</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pismo komornicze (spółka)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>K1_document_weight</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pismo komornicze w egzekucji przeciwko spółce — zaawansowany etap sprawy i przedpole odpowiedzialności z art. 299 KSH, ale bez bezpośredniego roszczenia wobec członka zarządu (analogicznie do nakazu przeciwko spółce).</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pismo komornicze (członek zarządu)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>K1_document_weight</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Najwyższa pilność. Bardzo krótki czas na reakcję.</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n">
+      <c r="F12" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_4_7</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>4–7 dni kalendarzowych</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>K2_urgency</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Wysoka pilność. Jest jeszcze czas, ale sprawa wymaga szybkiego działania.</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Egzekucja z majątku osobistego członka zarządu na podstawie tytułu wykonawczego — jeden z najwyższych ciężarów gatunkowych.</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>8–14 dni kalendarzowych</t>
+          <t>0–3 dni kalendarzowe</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -41127,14 +43480,14 @@
         <v>0</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Umiarkowana pilność. Termin wymaga kontroli, ale nie jest jeszcze krytyczny.</t>
+          <t>Najwyższa pilność. Bardzo krótki czas na reakcję.</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -41144,12 +43497,12 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Ponad 14 dni kalendarzowych</t>
+          <t>4–7 dni kalendarzowych</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -41161,14 +43514,14 @@
         <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Niska pilność czasowa, choć ryzyko może wynikać z rodzaju dokumentu.</t>
+          <t>Wysoka pilność. Jest jeszcze czas, ale sprawa wymaga szybkiego działania.</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -41178,12 +43531,12 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem / nie udało się ustalić</t>
+          <t>8–14 dni kalendarzowych</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -41198,11 +43551,11 @@
         <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Brak wiedzy o terminie jest ryzykiem samym w sobie. Dlatego przyznajemy 1 punkt za pilność i 1 punkt za niepewność.</t>
+          <t>Umiarkowana pilność. Termin wymaga kontroli, ale nie jest jeszcze krytyczny.</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -41212,17 +43565,17 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>K2A_DELIVERY_DATE_KNOWN</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Tak, znam datę doręczenia</t>
+          <t>Ponad 14 dni kalendarzowych</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>K2A_auxiliary</t>
+          <t>K2_urgency</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
@@ -41236,7 +43589,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Dane pomocnicze. Nie punktować samodzielnie. Służy do obliczenia K2.</t>
+          <t>Niska pilność czasowa, choć ryzyko może wynikać z rodzaju dokumentu.</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -41246,31 +43599,31 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>K2A_DELIVERY_DATE_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Nie znam daty doręczenia</t>
+          <t>Nie wiem / nie udało się ustalić</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>K2A_auxiliary</t>
+          <t>K2_urgency</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Brak daty doręczenia zwiększa niepewność.</t>
+          <t>Brak wiedzy o terminie jest ryzykiem samym w sobie. Dlatego przyznajemy 1 punkt za pilność i 1 punkt za niepewność.</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -41280,17 +43633,17 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>K3_SUPPORT_BASIC_NO_DOCS</t>
+          <t>K2A_DELIVERY_DATE_KNOWN</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Tylko wstępna ocena bez wysyłki dokumentów</t>
+          <t>Tak, znam datę doręczenia</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>K3_support_needed</t>
+          <t>K2A_auxiliary</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
@@ -41300,11 +43653,11 @@
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Ocena bez pełnych dokumentów jest bardziej niepewna.</t>
+          <t>Dane pomocnicze. Nie punktować samodzielnie. Służy do obliczenia K2.</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -41314,17 +43667,17 @@
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>K3_SUPPORT_NOW_DOCS_LATER</t>
+          <t>K2A_DELIVERY_DATE_UNKNOWN</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Wstępna ocena teraz + dokumenty dosyłam później</t>
+          <t>Nie znam daty doręczenia</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>K3_support_needed</t>
+          <t>K2A_auxiliary</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -41338,7 +43691,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Częściowa gotowość do uporządkowania sprawy.</t>
+          <t>Brak daty doręczenia zwiększa niepewność.</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -41348,12 +43701,12 @@
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>K3_READY_FOR_AUDIT_48H</t>
+          <t>K3_SUPPORT_BASIC_NO_DOCS</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Jestem gotowy wysłać dokumenty i wejść w Audyt 48h</t>
+          <t>Tylko wstępna ocena bez wysyłki dokumentów</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -41368,11 +43721,11 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Najmniejsza niepewność organizacyjna, użytkownik jest gotowy do pełniejszej analizy.</t>
+          <t>Ocena bez pełnych dokumentów jest bardziej niepewna.</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -41382,17 +43735,17 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_ACTIVE</t>
+          <t>K3_SUPPORT_NOW_DOCS_LATER</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Nadal pełnię funkcję</t>
+          <t>Wstępna ocena teraz + dokumenty dosyłam później</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>K4_board_status</t>
+          <t>K3_support_needed</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -41406,7 +43759,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Nadal pełniona funkcja może wymagać uporządkowania sytuacji, ale sama w sobie nie oznacza najwyższego chaosu.</t>
+          <t>Częściowa gotowość do uporządkowania sprawy.</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -41416,17 +43769,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_RESIGNED</t>
+          <t>K3_READY_FOR_AUDIT_48H</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Była rezygnacja / odwołanie</t>
+          <t>Jestem gotowy wysłać dokumenty i wejść w Audyt 48h</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>K4_board_status</t>
+          <t>K3_support_needed</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -41436,11 +43789,11 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Rezygnacja/odwołanie wymaga sprawdzenia dat i wpisu w KRS.</t>
+          <t>Najmniejsza niepewność organizacyjna, użytkownik jest gotowy do pełniejszej analizy.</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -41450,12 +43803,12 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_UNKNOWN</t>
+          <t>K4_BOARD_ACTIVE</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem / trudno powiedzieć</t>
+          <t>Nadal pełnię funkcję</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -41470,11 +43823,11 @@
         <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Niepewność co do statusu w zarządzie istotnie zwiększa chaos informacyjny.</t>
+          <t>Nadal pełniona funkcja może wymagać uporządkowania sytuacji, ale sama w sobie nie oznacza najwyższego chaosu.</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -41484,17 +43837,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_UPDATED</t>
+          <t>K4_BOARD_RESIGNED</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Tak — wpis w KRS widnieje</t>
+          <t>Była rezygnacja / odwołanie</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>K5_krs_status</t>
+          <t>K4_board_status</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -41504,11 +43857,11 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Najniższa niepewność formalna w zakresie wpisu KRS.</t>
+          <t>Rezygnacja/odwołanie wymaga sprawdzenia dat i wpisu w KRS.</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -41518,17 +43871,17 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_NOT_UPDATED</t>
+          <t>K4_BOARD_UNKNOWN</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Nie — brak aktualnego wpisu w KRS</t>
+          <t>Nie wiem / trudno powiedzieć</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>K5_krs_status</t>
+          <t>K4_board_status</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -41542,7 +43895,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Brak aktualnego wpisu może zwiększać chaos formalny i ryzyko nieporozumień.</t>
+          <t>Niepewność co do statusu w zarządzie istotnie zwiększa chaos informacyjny.</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -41552,12 +43905,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_UNKNOWN</t>
+          <t>K5_KRS_UPDATED</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem</t>
+          <t>Tak — wpis w KRS widnieje</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -41572,11 +43925,11 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Brak wiedzy o wpisie w KRS wymaga weryfikacji.</t>
+          <t>Najniższa niepewność formalna w zakresie wpisu KRS.</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -41586,12 +43939,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>K5_NOT_APPLICABLE</t>
+          <t>K5_KRS_NOT_UPDATED</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Nie dotyczy</t>
+          <t>Nie — brak aktualnego wpisu w KRS</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -41606,11 +43959,11 @@
         <v>0</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Stosować automatycznie, gdy użytkownik nadal pełni funkcję.</t>
+          <t>Brak aktualnego wpisu może zwiększać chaos formalny i ryzyko nieporozumień.</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -41620,17 +43973,17 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_DEFENSE</t>
+          <t>K5_KRS_UNKNOWN</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Chcę ocenić, czy mam realne podstawy obrony</t>
+          <t>Nie wiem</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>K6_goal</t>
+          <t>K5_krs_status</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -41640,11 +43993,11 @@
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Cel dotyczy merytorycznej oceny podstaw obrony i możliwych zarzutów.</t>
+          <t>Brak wiedzy o wpisie w KRS wymaga weryfikacji.</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -41654,17 +44007,17 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_BUY_TIME</t>
+          <t>K5_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Chcę zyskać czas na przygotowanie obrony</t>
+          <t>Nie dotyczy</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>K6_goal</t>
+          <t>K5_krs_status</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -41678,7 +44031,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Cel wymaga bezpiecznego języka: tylko legalne środki procesowe i faktyczna dokumentacja.</t>
+          <t>Stosować automatycznie, gdy użytkownik nadal pełni funkcję.</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -41688,12 +44041,12 @@
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_PROCEDURAL_LETTER</t>
+          <t>K6_GOAL_DEFENSE</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Chcę przygotować odpowiednie pismo procesowe</t>
+          <t>Chcę ocenić, czy mam realne podstawy obrony</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -41712,7 +44065,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Cel praktyczny: dobór właściwego pisma zależnie od dokumentu.</t>
+          <t>Cel dotyczy merytorycznej oceny podstaw obrony i możliwych zarzutów.</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -41722,12 +44075,12 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_PLAN</t>
+          <t>K6_GOAL_BUY_TIME</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Potrzebuję planu działania i oceny szans</t>
+          <t>Chcę zyskać czas na przygotowanie obrony</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -41746,7 +44099,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Cel dotyczy planu kolejnych kroków oraz oceny szans po weryfikacji dokumentów.</t>
+          <t>Cel wymaga bezpiecznego języka: tylko legalne środki procesowe i faktyczna dokumentacja.</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -41756,12 +44109,12 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_UNKNOWN</t>
+          <t>K6_GOAL_PROCEDURAL_LETTER</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem — potrzebuję uporządkowania sytuacji</t>
+          <t>Chcę przygotować odpowiednie pismo procesowe</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -41776,11 +44129,11 @@
         <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Niepewność celu zwiększa potrzebę uporządkowania sprawy.</t>
+          <t>Cel praktyczny: dobór właściwego pisma zależnie od dokumentu.</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -41788,110 +44141,110 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>K6_GOAL_PLAN</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Potrzebuję planu działania i oceny szans</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>K6_goal</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Cel dotyczy planu kolejnych kroków oraz oceny szans po weryfikacji dokumentów.</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>K6_GOAL_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Nie wiem — potrzebuję uporządkowania sytuacji</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>K6_goal</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Niepewność celu zwiększa potrzebę uporządkowania sprawy.</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>Treść</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>K7_AMOUNT_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Nie wiem / nie widzę kwoty</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>K7_claim_amount</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>Brak kwoty ogranicza pewność oceny; dodać H=1 i W=1.</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>K7_AMOUNT_UP_TO_10K</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Do 10 000 zł</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>K7_claim_amount</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Niska kwota nie podnosi samodzielnie ciężaru sprawy.</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_10K_50K</t>
+          <t>K7_AMOUNT_UNKNOWN</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>10 001 – 50 000 zł</t>
+          <t>Nie wiem / nie widzę kwoty</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -41906,11 +44259,11 @@
         <v>0</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Kwota umiarkowana — niewielkie podniesienie ciężaru finansowego.</t>
+          <t>Brak kwoty ogranicza pewność oceny; dodać H=1 i W=1.</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -41920,12 +44273,12 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_50K_150K</t>
+          <t>K7_AMOUNT_UP_TO_10K</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>50 001 – 150 000 zł</t>
+          <t>Do 10 000 zł</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -41944,22 +44297,22 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Kwota istotna — podnosi ciężar sprawy.</t>
+          <t>Niska kwota nie podnosi samodzielnie ciężaru sprawy.</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_150K_500K</t>
+          <t>K7_AMOUNT_10K_50K</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>150 001 – 500 000 zł</t>
+          <t>10 001 – 50 000 zł</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -41978,22 +44331,22 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Wysoka kwota — istotne konsekwencje finansowe.</t>
+          <t>Kwota umiarkowana — niewielkie podniesienie ciężaru finansowego.</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_ABOVE_500K</t>
+          <t>K7_AMOUNT_50K_150K</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Powyżej 500 000 zł</t>
+          <t>50 001 – 150 000 zł</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -42012,62 +44365,94 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
+          <t>Kwota istotna — podnosi ciężar sprawy.</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>K7_AMOUNT_150K_500K</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>150 001 – 500 000 zł</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>K7_claim_amount</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Wysoka kwota — istotne konsekwencje finansowe.</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>K7_AMOUNT_ABOVE_500K</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Powyżej 500 000 zł</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>K7_claim_amount</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
           <t>Bardzo wysoka kwota — znacząco podnosi ciężar sprawy.</t>
         </is>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="H42" s="5" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="25" t="n"/>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="25" t="n"/>
-      <c r="D42" s="25" t="n"/>
-      <c r="E42" s="25" t="n"/>
-      <c r="F42" s="25" t="n"/>
-      <c r="G42" s="25" t="n"/>
-      <c r="H42" s="25" t="n"/>
-    </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>Treść</t>
-        </is>
-      </c>
-      <c r="C43" s="25" t="n"/>
-      <c r="D43" s="25" t="n"/>
-      <c r="E43" s="25" t="n"/>
-      <c r="F43" s="25" t="n"/>
-      <c r="G43" s="25" t="n"/>
-      <c r="H43" s="25" t="n"/>
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="11" t="n"/>
     </row>
     <row r="44" ht="45" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Zasada liczenia C</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>C liczymy z rodzaju dokumentu i jego ciężaru procesowego.</t>
-        </is>
-      </c>
+      <c r="A44" s="25" t="n"/>
+      <c r="B44" s="25" t="n"/>
       <c r="C44" s="25" t="n"/>
       <c r="D44" s="25" t="n"/>
       <c r="E44" s="25" t="n"/>
@@ -42076,14 +44461,14 @@
       <c r="H44" s="25" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Zasada liczenia P</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>P liczymy przede wszystkim z czasu na reakcję.</t>
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Treść</t>
         </is>
       </c>
       <c r="C45" s="25" t="n"/>
@@ -42096,12 +44481,12 @@
     <row r="46" ht="60" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Zasada liczenia H</t>
+          <t>Zasada liczenia C</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>H liczymy z niepewności danych, statusu zarządu/KRS i organizacyjnej gotowości.</t>
+          <t>C liczymy z rodzaju dokumentu i jego ciężaru procesowego.</t>
         </is>
       </c>
       <c r="C46" s="25" t="n"/>
@@ -42114,12 +44499,12 @@
     <row r="47" ht="90" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Zasada liczenia W</t>
+          <t>Zasada liczenia P</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>W liczymy z przedziału kwoty roszczenia; W wpływa na ciężar finansowy, ale nie zastępuje oceny terminu i dokumentu.</t>
+          <t>P liczymy przede wszystkim z czasu na reakcję.</t>
         </is>
       </c>
       <c r="C47" s="25" t="n"/>
@@ -42130,14 +44515,14 @@
       <c r="H47" s="25" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="22" t="inlineStr">
-        <is>
-          <t>Wynik końcowy</t>
-        </is>
-      </c>
-      <c r="B48" s="22" t="inlineStr">
-        <is>
-          <t>S = C + P + H + W.</t>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Zasada liczenia H</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>H liczymy z niepewności danych, statusu zarządu/KRS i organizacyjnej gotowości.</t>
         </is>
       </c>
       <c r="C48" s="25" t="n"/>
@@ -42148,14 +44533,50 @@
       <c r="H48" s="25" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="25" t="n"/>
-      <c r="B49" s="25" t="n"/>
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Zasada liczenia W</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>W liczymy z przedziału kwoty roszczenia; W wpływa na ciężar finansowy, ale nie zastępuje oceny terminu i dokumentu.</t>
+        </is>
+      </c>
       <c r="C49" s="25" t="n"/>
       <c r="D49" s="25" t="n"/>
       <c r="E49" s="25" t="n"/>
       <c r="F49" s="25" t="n"/>
       <c r="G49" s="25" t="n"/>
       <c r="H49" s="25" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>Wynik końcowy</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>S = C + P + H + W.</t>
+        </is>
+      </c>
+      <c r="C50" s="25" t="n"/>
+      <c r="D50" s="25" t="n"/>
+      <c r="E50" s="25" t="n"/>
+      <c r="F50" s="25" t="n"/>
+      <c r="G50" s="25" t="n"/>
+      <c r="H50" s="25" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="n"/>
+      <c r="B51" s="25" t="n"/>
+      <c r="C51" s="25" t="n"/>
+      <c r="D51" s="25" t="n"/>
+      <c r="E51" s="25" t="n"/>
+      <c r="F51" s="25" t="n"/>
+      <c r="G51" s="25" t="n"/>
+      <c r="H51" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -1518,7 +1518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W210"/>
+  <dimension ref="A1:W222"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="8.25" customWidth="1" style="4" min="1" max="1"/>
@@ -16232,7 +16232,7 @@
     <row r="139" ht="165" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BASE_138</t>
+          <t>BASE_141</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -16247,12 +16247,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych — wezwanie przedsądowe do członka zarządu, 8–14 dni, dokumenty później</t>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 0–3 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+          <t>WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -16262,57 +16262,57 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>RISK_MEDIUM</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych</t>
+          <t>Wysokie ryzyko</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>przedsądowe wezwanie do zapłaty skierowane do członka zarządu; sprawdzić podstawę roszczenia, termin wskazany przez wierzyciela i dokumenty potwierdzające wcześniejszą egzekucję przeciwko spółce; pilność: termin umiarkowanie krótki; nadal wymaga kontroli daty doręczenia i pouczenia</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_0_3; RISK_HIGH</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: wezwanie przedsadowe czlonek zarzadu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję. Użytkownik może uzupełnić dokumenty później, dlatego wynik należy traktować jako wstępny. Użytkownik wskazał, że nadal pełni funkcję w zarządzie.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 0–3 dni.</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Wezwanie przedsądowe skierowane do Ciebie jako byłego członka zarządu wymaga sprawdzenia podstawy roszczenia. Ryzyko jest umiarkowane — warto potwierdzić zasadność żądania i dostępne opcje odpowiedzi.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że sąd wymaga Twojej odpowiedzi lub stawiennictwa. Masz jeszcze czas na weryfikację, ale termin i zakres wymaganej reakcji muszą zostać ustalone natychmiast.</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Wezwanie przedsądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Wierzyciel domaga się zapłaty lub wyjaśnień przed złożeniem pozwu. Brak reakcji może przyspieszyć skierowanie sprawy do sądu. Kluczowe do ustalenia: termin wyznaczony przez wierzyciela, podstawa roszczenia (art. 299 KSH lub inna), zasadność żądania oraz możliwości odpowiedzi — zapłata, wyjaśnienia lub przygotowanie obrony.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, treść pouczenia, termin reakcji, adresata dokumentu, podstawę roszczenia, status członka zarządu oraz aktualność wpisu w KRS.</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Warto uporządkować dokumenty i potwierdzić podstawowe dane. Audyt 48h może pomóc zweryfikować, czy sprawa została prawidłowo oceniona.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
         </is>
       </c>
       <c r="S139" t="n">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>SCN_011</t>
+          <t>SCN_299</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -16337,7 +16337,7 @@
     <row r="140" ht="150" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BASE_139</t>
+          <t>BASE_142</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Niższe ryzyko / prewencja — wezwanie przedsądowe do członka zarządu, ponad 14 dni, gotowość do Audytu 48h</t>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, 0–3 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+          <t>WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -16367,57 +16367,57 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>RISK_LOW</t>
+          <t>RISK_URGENT</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Niższe ryzyko / prewencja</t>
+          <t>Sprawa pilna</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>przedsądowe wezwanie do zapłaty skierowane do członka zarządu; sprawdzić podstawę roszczenia, termin wskazany przez wierzyciela i dokumenty potwierdzające wcześniejszą egzekucję przeciwko spółce; pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_0_3; RISK_URGENT</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Niższe ryzyko / prewencja. Dokument wymagający reakcji: wezwanie przedsadowe czlonek zarzadu. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję. Użytkownik jest gotowy przekazać dokumenty do Audytu 48h, co pozwala szybko zweryfikować daty, terminy i treść pisma. Wskazano rezygnację lub odwołanie oraz aktualny wpis w KRS.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 0–3 dni.</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Wezwanie przedsądowe skierowane do Ciebie jako byłego członka zarządu jest na tym etapie oceniane jako niższe ryzyko. Warto jednak potwierdzić treść żądania i termin wyznaczony przez wierzyciela, aby nie przeoczyć koniecznych działań.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że postępowanie jest już w toku i sąd wymaga Twojego działania w ściśle określonym terminie. Brak reakcji może skutkować wyrokiem zaocznym lub utratą możliwości obrony.</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Wezwanie przedsądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Wierzyciel domaga się zapłaty lub wyjaśnień przed złożeniem pozwu. Brak reakcji może przyspieszyć skierowanie sprawy do sądu. Kluczowe do ustalenia: termin wyznaczony przez wierzyciela, podstawa roszczenia (art. 299 KSH lub inna), zasadność żądania oraz możliwości odpowiedzi — zapłata, wyjaśnienia lub przygotowanie obrony.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, treść pouczenia, termin reakcji, adresata dokumentu, podstawę roszczenia, status członka zarządu oraz aktualność wpisu w KRS.</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Warto uporządkować dokumenty i potwierdzić podstawowe dane. Audyt 48h może pomóc zweryfikować, czy sprawa została prawidłowo oceniona.</t>
+          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
         </is>
       </c>
       <c r="S140" t="n">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>SCN_012</t>
+          <t>SCN_300</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -16442,7 +16442,7 @@
     <row r="141" ht="210" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BASE_140</t>
+          <t>BASE_143</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -16452,17 +16452,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BAZOWY+REGUŁA_TWARDA</t>
+          <t>BAZOWY</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sprawa pilna — wezwanie przedsądowe do członka zarządu, termin nieustalony, wstępna ocena bez dokumentów</t>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+          <t>WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -16472,62 +16472,57 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>RISK_URGENT</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Sprawa pilna</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>HR05</t>
+          <t>Wysokie ryzyko</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>przedsądowe wezwanie do zapłaty skierowane do członka zarządu; sprawdzić podstawę roszczenia, termin wskazany przez wierzyciela i dokumenty potwierdzające wcześniejszą egzekucję przeciwko spółce; pilność: nieustalona; brak pewności co do terminu powinien zwiększać ostrożność oceny</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_4_7; RISK_HIGH</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: wezwanie przedsadowe czlonek zarzadu. Na podstawie podanych danych nie udało się jednoznacznie ustalić, ile czasu pozostało na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów. Status pełnienia funkcji w zarządzie wymaga doprecyzowania.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 4–7 dni.</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Wezwanie przedsądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że wierzyciel grozi złożeniem pozwu i wyznaczył krótki termin do zapłaty lub wyjaśnień. Brak reakcji może przyspieszyć skierowanie sprawy do sądu.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że sąd wymaga Twojej odpowiedzi lub stawiennictwa. Masz jeszcze czas na weryfikację, ale termin i zakres wymaganej reakcji muszą zostać ustalone natychmiast.</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Wezwanie przedsądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Wierzyciel domaga się zapłaty lub wyjaśnień przed złożeniem pozwu. Brak reakcji może przyspieszyć skierowanie sprawy do sądu. Kluczowe do ustalenia: termin wyznaczony przez wierzyciela, podstawa roszczenia (art. 299 KSH lub inna), zasadność żądania oraz możliwości odpowiedzi — zapłata, wyjaśnienia lub przygotowanie obrony.</t>
+          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, treść pouczenia, termin reakcji, adresata dokumentu, podstawę roszczenia, status członka zarządu oraz aktualność wpisu w KRS.</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, adresata pisma i możliwe kierunki reakcji.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
         </is>
       </c>
       <c r="S141" t="n">
@@ -16535,7 +16530,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>SCN_007</t>
+          <t>SCN_301</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -16552,7 +16547,7 @@
     <row r="142" ht="105" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BASE_141</t>
+          <t>BASE_144</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -16567,7 +16562,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 0–3 dni, EPU=NIE</t>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -16587,32 +16582,32 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_0_3</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>RISK_HIGH</t>
+          <t>RISK_MEDIUM</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko</t>
+          <t>Średnie ryzyko / braki danych</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_0_3; RISK_HIGH</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_4_7; RISK_MEDIUM</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 0–3 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 4–7 dni.</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że sąd wymaga Twojej odpowiedzi lub stawiennictwa. Masz jeszcze czas na weryfikację, ale termin i zakres wymaganej reakcji muszą zostać ustalone natychmiast.</t>
+          <t>Wezwanie sądowe skierowane do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści i terminu. Ryzyko jest umiarkowane, ale brak weryfikacji może spowodować utratę możliwości procesowego działania.</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -16627,7 +16622,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
+          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -16640,7 +16635,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>SCN_299</t>
+          <t>SCN_302</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -16657,7 +16652,7 @@
     <row r="143" ht="135" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BASE_142</t>
+          <t>BASE_145</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -16672,7 +16667,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, 0–3 dni, EPU=NIE</t>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -16692,7 +16687,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_0_3</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -16707,12 +16702,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_0_3; RISK_URGENT</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_4_7; RISK_URGENT</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 0–3 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 4–7 dni.</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -16745,7 +16740,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>SCN_300</t>
+          <t>SCN_303</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
@@ -16762,7 +16757,7 @@
     <row r="144" ht="105" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BASE_143</t>
+          <t>BASE_146</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -16777,7 +16772,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
+          <t>Wysokie ryzyko — wezwanie sądowe do członka zarządu, 8–14 dni, gotowość do Audytu 48h</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -16797,7 +16792,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -16812,12 +16807,12 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_4_7; RISK_HIGH</t>
+          <t>wezwanie sądowe skierowane do członka zarządu; sprawdzić, czego sąd żąda, jaki termin wskazano i czy pismo wymaga złożenia odpowiedzi albo stawiennictwa; pilność: termin umiarkowanie krótki; nadal wymaga kontroli daty doręczenia i pouczenia</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 4–7 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: wezwanie sądowe do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję. Użytkownik jest gotowy przekazać dokumenty do Audytu 48h, co pozwala szybko zweryfikować daty, terminy i treść pisma. Status pełnienia funkcji w zarządzie wymaga doprecyzowania.</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -16832,30 +16827,35 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto zweryfikować: datę doręczenia, treść pouczenia, termin reakcji, adresata dokumentu, podstawę roszczenia, status członka zarządu oraz aktualność wpisu w KRS.</t>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, status KRS i możliwe kierunki dalszego działania.</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
         </is>
       </c>
       <c r="S144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>SCN_301</t>
+          <t>SCN_210, SCN_212</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Scalono 2 dawnych wariantów K3–K6 do jednego scenariusza bazowego.</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
@@ -16867,7 +16867,7 @@
     <row r="145" ht="120" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BASE_144</t>
+          <t>BASE_147</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 8–14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_4_7; RISK_MEDIUM</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_8_14; RISK_MEDIUM</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 4–7 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 8–14 dni.</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>SCN_302</t>
+          <t>SCN_304</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
@@ -16972,7 +16972,7 @@
     <row r="146" ht="135" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BASE_145</t>
+          <t>BASE_148</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, 4–7 dni, EPU=NIE</t>
+          <t>Sprawa pilna — wezwanie sądowe do członka zarządu, 8–14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -17022,12 +17022,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_4_7; RISK_URGENT</t>
+          <t>wezwanie sądowe skierowane do członka zarządu; sprawdzić, czego sąd żąda, jaki termin wskazano i czy pismo wymaga złożenia odpowiedzi albo stawiennictwa; pilność: termin umiarkowanie krótki; nadal wymaga kontroli daty doręczenia i pouczenia</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 4–7 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: wezwanie sądowe do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów. Status pełnienia funkcji w zarządzie wymaga doprecyzowania.</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -17042,30 +17042,35 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto zweryfikować: datę doręczenia, treść pouczenia, termin reakcji, adresata dokumentu, podstawę roszczenia, status członka zarządu oraz aktualność wpisu w KRS.</t>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
+          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, adresata pisma i możliwe kierunki reakcji.</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
         </is>
       </c>
       <c r="S146" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>SCN_303</t>
+          <t>SCN_204, SCN_205, SCN_206, SCN_207, SCN_208, SCN_209, SCN_211</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Scalono 7 dawnych wariantów K3–K6 do jednego scenariusza bazowego.</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
@@ -17077,7 +17082,7 @@
     <row r="147" ht="150" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BASE_146</t>
+          <t>BASE_149</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -17092,7 +17097,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — wezwanie sądowe do członka zarządu, 8–14 dni, gotowość do Audytu 48h</t>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -17112,7 +17117,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -17127,12 +17132,12 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>wezwanie sądowe skierowane do członka zarządu; sprawdzić, czego sąd żąda, jaki termin wskazano i czy pismo wymaga złożenia odpowiedzi albo stawiennictwa; pilność: termin umiarkowanie krótki; nadal wymaga kontroli daty doręczenia i pouczenia</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_HIGH</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: wezwanie sądowe do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję. Użytkownik jest gotowy przekazać dokumenty do Audytu 48h, co pozwala szybko zweryfikować daty, terminy i treść pisma. Status pełnienia funkcji w zarządzie wymaga doprecyzowania.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: ponad 14 dni.</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -17147,35 +17152,30 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, treść pouczenia, termin reakcji, adresata dokumentu, podstawę roszczenia, status członka zarządu oraz aktualność wpisu w KRS.</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, status KRS i możliwe kierunki dalszego działania.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
         </is>
       </c>
       <c r="S147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>SCN_210, SCN_212</t>
+          <t>SCN_305</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>Scalono 2 dawnych wariantów K3–K6 do jednego scenariusza bazowego.</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
@@ -17187,7 +17187,7 @@
     <row r="148" ht="120" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BASE_147</t>
+          <t>BASE_150</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, 8–14 dni, EPU=NIE</t>
+          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -17222,32 +17222,32 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>RISK_MEDIUM</t>
+          <t>RISK_LOW</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych</t>
+          <t>Niższe ryzyko / prewencja</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_8_14; RISK_MEDIUM</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_LOW</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: 8–14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Niższe ryzyko / prewencja. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: ponad 14 dni.</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe skierowane do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści i terminu. Ryzyko jest umiarkowane, ale brak weryfikacji może spowodować utratę możliwości procesowego działania.</t>
+          <t>Wezwanie sądowe skierowane do Ciebie jako byłego członka zarządu jest na tym etapie oceniane jako niższe ryzyko. Warto jednak potwierdzić treść wezwania i termin, aby nie przeoczyć wymaganych działań.</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
+          <t>Warto zachować dokumenty i potwierdzić podstawowe informacje, a w razie wątpliwości skorzystać z Audytu 48h.</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>SCN_304</t>
+          <t>SCN_306</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
@@ -17292,7 +17292,7 @@
     <row r="149" ht="135" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BASE_148</t>
+          <t>BASE_151</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Sprawa pilna — wezwanie sądowe do członka zarządu, 8–14 dni, wstępna ocena bez dokumentów</t>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -17327,32 +17327,32 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>RISK_URGENT</t>
+          <t>RISK_MEDIUM</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Sprawa pilna</t>
+          <t>Średnie ryzyko / braki danych</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>wezwanie sądowe skierowane do członka zarządu; sprawdzić, czego sąd żąda, jaki termin wskazano i czy pismo wymaga złożenia odpowiedzi albo stawiennictwa; pilność: termin umiarkowanie krótki; nadal wymaga kontroli daty doręczenia i pouczenia</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_MEDIUM</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: wezwanie sądowe do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów. Status pełnienia funkcji w zarządzie wymaga doprecyzowania.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: ponad 14 dni.</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że postępowanie jest już w toku i sąd wymaga Twojego działania w ściśle określonym terminie. Brak reakcji może skutkować wyrokiem zaocznym lub utratą możliwości obrony.</t>
+          <t>Wezwanie sądowe skierowane do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści i terminu. Ryzyko jest umiarkowane, ale brak weryfikacji może spowodować utratę możliwości procesowego działania.</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -17362,35 +17362,30 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, treść pouczenia, termin reakcji, adresata dokumentu, podstawę roszczenia, status członka zarządu oraz aktualność wpisu w KRS.</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, adresata pisma i możliwe kierunki reakcji.</t>
+          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
         </is>
       </c>
       <c r="S149" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>SCN_204, SCN_205, SCN_206, SCN_207, SCN_208, SCN_209, SCN_211</t>
+          <t>SCN_307</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
-        </is>
-      </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>Scalono 7 dawnych wariantów K3–K6 do jednego scenariusza bazowego.</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -17402,7 +17397,7 @@
     <row r="150" ht="105" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BASE_149</t>
+          <t>BASE_152</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -17417,7 +17412,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -17442,27 +17437,27 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>RISK_HIGH</t>
+          <t>RISK_URGENT</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko</t>
+          <t>Sprawa pilna</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_HIGH</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_URGENT</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: ponad 14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: ponad 14 dni.</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że sąd wymaga Twojej odpowiedzi lub stawiennictwa. Masz jeszcze czas na weryfikację, ale termin i zakres wymaganej reakcji muszą zostać ustalone natychmiast.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że postępowanie jest już w toku i sąd wymaga Twojego działania w ściśle określonym terminie. Brak reakcji może skutkować wyrokiem zaocznym lub utratą możliwości obrony.</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -17477,7 +17472,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
+          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -17490,7 +17485,7 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>SCN_305</t>
+          <t>SCN_308</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
@@ -17507,7 +17502,7 @@
     <row r="151" ht="105" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BASE_150</t>
+          <t>BASE_153</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -17522,7 +17517,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -17542,32 +17537,32 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>RISK_LOW</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Niższe ryzyko / prewencja</t>
+          <t>Wysokie ryzyko</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_LOW</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_UNKNOWN; RISK_HIGH</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Niższe ryzyko / prewencja. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: ponad 14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: termin nieustalony.</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe skierowane do Ciebie jako byłego członka zarządu jest na tym etapie oceniane jako niższe ryzyko. Warto jednak potwierdzić treść wezwania i termin, aby nie przeoczyć wymaganych działań.</t>
+          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że sąd wymaga Twojej odpowiedzi lub stawiennictwa. Masz jeszcze czas na weryfikację, ale termin i zakres wymaganej reakcji muszą zostać ustalone natychmiast.</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -17582,7 +17577,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>Warto zachować dokumenty i potwierdzić podstawowe informacje, a w razie wątpliwości skorzystać z Audytu 48h.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -17595,7 +17590,7 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>SCN_306</t>
+          <t>SCN_309</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -17612,7 +17607,7 @@
     <row r="152" ht="120" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BASE_151</t>
+          <t>BASE_154</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -17627,7 +17622,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -17647,7 +17642,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -17662,12 +17657,12 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_MEDIUM</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_UNKNOWN; RISK_MEDIUM</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: ponad 14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: termin nieustalony.</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -17700,7 +17695,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>SCN_307</t>
+          <t>SCN_310</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -17717,7 +17712,7 @@
     <row r="153" ht="135" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BASE_152</t>
+          <t>BASE_155</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -17732,7 +17727,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, ponad 14 dni, EPU=NIE</t>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -17752,7 +17747,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -17767,12 +17762,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_URGENT</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_UNKNOWN; RISK_URGENT</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: ponad 14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: termin nieustalony.</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -17805,7 +17800,7 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>SCN_308</t>
+          <t>SCN_311</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
@@ -17822,7 +17817,7 @@
     <row r="154" ht="105" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BASE_153</t>
+          <t>BASE_156</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -17837,12 +17832,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -17852,12 +17847,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -17872,22 +17867,22 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_UNKNOWN; RISK_HIGH</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_0_3; RISK_HIGH</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: termin nieustalony.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 0–3 dni.</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że sąd wymaga Twojej odpowiedzi lub stawiennictwa. Masz jeszcze czas na weryfikację, ale termin i zakres wymaganej reakcji muszą zostać ustalone natychmiast.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest istotne z Twojej perspektywy jako byłego członka zarządu — jeśli spółka przegra sprawę lub nie zareaguje, wierzyciel może dochodzić roszczeń bezpośrednio od Ciebie z art. 299 KSH. Masz jeszcze czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -17910,7 +17905,7 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>SCN_309</t>
+          <t>SCN_312</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
@@ -17927,7 +17922,7 @@
     <row r="155" ht="120" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BASE_154</t>
+          <t>BASE_157</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -17942,12 +17937,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -17957,12 +17952,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -17977,22 +17972,22 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_UNKNOWN; RISK_MEDIUM</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_0_3; RISK_MEDIUM</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: termin nieustalony.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 0–3 dni.</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe skierowane do Ciebie jako byłego członka zarządu wymaga sprawdzenia treści i terminu. Ryzyko jest umiarkowane, ale brak weryfikacji może spowodować utratę możliwości procesowego działania.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga sprawdzenia, czy spółka podjęła już działania. Brak reakcji spółki może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -18015,7 +18010,7 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>SCN_310</t>
+          <t>SCN_313</t>
         </is>
       </c>
       <c r="U155" t="inlineStr">
@@ -18032,7 +18027,7 @@
     <row r="156" ht="135" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BASE_155</t>
+          <t>BASE_158</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -18047,12 +18042,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe do członka zarządu, termin nieustalony, EPU=NIE</t>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
+          <t>WEZWANIE_SADOWE_SPOLKA</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -18062,12 +18057,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -18082,22 +18077,22 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_UNKNOWN; RISK_URGENT</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_0_3; RISK_URGENT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe do członka zarządu. Szacowany czas na reakcję: termin nieustalony.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 0–3 dni.</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe skierowane bezpośrednio do Ciebie jako byłego członka zarządu oznacza, że postępowanie jest już w toku i sąd wymaga Twojego działania w ściśle określonym terminie. Brak reakcji może skutkować wyrokiem zaocznym lub utratą możliwości obrony.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga pilnej reakcji — jeśli spółka nie odpowie w terminie, sąd może wydać wyrok zaoczny. Po bezskutecznej egzekucji wobec spółki wierzyciel może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe jest skierowane bezpośrednio do Ciebie jako byłego członka zarządu. Kluczowe jest ustalenie czego dokładnie sąd wymaga: stawiennictwa na rozprawie, złożenia pisma procesowego, dostarczenia dokumentów czy złożenia wyjaśnień. Termin wskazany w wezwaniu jest ściśle określony przez sąd i nie podlega automatycznemu przedłużeniu — brak reakcji może skutkować wyrokiem zaocznym lub ograniczeniem możliwości obrony.</t>
+          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -18120,7 +18115,7 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>SCN_311</t>
+          <t>SCN_314</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -18137,7 +18132,7 @@
     <row r="157" ht="105" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BASE_156</t>
+          <t>BASE_159</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -18152,7 +18147,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -18172,7 +18167,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_0_3</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -18187,12 +18182,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_0_3; RISK_HIGH</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_4_7; RISK_HIGH</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 0–3 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 4–7 dni.</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -18225,7 +18220,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>SCN_312</t>
+          <t>SCN_315</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -18242,7 +18237,7 @@
     <row r="158" ht="120" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BASE_157</t>
+          <t>BASE_160</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -18257,7 +18252,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -18277,7 +18272,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_0_3</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -18292,12 +18287,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_0_3; RISK_MEDIUM</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_4_7; RISK_MEDIUM</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 0–3 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 4–7 dni.</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -18330,7 +18325,7 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>SCN_313</t>
+          <t>SCN_316</t>
         </is>
       </c>
       <c r="U158" t="inlineStr">
@@ -18347,7 +18342,7 @@
     <row r="159" ht="135" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BASE_158</t>
+          <t>BASE_161</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -18362,7 +18357,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 0–3 dni, EPU=NIE</t>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -18382,7 +18377,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_0_3</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -18397,12 +18392,12 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_0_3; RISK_URGENT</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_4_7; RISK_URGENT</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 0–3 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 4–7 dni.</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -18435,7 +18430,7 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>SCN_314</t>
+          <t>SCN_317</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
@@ -18452,7 +18447,7 @@
     <row r="160" ht="105" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BASE_159</t>
+          <t>BASE_162</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -18467,7 +18462,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -18487,7 +18482,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -18502,12 +18497,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_4_7; RISK_HIGH</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_8_14; RISK_HIGH</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 4–7 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 8–14 dni.</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -18540,7 +18535,7 @@
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>SCN_315</t>
+          <t>SCN_318</t>
         </is>
       </c>
       <c r="U160" t="inlineStr">
@@ -18557,7 +18552,7 @@
     <row r="161" ht="120" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BASE_160</t>
+          <t>BASE_163</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -18572,7 +18567,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
+          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -18592,32 +18587,32 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>RISK_MEDIUM</t>
+          <t>RISK_LOW</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych</t>
+          <t>Niższe ryzyko / prewencja</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_4_7; RISK_MEDIUM</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_8_14; RISK_LOW</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 4–7 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Niższe ryzyko / prewencja. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 8–14 dni.</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe dotyczące spółki wymaga sprawdzenia, czy spółka podjęła już działania. Brak reakcji spółki może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla byłego członka zarządu.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest na tym etapie oceniane jako niższe ryzyko bezpośrednie. Warto jednak sprawdzić, czy spółka jest aktywnie reprezentowana w postępowaniu — brak reakcji mógłby doprowadzić do wyroku zaocznego.</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -18632,7 +18627,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
+          <t>Warto zachować dokumenty i potwierdzić podstawowe informacje, a w razie wątpliwości skorzystać z Audytu 48h.</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -18645,7 +18640,7 @@
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>SCN_316</t>
+          <t>SCN_319</t>
         </is>
       </c>
       <c r="U161" t="inlineStr">
@@ -18662,7 +18657,7 @@
     <row r="162" ht="135" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BASE_161</t>
+          <t>BASE_164</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -18677,7 +18672,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 4–7 dni, EPU=NIE</t>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -18697,32 +18692,32 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>RISK_URGENT</t>
+          <t>RISK_MEDIUM</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Sprawa pilna</t>
+          <t>Średnie ryzyko / braki danych</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_4_7; RISK_URGENT</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_8_14; RISK_MEDIUM</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 4–7 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 8–14 dni.</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe dotyczące spółki wymaga pilnej reakcji — jeśli spółka nie odpowie w terminie, sąd może wydać wyrok zaoczny. Po bezskutecznej egzekucji wobec spółki wierzyciel może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga sprawdzenia, czy spółka podjęła już działania. Brak reakcji spółki może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -18737,7 +18732,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
+          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -18750,7 +18745,7 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>SCN_317</t>
+          <t>SCN_320</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
@@ -18767,7 +18762,7 @@
     <row r="163" ht="105" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BASE_162</t>
+          <t>BASE_165</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -18782,7 +18777,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -18807,27 +18802,27 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>RISK_HIGH</t>
+          <t>RISK_URGENT</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko</t>
+          <t>Sprawa pilna</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_8_14; RISK_HIGH</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_8_14; RISK_URGENT</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 8–14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 8–14 dni.</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe dotyczące spółki jest istotne z Twojej perspektywy jako byłego członka zarządu — jeśli spółka przegra sprawę lub nie zareaguje, wierzyciel może dochodzić roszczeń bezpośrednio od Ciebie z art. 299 KSH. Masz jeszcze czas na weryfikację, ale działanie jest potrzebne.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga pilnej reakcji — jeśli spółka nie odpowie w terminie, sąd może wydać wyrok zaoczny. Po bezskutecznej egzekucji wobec spółki wierzyciel może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -18842,7 +18837,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
+          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -18855,7 +18850,7 @@
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t>SCN_318</t>
+          <t>SCN_321</t>
         </is>
       </c>
       <c r="U163" t="inlineStr">
@@ -18872,7 +18867,7 @@
     <row r="164" ht="105" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BASE_163</t>
+          <t>BASE_166</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -18887,7 +18882,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -18907,32 +18902,32 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>RISK_LOW</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Niższe ryzyko / prewencja</t>
+          <t>Wysokie ryzyko</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_8_14; RISK_LOW</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_ABOVE_14; RISK_HIGH</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Niższe ryzyko / prewencja. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 8–14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: ponad 14 dni.</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe dotyczące spółki jest na tym etapie oceniane jako niższe ryzyko bezpośrednie. Warto jednak sprawdzić, czy spółka jest aktywnie reprezentowana w postępowaniu — brak reakcji mógłby doprowadzić do wyroku zaocznego.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest istotne z Twojej perspektywy jako byłego członka zarządu — jeśli spółka przegra sprawę lub nie zareaguje, wierzyciel może dochodzić roszczeń bezpośrednio od Ciebie z art. 299 KSH. Masz jeszcze czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -18947,7 +18942,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>Warto zachować dokumenty i potwierdzić podstawowe informacje, a w razie wątpliwości skorzystać z Audytu 48h.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -18960,7 +18955,7 @@
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>SCN_319</t>
+          <t>SCN_322</t>
         </is>
       </c>
       <c r="U164" t="inlineStr">
@@ -18977,7 +18972,7 @@
     <row r="165" ht="120" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BASE_164</t>
+          <t>BASE_167</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -18992,7 +18987,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
+          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -19012,32 +19007,32 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>RISK_MEDIUM</t>
+          <t>RISK_LOW</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych</t>
+          <t>Niższe ryzyko / prewencja</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_8_14; RISK_MEDIUM</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_ABOVE_14; RISK_LOW</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 8–14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Niższe ryzyko / prewencja. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: ponad 14 dni.</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe dotyczące spółki wymaga sprawdzenia, czy spółka podjęła już działania. Brak reakcji spółki może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla byłego członka zarządu.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest na tym etapie oceniane jako niższe ryzyko bezpośrednie. Warto jednak sprawdzić, czy spółka jest aktywnie reprezentowana w postępowaniu — brak reakcji mógłby doprowadzić do wyroku zaocznego.</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -19052,7 +19047,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
+          <t>Warto zachować dokumenty i potwierdzić podstawowe informacje, a w razie wątpliwości skorzystać z Audytu 48h.</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -19065,7 +19060,7 @@
       </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>SCN_320</t>
+          <t>SCN_323</t>
         </is>
       </c>
       <c r="U165" t="inlineStr">
@@ -19082,7 +19077,7 @@
     <row r="166" ht="135" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BASE_165</t>
+          <t>BASE_168</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -19097,7 +19092,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, 8–14 dni, EPU=NIE</t>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -19117,32 +19112,32 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>RISK_URGENT</t>
+          <t>RISK_MEDIUM</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Sprawa pilna</t>
+          <t>Średnie ryzyko / braki danych</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_8_14; RISK_URGENT</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_ABOVE_14; RISK_MEDIUM</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: 8–14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: ponad 14 dni.</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe dotyczące spółki wymaga pilnej reakcji — jeśli spółka nie odpowie w terminie, sąd może wydać wyrok zaoczny. Po bezskutecznej egzekucji wobec spółki wierzyciel może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga sprawdzenia, czy spółka podjęła już działania. Brak reakcji spółki może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla byłego członka zarządu.</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -19157,7 +19152,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
+          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -19170,7 +19165,7 @@
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>SCN_321</t>
+          <t>SCN_324</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
@@ -19187,7 +19182,7 @@
     <row r="167" ht="105" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BASE_166</t>
+          <t>BASE_169</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -19202,7 +19197,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -19227,27 +19222,27 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>RISK_HIGH</t>
+          <t>RISK_URGENT</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko</t>
+          <t>Sprawa pilna</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_ABOVE_14; RISK_HIGH</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_ABOVE_14; RISK_URGENT</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: ponad 14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: ponad 14 dni.</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe dotyczące spółki jest istotne z Twojej perspektywy jako byłego członka zarządu — jeśli spółka przegra sprawę lub nie zareaguje, wierzyciel może dochodzić roszczeń bezpośrednio od Ciebie z art. 299 KSH. Masz jeszcze czas na weryfikację, ale działanie jest potrzebne.</t>
+          <t>Wezwanie sądowe dotyczące spółki wymaga pilnej reakcji — jeśli spółka nie odpowie w terminie, sąd może wydać wyrok zaoczny. Po bezskutecznej egzekucji wobec spółki wierzyciel może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH.</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -19262,7 +19257,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
+          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -19275,7 +19270,7 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>SCN_322</t>
+          <t>SCN_325</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
@@ -19292,7 +19287,7 @@
     <row r="168" ht="105" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BASE_167</t>
+          <t>BASE_170</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -19307,7 +19302,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Niższe ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
+          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -19327,32 +19322,32 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>RISK_LOW</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Niższe ryzyko / prewencja</t>
+          <t>Wysokie ryzyko</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_ABOVE_14; RISK_LOW</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_UNKNOWN; RISK_HIGH</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Niższe ryzyko / prewencja. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: ponad 14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: termin nieustalony.</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe dotyczące spółki jest na tym etapie oceniane jako niższe ryzyko bezpośrednie. Warto jednak sprawdzić, czy spółka jest aktywnie reprezentowana w postępowaniu — brak reakcji mógłby doprowadzić do wyroku zaocznego.</t>
+          <t>Wezwanie sądowe dotyczące spółki jest istotne z Twojej perspektywy jako byłego członka zarządu — jeśli spółka przegra sprawę lub nie zareaguje, wierzyciel może dochodzić roszczeń bezpośrednio od Ciebie z art. 299 KSH. Masz jeszcze czas na weryfikację, ale działanie jest potrzebne.</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -19367,7 +19362,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>Warto zachować dokumenty i potwierdzić podstawowe informacje, a w razie wątpliwości skorzystać z Audytu 48h.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -19380,7 +19375,7 @@
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>SCN_323</t>
+          <t>SCN_326</t>
         </is>
       </c>
       <c r="U168" t="inlineStr">
@@ -19397,7 +19392,7 @@
     <row r="169" ht="120" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BASE_168</t>
+          <t>BASE_171</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -19412,7 +19407,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
+          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -19432,7 +19427,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -19447,12 +19442,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_ABOVE_14; RISK_MEDIUM</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_UNKNOWN; RISK_MEDIUM</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: ponad 14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: termin nieustalony.</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -19485,7 +19480,7 @@
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>SCN_324</t>
+          <t>SCN_327</t>
         </is>
       </c>
       <c r="U169" t="inlineStr">
@@ -19502,7 +19497,7 @@
     <row r="170" ht="135" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BASE_169</t>
+          <t>BASE_172</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -19517,7 +19512,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, ponad 14 dni, EPU=NIE</t>
+          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -19537,7 +19532,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -19552,12 +19547,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_ABOVE_14; RISK_URGENT</t>
+          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_UNKNOWN; RISK_URGENT</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: ponad 14 dni.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: termin nieustalony.</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -19590,7 +19585,7 @@
       </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>SCN_325</t>
+          <t>SCN_328</t>
         </is>
       </c>
       <c r="U170" t="inlineStr">
@@ -19607,7 +19602,7 @@
     <row r="171" ht="105" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>BASE_170</t>
+          <t>BASE_173</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -19622,12 +19617,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
+          <t>Sprawa pilna — pismo organu publicznego ZUS/US, 0-3</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -19637,70 +19632,65 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>RISK_HIGH</t>
+          <t>RISK_URGENT</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko</t>
+          <t>Sprawa pilna</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_UNKNOWN; RISK_HIGH</t>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: termin nieustalony.</t>
+          <t>Pismo z ZUS / urzędu — pilna reakcja wymagana.</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe dotyczące spółki jest istotne z Twojej perspektywy jako byłego członka zarządu — jeśli spółka przegra sprawę lub nie zareaguje, wierzyciel może dochodzić roszczeń bezpośrednio od Ciebie z art. 299 KSH. Masz jeszcze czas na weryfikację, ale działanie jest potrzebne.</t>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga pilnej reakcji. Termin na złożenie wyjaśnień lub odwołania jest ściśle określony w pouczeniu — jego przekroczenie może zamknąć drogę do obrony.</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto zweryfikować: datę doręczenia, treść pouczenia, termin reakcji, adresata dokumentu, podstawę roszczenia, status członka zarządu oraz aktualność wpisu w KRS.</t>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
+          <t>Ze względu na krótki termin warto jak najszybciej przejść do Audytu 48h, aby ustalić termin, zakres żądania i właściwy tryb odpowiedzi na pismo organu.</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
         </is>
       </c>
       <c r="S171" t="n">
         <v>1</v>
       </c>
-      <c r="T171" t="inlineStr">
-        <is>
-          <t>SCN_326</t>
-        </is>
-      </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>OK_DO_TESTÓW</t>
+          <t>ZATWIERDZONA</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
@@ -19712,7 +19702,7 @@
     <row r="172" ht="120" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>BASE_171</t>
+          <t>BASE_174</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -19727,12 +19717,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Średnie ryzyko — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
+          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, 0-3</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -19742,70 +19732,65 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>RISK_MEDIUM</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych</t>
+          <t>Wysokie ryzyko</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_UNKNOWN; RISK_MEDIUM</t>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: termin nieustalony.</t>
+          <t>Pismo z ZUS / urzędu — szybka weryfikacja i odpowiedź.</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe dotyczące spółki wymaga sprawdzenia, czy spółka podjęła już działania. Brak reakcji spółki może w przyszłości przełożyć się na ryzyko z art. 299 KSH dla byłego członka zarządu.</t>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga przygotowanej odpowiedzi. Właściwą formą jest złożenie wyjaśnień i dokumentów — nie sprzeciw ani pismo do sądu. Czas na reakcję jest ograniczony.</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto zweryfikować: datę doręczenia, treść pouczenia, termin reakcji, adresata dokumentu, podstawę roszczenia, status członka zarządu oraz aktualność wpisu w KRS.</t>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
+          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma, termin i możliwe kierunki odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
         </is>
       </c>
       <c r="S172" t="n">
         <v>1</v>
       </c>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t>SCN_327</t>
-        </is>
-      </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>OK_DO_TESTÓW</t>
+          <t>ZATWIERDZONA</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
@@ -19817,7 +19802,7 @@
     <row r="173" ht="135" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BASE_172</t>
+          <t>BASE_175</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -19832,12 +19817,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Sprawa pilna — scenariusz bazowy: wezwanie sądowe dotyczące spółki, termin nieustalony, EPU=NIE</t>
+          <t>Sprawa pilna — pismo organu publicznego ZUS/US, 4-7</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>WEZWANIE_SADOWE_SPOLKA</t>
+          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -19847,12 +19832,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -19867,50 +19852,45 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>scenariusz bazowy; WEZWANIE_SADOWE_SPOLKA; EPU=NIE; K1_WEZWANIE_SADOWE_SPOLKA; K2_DAYS_LEFT_UNKNOWN; RISK_URGENT</t>
+          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to wezwanie sądowe dotyczące spółki. Szacowany czas na reakcję: termin nieustalony.</t>
+          <t>Pismo z ZUS / urzędu — pilna reakcja wymagana.</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe dotyczące spółki wymaga pilnej reakcji — jeśli spółka nie odpowie w terminie, sąd może wydać wyrok zaoczny. Po bezskutecznej egzekucji wobec spółki wierzyciel może skierować roszczenie bezpośrednio do Ciebie jako byłego członka zarządu z art. 299 KSH.</t>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga pilnej reakcji. Termin na złożenie wyjaśnień lub odwołania jest ściśle określony w pouczeniu — jego przekroczenie może zamknąć drogę do obrony.</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Wezwanie sądowe jest skierowane do spółki. Właściwa reakcja zależy od treści wezwania: może to być stawiennictwo pełnomocnika spółki na rozprawie, złożenie pisma procesowego lub dostarczenie dokumentów. Brak reakcji spółki może doprowadzić do wyroku zaocznego i egzekucji, a po jej bezskuteczności — do roszczenia bezpośrednio wobec Ciebie jako byłego członka zarządu z art. 299 KSH. Kluczowe jest ustalenie, czy spółka ma pełnomocnika procesowego i czy planuje zareagować na wezwanie.</t>
+          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto zweryfikować: datę doręczenia, treść pouczenia, termin reakcji, adresata dokumentu, podstawę roszczenia, status członka zarządu oraz aktualność wpisu w KRS.</t>
+          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
+          <t>Ze względu na krótki termin warto jak najszybciej przejść do Audytu 48h, aby ustalić termin, zakres żądania i właściwy tryb odpowiedzi na pismo organu.</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
         </is>
       </c>
       <c r="S173" t="n">
         <v>1</v>
       </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>SCN_328</t>
-        </is>
-      </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>OK_DO_TESTÓW</t>
+          <t>ZATWIERDZONA</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
@@ -19922,7 +19902,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BASE_173</t>
+          <t>BASE_176</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -19937,7 +19917,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Sprawa pilna — pismo organu publicznego ZUS/US, 0-3</t>
+          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, 4-7</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -19957,17 +19937,17 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_0_3</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>RISK_URGENT</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Sprawa pilna</t>
+          <t>Wysokie ryzyko</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -19977,12 +19957,12 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu — pilna reakcja wymagana.</t>
+          <t>Pismo z ZUS / urzędu — szybka weryfikacja i odpowiedź.</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga pilnej reakcji. Termin na złożenie wyjaśnień lub odwołania jest ściśle określony w pouczeniu — jego przekroczenie może zamknąć drogę do obrony.</t>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga przygotowanej odpowiedzi. Właściwą formą jest złożenie wyjaśnień i dokumentów — nie sprzeciw ani pismo do sądu. Czas na reakcję jest ograniczony.</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -19997,7 +19977,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>Ze względu na krótki termin warto jak najszybciej przejść do Audytu 48h, aby ustalić termin, zakres żądania i właściwy tryb odpowiedzi na pismo organu.</t>
+          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma, termin i możliwe kierunki odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -20022,7 +20002,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BASE_174</t>
+          <t>BASE_177</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -20037,7 +20017,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, 0-3</t>
+          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, 4-7</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -20057,17 +20037,17 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_0_3</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>RISK_HIGH</t>
+          <t>RISK_MEDIUM</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko</t>
+          <t>Średnie ryzyko / braki danych</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -20077,12 +20057,12 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu — szybka weryfikacja i odpowiedź.</t>
+          <t>Pismo z ZUS / urzędu — weryfikacja terminu i zakresu.</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga przygotowanej odpowiedzi. Właściwą formą jest złożenie wyjaśnień i dokumentów — nie sprzeciw ani pismo do sądu. Czas na reakcję jest ograniczony.</t>
+          <t>Pismo z ZUS lub urzędu skarbowego wymaga weryfikacji i przygotowania właściwej odpowiedzi. Masz jeszcze czas, ale warto bez zwłoki potwierdzić termin określony w pouczeniu i ustalić zakres żądania organu.</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -20097,7 +20077,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma, termin i możliwe kierunki odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
+          <t>Audyt 48h może pomóc ocenić treść pisma organu, termin i zakres odpowiedzialności — zanim zdecydujesz o formie odpowiedzi.</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -20122,7 +20102,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BASE_175</t>
+          <t>BASE_178</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -20137,7 +20117,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Sprawa pilna — pismo organu publicznego ZUS/US, 4-7</t>
+          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, 8-14</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -20157,17 +20137,17 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>RISK_URGENT</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Sprawa pilna</t>
+          <t>Wysokie ryzyko</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -20177,12 +20157,12 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu — pilna reakcja wymagana.</t>
+          <t>Pismo z ZUS / urzędu — szybka weryfikacja i odpowiedź.</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga pilnej reakcji. Termin na złożenie wyjaśnień lub odwołania jest ściśle określony w pouczeniu — jego przekroczenie może zamknąć drogę do obrony.</t>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga przygotowanej odpowiedzi. Właściwą formą jest złożenie wyjaśnień i dokumentów — nie sprzeciw ani pismo do sądu. Czas na reakcję jest ograniczony.</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -20197,7 +20177,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>Ze względu na krótki termin warto jak najszybciej przejść do Audytu 48h, aby ustalić termin, zakres żądania i właściwy tryb odpowiedzi na pismo organu.</t>
+          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma, termin i możliwe kierunki odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -20222,7 +20202,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BASE_176</t>
+          <t>BASE_179</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -20237,7 +20217,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, 4-7</t>
+          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, 8-14</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -20257,17 +20237,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>RISK_HIGH</t>
+          <t>RISK_MEDIUM</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko</t>
+          <t>Średnie ryzyko / braki danych</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -20277,12 +20257,12 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu — szybka weryfikacja i odpowiedź.</t>
+          <t>Pismo z ZUS / urzędu — weryfikacja terminu i zakresu.</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga przygotowanej odpowiedzi. Właściwą formą jest złożenie wyjaśnień i dokumentów — nie sprzeciw ani pismo do sądu. Czas na reakcję jest ograniczony.</t>
+          <t>Pismo z ZUS lub urzędu skarbowego wymaga weryfikacji i przygotowania właściwej odpowiedzi. Masz jeszcze czas, ale warto bez zwłoki potwierdzić termin określony w pouczeniu i ustalić zakres żądania organu.</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -20297,7 +20277,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma, termin i możliwe kierunki odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
+          <t>Audyt 48h może pomóc ocenić treść pisma organu, termin i zakres odpowiedzialności — zanim zdecydujesz o formie odpowiedzi.</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -20322,7 +20302,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BASE_177</t>
+          <t>BASE_180</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -20337,7 +20317,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, 4-7</t>
+          <t>Niższe ryzyko / prewencja — pismo organu publicznego ZUS/US, 8-14</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -20357,17 +20337,17 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>RISK_MEDIUM</t>
+          <t>RISK_LOW</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych</t>
+          <t>Niższe ryzyko / prewencja</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -20377,12 +20357,12 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu — weryfikacja terminu i zakresu.</t>
+          <t>Pismo z ZUS / urzędu — niższe ryzyko, warto potwierdzić termin.</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>Pismo z ZUS lub urzędu skarbowego wymaga weryfikacji i przygotowania właściwej odpowiedzi. Masz jeszcze czas, ale warto bez zwłoki potwierdzić termin określony w pouczeniu i ustalić zakres żądania organu.</t>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej sprawy wskazuje na niższe ryzyko. Właściwa reakcja — wyjaśnienia lub odwołanie — wymaga jednak potwierdzenia terminu, adresata i zakresu żądania.</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -20422,7 +20402,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BASE_178</t>
+          <t>BASE_181</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -20437,7 +20417,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, 8-14</t>
+          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, above-14</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -20457,7 +20437,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -20522,7 +20502,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BASE_179</t>
+          <t>BASE_182</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -20537,7 +20517,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, 8-14</t>
+          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, above-14</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -20557,7 +20537,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -20622,7 +20602,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BASE_180</t>
+          <t>BASE_183</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -20637,7 +20617,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Niższe ryzyko / prewencja — pismo organu publicznego ZUS/US, 8-14</t>
+          <t>Niższe ryzyko / prewencja — pismo organu publicznego ZUS/US, above-14</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -20657,7 +20637,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -20722,7 +20702,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BASE_181</t>
+          <t>BASE_184</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -20737,7 +20717,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, above-14</t>
+          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, unknown</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -20757,7 +20737,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -20822,7 +20802,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>BASE_182</t>
+          <t>BASE_185</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -20837,7 +20817,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, above-14</t>
+          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, unknown</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -20857,7 +20837,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -20922,7 +20902,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BASE_183</t>
+          <t>BASE_186</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -20937,7 +20917,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Niższe ryzyko / prewencja — pismo organu publicznego ZUS/US, above-14</t>
+          <t>Sprawa pilna – pismo organu publicznego ZUS/US, 8-14 dni</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -20957,17 +20937,17 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>RISK_LOW</t>
+          <t>RISK_URGENT</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Niższe ryzyko / prewencja</t>
+          <t>Sprawa pilna</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -20977,12 +20957,12 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu — niższe ryzyko, warto potwierdzić termin.</t>
+          <t>Pismo z ZUS / urzędu – wysoki ciężar dokumentu, termin wymaga potwierdzenia.</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej sprawy wskazuje na niższe ryzyko. Właściwa reakcja — wyjaśnienia lub odwołanie — wymaga jednak potwierdzenia terminu, adresata i zakresu żądania.</t>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki należy do dokumentów o wysokim ciężarze prawnym — niezależnie od długości terminu. Organ, wysyłając takie pismo, wszczyna postępowanie, które może zakończyć się decyzją o odpowiedzialności osobistej. Termin odpowiedzi jest określony w pouczeniu i powinien być niezwłocznie potwierdzony.</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -20997,7 +20977,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>Audyt 48h może pomóc ocenić treść pisma organu, termin i zakres odpowiedzialności — zanim zdecydujesz o formie odpowiedzi.</t>
+          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma organu, potwierdzić termin i ustalić właściwy tryb odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -21022,7 +21002,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BASE_184</t>
+          <t>BASE_187</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -21037,7 +21017,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — pismo organu publicznego ZUS/US, unknown</t>
+          <t>Sprawa pilna – pismo organu publicznego ZUS/US, ponad 14 dni</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -21057,17 +21037,17 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>RISK_HIGH</t>
+          <t>RISK_URGENT</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko</t>
+          <t>Sprawa pilna</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -21077,12 +21057,12 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu — szybka weryfikacja i odpowiedź.</t>
+          <t>Pismo z ZUS / urzędu – wysoki ciężar dokumentu, czas na przemyślane działanie.</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki wymaga przygotowanej odpowiedzi. Właściwą formą jest złożenie wyjaśnień i dokumentów — nie sprzeciw ani pismo do sądu. Czas na reakcję jest ograniczony.</t>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki ma wysoki ciężar prawny — nawet gdy termin odpowiedzi nie jest bezpośrednio zagrożony. Organ wszczyna postępowanie, które może zakończyć się decyzją o odpowiedzialności osobistej. Posiadasz czas na odpowiednią reakcję, ale sprawa wymaga poważnego podejścia.</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -21097,7 +21077,7 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma, termin i możliwe kierunki odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
+          <t>Dysponujesz czasem na właściwe przygotowanie odpowiedzi — Audyt 48h pozwoli ocenić treść pisma, termin, zakres żądania organu i możliwe kierunki obrony.</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -21122,7 +21102,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BASE_185</t>
+          <t>BASE_188</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -21137,7 +21117,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych — pismo organu publicznego ZUS/US, unknown</t>
+          <t>Sprawa pilna – pismo organu publicznego ZUS/US, nieznany termin</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -21162,12 +21142,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>RISK_MEDIUM</t>
+          <t>RISK_URGENT</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych</t>
+          <t>Sprawa pilna</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -21177,12 +21157,12 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu — weryfikacja terminu i zakresu.</t>
+          <t>Pismo z ZUS / urzędu – wysoki ciężar dokumentu, termin nieznany.</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>Pismo z ZUS lub urzędu skarbowego wymaga weryfikacji i przygotowania właściwej odpowiedzi. Masz jeszcze czas, ale warto bez zwłoki potwierdzić termin określony w pouczeniu i ustalić zakres żądania organu.</t>
+          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki należy do dokumentów o wysokim ciężarze prawnym. Brak znajomości terminu odpowiedzi dodatkowo zwiększa ryzyko — organ wyznacza termin w pouczeniu, którego przekroczenie może zamknąć drogę do obrony.</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -21197,7 +21177,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>Audyt 48h może pomóc ocenić treść pisma organu, termin i zakres odpowiedzialności — zanim zdecydujesz o formie odpowiedzi.</t>
+          <t>W pierwszej kolejności ustal termin odpowiedzi wskazany w pouczeniu pisma — Audyt 48h pozwoli ocenić treść dokumentu, termin i właściwy tryb odpowiedzi.</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -21222,7 +21202,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BASE_186</t>
+          <t>BASE_189</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -21237,12 +21217,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Sprawa pilna – pismo organu publicznego ZUS/US, 8-14 dni</t>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, 0–3 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -21252,52 +21232,52 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>RISK_URGENT</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Sprawa pilna</t>
+          <t>Wysokie ryzyko</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: bardzo krótki czas pozostały na reakcję, wymagana ostrożna weryfikacja terminu</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu – wysoki ciężar dokumentu, termin wymaga potwierdzenia.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało bardzo mało czasu na reakcję — około 0–3 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki należy do dokumentów o wysokim ciężarze prawnym — niezależnie od długości terminu. Organ, wysyłając takie pismo, wszczyna postępowanie, które może zakończyć się decyzją o odpowiedzialności osobistej. Termin odpowiedzi jest określony w pouczeniu i powinien być niezwłocznie potwierdzony.</t>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście — ale bezskuteczność egzekucji otwiera wierzycielowi drogę do roszczeń wobec członków zarządu (art. 299 KSH). Wymagana jest pilna weryfikacja stanu egzekucji i majątku spółki.</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>Warto bez zwłoki przejść do Audytu 48h, aby ocenić treść pisma organu, potwierdzić termin i ustalić właściwy tryb odpowiedzi — zanim zdecydujesz o dalszych krokach.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -21306,11 +21286,16 @@
         </is>
       </c>
       <c r="S187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>ZATWIERDZONA</t>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
@@ -21322,7 +21307,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BASE_187</t>
+          <t>BASE_190</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -21337,12 +21322,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Sprawa pilna – pismo organu publicznego ZUS/US, ponad 14 dni</t>
+          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, 0–3 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -21352,12 +21337,12 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -21372,32 +21357,32 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: bardzo krótki czas pozostały na reakcję, wymagana ostrożna weryfikacja terminu</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu – wysoki ciężar dokumentu, czas na przemyślane działanie.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało bardzo mało czasu na reakcję — około 0–3 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki ma wysoki ciężar prawny — nawet gdy termin odpowiedzi nie jest bezpośrednio zagrożony. Organ wszczyna postępowanie, które może zakończyć się decyzją o odpowiedzialności osobistej. Posiadasz czas na odpowiednią reakcję, ale sprawa wymaga poważnego podejścia.</t>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się już postępowanie egzekucyjne na podstawie tytułu wykonawczego — to jeden z najbardziej zaawansowanych etapów sprawy. Jeżeli egzekucja z majątku spółki okaże się bezskuteczna, wierzyciel może następnie dochodzić zapłaty od członków zarządu (art. 299 KSH). Sprawa wymaga natychmiastowej weryfikacji dokumentów i terminów.</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>Dysponujesz czasem na właściwe przygotowanie odpowiedzi — Audyt 48h pozwoli ocenić treść pisma, termin, zakres żądania organu i możliwe kierunki obrony.</t>
+          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, zakres egzekucji i możliwe kierunki reakcji — w tym ocenę ryzyka osobistego członków zarządu.</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -21406,11 +21391,16 @@
         </is>
       </c>
       <c r="S188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>ZATWIERDZONA</t>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
@@ -21422,7 +21412,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BASE_188</t>
+          <t>BASE_191</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -21437,12 +21427,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Sprawa pilna – pismo organu publicznego ZUS/US, nieznany termin</t>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, 4–7 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+          <t>PISMO_KOMORNIK_SPOLKA</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -21452,52 +21442,52 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>RISK_URGENT</t>
+          <t>RISK_MEDIUM</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Sprawa pilna</t>
+          <t>Średnie ryzyko / braki danych</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>pismo ZUS lub urzędu skarbowego o odpowiedzialności członka zarządu; wyjaśnienia lub odwołanie, nie sprzeciw; sprawdzić termin z pouczenia, zakres zaległości, okres funkcji</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: krótki czas pozostały na reakcję, termin należy potwierdzić z dokumentu i daty doręczenia</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu – wysoki ciężar dokumentu, termin nieznany.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało niewiele czasu na reakcję — około 4–7 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>Pismo z ZUS lub urzędu skarbowego dotyczące Twojej odpowiedzialności za zobowiązania spółki należy do dokumentów o wysokim ciężarze prawnym. Brak znajomości terminu odpowiedzi dodatkowo zwiększa ryzyko — organ wyznacza termin w pouczeniu, którego przekroczenie może zamknąć drogę do obrony.</t>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny. Warto zweryfikować stan egzekucji i majątku spółki — bezskuteczność egzekucji jest podstawową przesłanką późniejszej odpowiedzialności członków zarządu (art. 299 KSH).</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>W praktyce należy potwierdzić: datę doręczenia, termin odpowiedzi wskazany w pouczeniu, zakres zaległości, okres pełnienia funkcji w zarządzie oraz dokumenty potwierdzające brak winy lub wyłączające odpowiedzialność.</t>
+          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto zweryfikować: datę doręczenia, termin odpowiedzi, adresata pisma, zakres zaległości, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz dokumenty wyłączające odpowiedzialność.</t>
+          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>W pierwszej kolejności ustal termin odpowiedzi wskazany w pouczeniu pisma — Audyt 48h pozwoli ocenić treść dokumentu, termin i właściwy tryb odpowiedzi.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -21506,11 +21496,16 @@
         </is>
       </c>
       <c r="S189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>ZATWIERDZONA</t>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
@@ -21522,7 +21517,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>BASE_189</t>
+          <t>BASE_192</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -21537,7 +21532,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, 0–3 dni, wstępna ocena bez dokumentów</t>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, 4–7 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -21557,7 +21552,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_0_3</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -21570,15 +21565,14 @@
           <t>Wysokie ryzyko</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: bardzo krótki czas pozostały na reakcję, wymagana ostrożna weryfikacja terminu</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: krótki czas pozostały na reakcję, termin należy potwierdzić z dokumentu i daty doręczenia</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało bardzo mało czasu na reakcję — około 0–3 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało niewiele czasu na reakcję — około 4–7 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -21609,7 +21603,6 @@
       <c r="S190" t="n">
         <v>0</v>
       </c>
-      <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -21629,7 +21622,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BASE_190</t>
+          <t>BASE_193</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -21644,7 +21637,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, 0–3 dni, wstępna ocena bez dokumentów</t>
+          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, 4–7 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -21664,7 +21657,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_0_3</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -21677,15 +21670,14 @@
           <t>Sprawa pilna</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: bardzo krótki czas pozostały na reakcję, wymagana ostrożna weryfikacja terminu</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: krótki czas pozostały na reakcję, termin należy potwierdzić z dokumentu i daty doręczenia</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało bardzo mało czasu na reakcję — około 0–3 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało niewiele czasu na reakcję — około 4–7 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -21716,7 +21708,6 @@
       <c r="S191" t="n">
         <v>0</v>
       </c>
-      <c r="T191" t="inlineStr"/>
       <c r="U191" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -21736,7 +21727,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BASE_191</t>
+          <t>BASE_194</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -21751,7 +21742,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, 4–7 dni, wstępna ocena bez dokumentów</t>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, 8–14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -21771,7 +21762,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -21784,15 +21775,14 @@
           <t>Średnie ryzyko / braki danych</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: krótki czas pozostały na reakcję, termin należy potwierdzić z dokumentu i daty doręczenia</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało niewiele czasu na reakcję — około 4–7 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -21823,7 +21813,6 @@
       <c r="S192" t="n">
         <v>0</v>
       </c>
-      <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -21843,7 +21832,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BASE_192</t>
+          <t>BASE_195</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -21858,7 +21847,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, 4–7 dni, wstępna ocena bez dokumentów</t>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, 8–14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -21878,7 +21867,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -21891,15 +21880,14 @@
           <t>Wysokie ryzyko</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: krótki czas pozostały na reakcję, termin należy potwierdzić z dokumentu i daty doręczenia</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało niewiele czasu na reakcję — około 4–7 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -21930,7 +21918,6 @@
       <c r="S193" t="n">
         <v>0</v>
       </c>
-      <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -21950,7 +21937,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BASE_193</t>
+          <t>BASE_196</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -21965,7 +21952,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, 4–7 dni, wstępna ocena bez dokumentów</t>
+          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, 8–14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -21985,7 +21972,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -21998,15 +21985,14 @@
           <t>Sprawa pilna</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: krótki czas pozostały na reakcję, termin należy potwierdzić z dokumentu i daty doręczenia</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało niewiele czasu na reakcję — około 4–7 dni kalendarzowych (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -22037,7 +22023,6 @@
       <c r="S194" t="n">
         <v>0</v>
       </c>
-      <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -22057,7 +22042,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BASE_194</t>
+          <t>BASE_197</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -22072,7 +22057,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, 8–14 dni, wstępna ocena bez dokumentów</t>
+          <t>Niższe ryzyko / prewencja — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -22092,33 +22077,32 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>RISK_MEDIUM</t>
+          <t>RISK_LOW</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
+          <t>Niższe ryzyko / prewencja</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Niższe ryzyko / prewencja. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny. Warto zweryfikować stan egzekucji i majątku spółki — bezskuteczność egzekucji jest podstawową przesłanką późniejszej odpowiedzialności członków zarządu (art. 299 KSH).</t>
+          <t>Pismo komornika dotyczy egzekucji z majątku spółki i na tym etapie jest oceniane jako niższe ryzyko osobiste. Warto jednak monitorować przebieg egzekucji — jeżeli okaże się bezskuteczna, wierzyciel może dochodzić zapłaty od członków zarządu (art. 299 KSH).</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -22133,7 +22117,7 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+          <t>Warto uporządkować dokumenty i monitorować przebieg egzekucji. Audyt 48h może pomóc ocenić, czy sprawa nie zmierza w stronę odpowiedzialności osobistej członków zarządu.</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -22144,7 +22128,6 @@
       <c r="S195" t="n">
         <v>0</v>
       </c>
-      <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -22164,7 +22147,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BASE_195</t>
+          <t>BASE_198</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -22179,7 +22162,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, 8–14 dni, wstępna ocena bez dokumentów</t>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -22199,33 +22182,32 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>RISK_HIGH</t>
+          <t>RISK_MEDIUM</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście — ale bezskuteczność egzekucji otwiera wierzycielowi drogę do roszczeń wobec członków zarządu (art. 299 KSH). Wymagana jest pilna weryfikacja stanu egzekucji i majątku spółki.</t>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny. Warto zweryfikować stan egzekucji i majątku spółki — bezskuteczność egzekucji jest podstawową przesłanką późniejszej odpowiedzialności członków zarządu (art. 299 KSH).</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -22251,7 +22233,6 @@
       <c r="S196" t="n">
         <v>0</v>
       </c>
-      <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -22271,7 +22252,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BASE_196</t>
+          <t>BASE_199</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -22286,7 +22267,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, 8–14 dni, wstępna ocena bez dokumentów</t>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -22306,33 +22287,32 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>RISK_URGENT</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Sprawa pilna</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>Pismo komornika oznacza, że przeciwko spółce toczy się już postępowanie egzekucyjne na podstawie tytułu wykonawczego — to jeden z najbardziej zaawansowanych etapów sprawy. Jeżeli egzekucja z majątku spółki okaże się bezskuteczna, wierzyciel może następnie dochodzić zapłaty od członków zarządu (art. 299 KSH). Sprawa wymaga natychmiastowej weryfikacji dokumentów i terminów.</t>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście — ale bezskuteczność egzekucji otwiera wierzycielowi drogę do roszczeń wobec członków zarządu (art. 299 KSH). Wymagana jest pilna weryfikacja stanu egzekucji i majątku spółki.</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -22347,7 +22327,7 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, zakres egzekucji i możliwe kierunki reakcji — w tym ocenę ryzyka osobistego członków zarządu.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -22358,7 +22338,6 @@
       <c r="S197" t="n">
         <v>0</v>
       </c>
-      <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -22378,7 +22357,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BASE_197</t>
+          <t>BASE_200</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -22393,7 +22372,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Niższe ryzyko / prewencja — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
+          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -22418,15 +22397,14 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>RISK_LOW</t>
+          <t>RISK_URGENT</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Niższe ryzyko / prewencja</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
@@ -22434,12 +22412,12 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Niższe ryzyko / prewencja. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>Pismo komornika dotyczy egzekucji z majątku spółki i na tym etapie jest oceniane jako niższe ryzyko osobiste. Warto jednak monitorować przebieg egzekucji — jeżeli okaże się bezskuteczna, wierzyciel może dochodzić zapłaty od członków zarządu (art. 299 KSH).</t>
+          <t>Pismo komornika oznacza, że przeciwko spółce toczy się już postępowanie egzekucyjne na podstawie tytułu wykonawczego — to jeden z najbardziej zaawansowanych etapów sprawy. Jeżeli egzekucja z majątku spółki okaże się bezskuteczna, wierzyciel może następnie dochodzić zapłaty od członków zarządu (art. 299 KSH). Sprawa wymaga natychmiastowej weryfikacji dokumentów i terminów.</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -22454,7 +22432,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>Warto uporządkować dokumenty i monitorować przebieg egzekucji. Audyt 48h może pomóc ocenić, czy sprawa nie zmierza w stronę odpowiedzialności osobistej członków zarządu.</t>
+          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, zakres egzekucji i możliwe kierunki reakcji — w tym ocenę ryzyka osobistego członków zarządu.</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -22465,7 +22443,6 @@
       <c r="S198" t="n">
         <v>0</v>
       </c>
-      <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -22485,7 +22462,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BASE_198</t>
+          <t>BASE_201</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -22495,12 +22472,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>BAZOWY</t>
+          <t>BAZOWY+REGUŁA_TWARDA</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, termin nieustalony, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -22520,7 +22497,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -22533,15 +22510,19 @@
           <t>Średnie ryzyko / braki danych</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>HR05</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: nieustalona, brak pewności co do terminu powinien zwiększać ostrożność oceny</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych nie udało się jednoznacznie ustalić, ile czasu pozostało na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -22572,7 +22553,6 @@
       <c r="S199" t="n">
         <v>0</v>
       </c>
-      <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -22592,7 +22572,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BASE_199</t>
+          <t>BASE_202</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -22602,12 +22582,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>BAZOWY</t>
+          <t>BAZOWY+REGUŁA_TWARDA</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, termin nieustalony, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -22627,7 +22607,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -22640,15 +22620,19 @@
           <t>Wysokie ryzyko</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>HR05</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: nieustalona, brak pewności co do terminu powinien zwiększać ostrożność oceny</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych nie udało się jednoznacznie ustalić, ile czasu pozostało na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -22679,7 +22663,6 @@
       <c r="S200" t="n">
         <v>0</v>
       </c>
-      <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -22699,7 +22682,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BASE_200</t>
+          <t>BASE_203</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -22709,12 +22692,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>BAZOWY</t>
+          <t>BAZOWY+REGUŁA_TWARDA</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, ponad 14 dni, wstępna ocena bez dokumentów</t>
+          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, termin nieustalony, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -22734,7 +22717,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -22747,15 +22730,19 @@
           <t>Sprawa pilna</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>HR05</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: nieustalona, brak pewności co do terminu powinien zwiększać ostrożność oceny</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych nie udało się jednoznacznie ustalić, ile czasu pozostało na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -22786,7 +22773,6 @@
       <c r="S201" t="n">
         <v>0</v>
       </c>
-      <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -22806,7 +22792,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BASE_201</t>
+          <t>BASE_204</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -22816,17 +22802,17 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>BAZOWY+REGUŁA_TWARDA</t>
+          <t>BAZOWY</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_SPOLKA, termin nieustalony, wstępna ocena bez dokumentów</t>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_CZLONEK_ZARZADU, 8–14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PISMO_KOMORNIK_SPOLKA</t>
+          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -22836,12 +22822,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -22854,29 +22840,24 @@
           <t>Średnie ryzyko / braki danych</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>HR05</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: nieustalona, brak pewności co do terminu powinien zwiększać ostrożność oceny</t>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych nie udało się jednoznacznie ustalić, ile czasu pozostało na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny. Warto zweryfikować stan egzekucji i majątku spółki — bezskuteczność egzekucji jest podstawową przesłanką późniejszej odpowiedzialności członków zarządu (art. 299 KSH).</t>
+          <t>Pismo komornika skierowane do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że postępowanie egzekucyjne jest w toku na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny — kluczowa jest weryfikacja tytułu wykonawczego i zakresu egzekucji.</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22886,7 +22867,7 @@
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, status KRS i możliwe kierunki dalszego działania.</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -22897,7 +22878,6 @@
       <c r="S202" t="n">
         <v>0</v>
       </c>
-      <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -22917,7 +22897,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BASE_202</t>
+          <t>BASE_205</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -22927,17 +22907,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>BAZOWY+REGUŁA_TWARDA</t>
+          <t>BAZOWY</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — PISMO_KOMORNIK_SPOLKA, termin nieustalony, wstępna ocena bez dokumentów</t>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_CZLONEK_ZARZADU, 8–14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PISMO_KOMORNIK_SPOLKA</t>
+          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -22947,12 +22927,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -22965,29 +22945,24 @@
           <t>Wysokie ryzyko</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>HR05</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: nieustalona, brak pewności co do terminu powinien zwiększać ostrożność oceny</t>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych nie udało się jednoznacznie ustalić, ile czasu pozostało na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>Pismo komornika oznacza, że przeciwko spółce toczy się postępowanie egzekucyjne na podstawie tytułu wykonawczego. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście — ale bezskuteczność egzekucji otwiera wierzycielowi drogę do roszczeń wobec członków zarządu (art. 299 KSH). Wymagana jest pilna weryfikacja stanu egzekucji i majątku spółki.</t>
+          <t>Pismo komornika skierowane do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że postępowanie egzekucyjne jest w toku na podstawie tytułu wykonawczego. Twoje zasoby majątkowe mogą zostać zajęte — wymagana jest pilna weryfikacja.</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22997,7 +22972,7 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić stan egzekucji, terminy, zakres zajęcia i możliwe kierunki dalszego działania — w tym ocenę ryzyka osobistego członków zarządu.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, status KRS i możliwe kierunki dalszego działania.</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -23008,7 +22983,6 @@
       <c r="S203" t="n">
         <v>0</v>
       </c>
-      <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -23028,7 +23002,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BASE_203</t>
+          <t>BASE_206</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -23038,17 +23012,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>BAZOWY+REGUŁA_TWARDA</t>
+          <t>BAZOWY</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Sprawa pilna — PISMO_KOMORNIK_SPOLKA, termin nieustalony, wstępna ocena bez dokumentów</t>
+          <t>Sprawa pilna — PISMO_KOMORNIK_CZLONEK_ZARZADU, 8–14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>PISMO_KOMORNIK_SPOLKA</t>
+          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -23058,12 +23032,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -23076,29 +23050,24 @@
           <t>Sprawa pilna</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>HR05</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>pismo komornicze w egzekucji prowadzonej przeciwko spółce — sprawdzić rodzaj czynności komornika, tytuł wykonawczy, zakres zajęcia i ewentualny termin reakcji, pilność: nieustalona, brak pewności co do terminu powinien zwiększać ostrożność oceny</t>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze w postępowaniu egzekucyjnym prowadzonym wobec spółki. Na podstawie podanych danych nie udało się jednoznacznie ustalić, ile czasu pozostało na reakcję. Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>Pismo komornika oznacza, że przeciwko spółce toczy się już postępowanie egzekucyjne na podstawie tytułu wykonawczego — to jeden z najbardziej zaawansowanych etapów sprawy. Jeżeli egzekucja z majątku spółki okaże się bezskuteczna, wierzyciel może następnie dochodzić zapłaty od członków zarządu (art. 299 KSH). Sprawa wymaga natychmiastowej weryfikacji dokumentów i terminów.</t>
+          <t>Pismo komornika skierowane bezpośrednio do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że wierzyciel wszczął już egzekucję na podstawie tytułu wykonawczego. To jeden z najbardziej zaawansowanych etapów postępowania — wymagana jest natychmiastowa weryfikacja.</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>Pismo komornika w sprawie spółki oznacza, że wierzyciel uzyskał tytuł wykonawczy i prowadzi egzekucję z majątku spółki. Na tym etapie komornik działa przeciwko spółce, nie przeciwko członkowi zarządu osobiście. Kluczowe do ustalenia: jakiej czynności dotyczy pismo (np. wszczęcie egzekucji, zajęcie rachunku bankowego, wezwanie do złożenia wykazu majątku), na jakim tytule wykonawczym opiera się egzekucja oraz jaki jest stan majątku spółki — bezskuteczność egzekucji wobec spółki jest podstawową przesłanką osobistej odpowiedzialności członków zarządu z art. 299 KSH.</t>
+          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -23108,7 +23077,7 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, zakres egzekucji i możliwe kierunki reakcji — w tym ocenę ryzyka osobistego członków zarządu.</t>
+          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, adresata pisma i możliwe kierunki reakcji.</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -23119,7 +23088,6 @@
       <c r="S204" t="n">
         <v>0</v>
       </c>
-      <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -23139,7 +23107,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>BASE_204</t>
+          <t>BASE_207</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -23154,7 +23122,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_CZLONEK_ZARZADU, 8–14 dni, wstępna ocena bez dokumentów</t>
+          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_CZLONEK_ZARZADU, ponad 14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -23174,7 +23142,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -23187,15 +23155,14 @@
           <t>Średnie ryzyko / braki danych</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -23226,7 +23193,6 @@
       <c r="S205" t="n">
         <v>0</v>
       </c>
-      <c r="T205" t="inlineStr"/>
       <c r="U205" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -23246,7 +23212,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>BASE_205</t>
+          <t>BASE_208</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -23261,7 +23227,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — PISMO_KOMORNIK_CZLONEK_ZARZADU, 8–14 dni, wstępna ocena bez dokumentów</t>
+          <t>Wysokie ryzyko — PISMO_KOMORNIK_CZLONEK_ZARZADU, ponad 14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -23281,7 +23247,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -23294,15 +23260,14 @@
           <t>Wysokie ryzyko</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -23333,7 +23298,6 @@
       <c r="S206" t="n">
         <v>0</v>
       </c>
-      <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -23353,7 +23317,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BASE_206</t>
+          <t>BASE_209</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -23368,7 +23332,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Sprawa pilna — PISMO_KOMORNIK_CZLONEK_ZARZADU, 8–14 dni, wstępna ocena bez dokumentów</t>
+          <t>Sprawa pilna — PISMO_KOMORNIK_CZLONEK_ZARZADU, ponad 14 dni, wstępna ocena bez dokumentów</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -23388,7 +23352,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -23401,15 +23365,14 @@
           <t>Sprawa pilna</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin umiarkowanie krótki, nadal wymaga kontroli daty doręczenia i pouczenia</t>
+          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało około 8–14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -23440,7 +23403,6 @@
       <c r="S207" t="n">
         <v>0</v>
       </c>
-      <c r="T207" t="inlineStr"/>
       <c r="U207" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -23460,7 +23422,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BASE_207</t>
+          <t>BASE_210</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -23475,12 +23437,12 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych — PISMO_KOMORNIK_CZLONEK_ZARZADU, ponad 14 dni, wstępna ocena bez dokumentów</t>
+          <t>Wysokie ryzyko — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), 0–3 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -23490,64 +23452,62 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>RISK_MEDIUM</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Średnie ryzyko / braki danych</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr"/>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_0_3; RISK_HIGH</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: 0–3 dni.</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>Pismo komornika skierowane do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że postępowanie egzekucyjne jest w toku na podstawie tytułu wykonawczego. Część danych wymaga uzupełnienia lub potwierdzenia, dlatego ocena ma charakter wstępny — kluczowa jest weryfikacja tytułu wykonawczego i zakresu egzekucji.</t>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu, powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki, to poważny sygnał — wierzyciel sygnalizuje zamiar dochodzenia zapłaty bezpośrednio od Ciebie. To jeszcze nie jest pozew ani nakaz, ale brak reakcji może przyspieszyć skierowanie sprawy do sądu.</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, status KRS i możliwe kierunki dalszego działania.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
         </is>
       </c>
       <c r="S208" t="n">
         <v>0</v>
       </c>
-      <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -23555,7 +23515,7 @@
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
@@ -23567,7 +23527,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>BASE_208</t>
+          <t>BASE_211</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -23582,12 +23542,12 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko — PISMO_KOMORNIK_CZLONEK_ZARZADU, ponad 14 dni, wstępna ocena bez dokumentów</t>
+          <t>Sprawa pilna — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), 0–3 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -23597,64 +23557,62 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>RISK_HIGH</t>
+          <t>RISK_URGENT</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Wysokie ryzyko</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr"/>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_0_3; RISK_URGENT</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: 0–3 dni.</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>Pismo komornika skierowane do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że postępowanie egzekucyjne jest w toku na podstawie tytułu wykonawczego. Twoje zasoby majątkowe mogą zostać zajęte — wymagana jest pilna weryfikacja.</t>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu, powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki, to zaawansowany etap sprawy — wierzyciel ma już podstawy do wystąpienia z pozwem, jeśli wezwanie pozostanie bez odpowiedzi. Krótki czas na reakcję wymaga natychmiastowego działania.</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, status KRS i możliwe kierunki dalszego działania.</t>
+          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
         </is>
       </c>
       <c r="S209" t="n">
         <v>0</v>
       </c>
-      <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -23662,7 +23620,7 @@
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
@@ -23674,7 +23632,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BASE_209</t>
+          <t>BASE_212</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -23689,12 +23647,12 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Sprawa pilna — PISMO_KOMORNIK_CZLONEK_ZARZADU, ponad 14 dni, wstępna ocena bez dokumentów</t>
+          <t>Wysokie ryzyko — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), 4–7 dni, EPU=NIE</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -23704,64 +23662,62 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>RISK_URGENT</t>
+          <t>RISK_HIGH</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Sprawa pilna</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr"/>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>pismo komornicze skierowane do członka zarządu — sprawdzić rodzaj czynności, podstawę egzekucji, adresata pisma, zakres zajęcia i ewentualny termin reakcji, pilność: termin nie wydaje się natychmiastowy, ale należy potwierdzić go z dokumentu</t>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_4_7; RISK_HIGH</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji: pismo komornicze skierowane do członka zarządu. Na podstawie podanych danych zostało ponad 14 dni kalendarzowych na reakcję (wliczają się soboty, niedziele i dni świąteczne). Ocena ma ograniczoną pewność, ponieważ nie opiera się jeszcze na pełnym komplecie dokumentów.</t>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: 4–7 dni.</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>Pismo komornika skierowane bezpośrednio do Ciebie jako członka zarządu (obecnego lub byłego) oznacza, że wierzyciel wszczął już egzekucję na podstawie tytułu wykonawczego. To jeden z najbardziej zaawansowanych etapów postępowania — wymagana jest natychmiastowa weryfikacja.</t>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu, powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki, to poważny sygnał — wierzyciel sygnalizuje zamiar dochodzenia zapłaty bezpośrednio od Ciebie. To jeszcze nie jest pozew ani nakaz, ale brak reakcji może przyspieszyć skierowanie sprawy do sądu.</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>Pismo komornika jest skierowane bezpośrednio do Ciebie jako członka zarządu. Oznacza to, że istnieje prawomocne orzeczenie lub nakaz stanowiący tytuł wykonawczy — wierzyciel dochodzi Twojej odpowiedzialności osobistej w drodze egzekucji. Kluczowe do ustalenia: treść tytułu wykonawczego, czy upłynął termin na zaskarżenie, czy egzekucja została wszczęta prawidłowo oraz czy możliwe jest jej zawieszenie lub umorzenie.</t>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>W Audycie 48h warto w pierwszej kolejności zweryfikować: dokument główny, datę doręczenia, termin reakcji, adresata pisma, podstawę roszczenia, okres pełnienia funkcji w zarządzie, aktualność wpisu w KRS oraz komplet dokumentów pomocniczych.</t>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>Ze względu na pilny charakter sprawy rozsądnym kolejnym krokiem jest Audyt 48h. Audyt pozwala szybko sprawdzić dokumenty, daty, terminy, adresata pisma i możliwe kierunki reakcji.</t>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani rekomendacji procesowej. Indywidualna rekomendacja ścieżki obrony może zostać przygotowana dopiero po analizie dokumentów w ramach Audytu 48h.</t>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
         </is>
       </c>
       <c r="S210" t="n">
         <v>0</v>
       </c>
-      <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr">
         <is>
           <t>OK_DO_TESTÓW</t>
@@ -23769,10 +23725,1270 @@
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>Nowy scenariusz 05.07.2026 — obsługa pism komorniczych (wariant spółki / uzupełnienie kombinacji).</t>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>BASE_213</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_4_7</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_4_7; RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: 4–7 dni.</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu wymaga sprawdzenia treści i podstawy roszczenia. To jeszcze nie postępowanie sądowe, ale powołanie się na art. 299 KSH i bezskuteczność egzekucji wobec spółki oznacza realne ryzyko, że sprawa trafi do sądu, jeśli nie zostanie wyjaśniona.</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>BASE_214</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), 4–7 dni, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_4_7</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_4_7; RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: 4–7 dni.</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu, powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki, to zaawansowany etap sprawy — wierzyciel ma już podstawy do wystąpienia z pozwem, jeśli wezwanie pozostanie bez odpowiedzi. Krótki czas na reakcję wymaga natychmiastowego działania.</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>BASE_215</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_8_14; RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: 8–14 dni.</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu, powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki, to poważny sygnał — wierzyciel sygnalizuje zamiar dochodzenia zapłaty bezpośrednio od Ciebie. To jeszcze nie jest pozew ani nakaz, ale brak reakcji może przyspieszyć skierowanie sprawy do sądu.</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>BASE_216</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_8_14; RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: 8–14 dni.</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu wymaga sprawdzenia treści i podstawy roszczenia. To jeszcze nie postępowanie sądowe, ale powołanie się na art. 299 KSH i bezskuteczność egzekucji wobec spółki oznacza realne ryzyko, że sprawa trafi do sądu, jeśli nie zostanie wyjaśniona.</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>BASE_217</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), 8–14 dni, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_8_14</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_8_14; RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: 8–14 dni.</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu, powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki, to zaawansowany etap sprawy — wierzyciel ma już podstawy do wystąpienia z pozwem, jeśli wezwanie pozostanie bez odpowiedzi. Krótki czas na reakcję wymaga natychmiastowego działania.</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>BASE_218</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: ponad 14 dni.</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu, powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki, to poważny sygnał — wierzyciel sygnalizuje zamiar dochodzenia zapłaty bezpośrednio od Ciebie. To jeszcze nie jest pozew ani nakaz, ale brak reakcji może przyspieszyć skierowanie sprawy do sądu.</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>BASE_219</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>RISK_LOW</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Niższe ryzyko / prewencja</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_LOW</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Niższe ryzyko / prewencja. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: ponad 14 dni.</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu jest na tym etapie oceniane jako niższe ryzyko. Warto jednak potwierdzić treść wezwania, podstawę roszczenia i to, czy egzekucja wobec spółki rzeczywiście była bezskuteczna, zanim sprawa ewentualnie trafi do sądu.</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Warto zachować dokumenty i potwierdzić podstawowe informacje, a w razie wątpliwości skorzystać z Audytu 48h.</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S217" t="n">
+        <v>0</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>BASE_220</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: ponad 14 dni.</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu wymaga sprawdzenia treści i podstawy roszczenia. To jeszcze nie postępowanie sądowe, ale powołanie się na art. 299 KSH i bezskuteczność egzekucji wobec spółki oznacza realne ryzyko, że sprawa trafi do sądu, jeśli nie zostanie wyjaśniona.</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>BASE_221</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), ponad 14 dni, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_ABOVE_14; RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: ponad 14 dni.</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu, powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki, to zaawansowany etap sprawy — wierzyciel ma już podstawy do wystąpienia z pozwem, jeśli wezwanie pozostanie bez odpowiedzi. Krótki czas na reakcję wymaga natychmiastowego działania.</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S219" t="n">
+        <v>0</v>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>BASE_222</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Wysokie ryzyko</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_UNKNOWN; RISK_HIGH</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Wysokie ryzyko. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: termin nieustalony.</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu, powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki, to poważny sygnał — wierzyciel sygnalizuje zamiar dochodzenia zapłaty bezpośrednio od Ciebie. To jeszcze nie jest pozew ani nakaz, ale brak reakcji może przyspieszyć skierowanie sprawy do sądu.</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Warto rozważyć Audyt 48h, aby potwierdzić termin, adresata pisma, podstawę roszczenia i możliwe kierunki dalszego działania.</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>BASE_223</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Średnie ryzyko / braki danych</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_UNKNOWN; RISK_MEDIUM</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Średnie ryzyko / braki danych. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: termin nieustalony.</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu wymaga sprawdzenia treści i podstawy roszczenia. To jeszcze nie postępowanie sądowe, ale powołanie się na art. 299 KSH i bezskuteczność egzekucji wobec spółki oznacza realne ryzyko, że sprawa trafi do sądu, jeśli nie zostanie wyjaśniona.</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Audyt 48h może pomóc potwierdzić, czy dokumenty i terminy zostały prawidłowo ocenione.</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>BASE_224</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>AKTYWNY</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>BAZOWY</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Sprawa pilna — scenariusz bazowy: przedsądowe wezwanie do zapłaty do członka zarządu (art. 299 KSH), termin nieustalony, EPU=NIE</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Sprawa pilna</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>scenariusz bazowy; WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; EPU=NIE; K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU; K2_DAYS_LEFT_UNKNOWN; RISK_URGENT</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Sprawa została wstępnie zakwalifikowana jako: Sprawa pilna. Dokument wymagający reakcji to przedsądowe wezwanie do zapłaty skierowane do członka zarządu, powołujące się na art. 299 KSH. Szacowany czas na reakcję: termin nieustalony.</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty skierowane do Ciebie jako członka zarządu, powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki, to zaawansowany etap sprawy — wierzyciel ma już podstawy do wystąpienia z pozwem, jeśli wezwanie pozostanie bez odpowiedzi. Krótki czas na reakcję wymaga natychmiastowego działania.</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie do zapłaty jest skierowane bezpośrednio do Ciebie jako członka zarządu i powołuje się na art. 299 KSH oraz bezskuteczność egzekucji wobec spółki. To jeszcze nie jest pismo procesowe ani orzeczenie sądu — nie ma tu mowy o sprzeciwie, odpowiedzi na pozew ani ryzyku wyroku zaocznego. Właściwą reakcją jest odpowiedź na wezwanie, zakwestionowanie roszczenia (jeśli istnieją ku temu podstawy), próba ugody lub spłaty, albo przygotowanie dokumentów na wypadek skierowania sprawy do sądu. Kluczowe do ustalenia: czy egzekucja wobec spółki rzeczywiście była bezskuteczna, okres pełnienia funkcji w zarządzie w chwili powstania zobowiązania, aktualność wpisu w KRS oraz czy złożono wniosek o upadłość we właściwym czasie — to typowe argumenty obrony z art. 299 KSH.</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>W Audycie 48h warto zweryfikować: treść wezwania, podstawę roszczenia, dowód bezskuteczności egzekucji wobec spółki, termin reakcji, okres pełnienia funkcji w zarządzie oraz aktualność wpisu w KRS.</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Ze względu na pilny charakter sprawy warto przejść do Audytu 48h, aby szybko sprawdzić dokumenty, daty, terminy i możliwe kierunki reakcji.</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>To jest automatyczna, orientacyjna ocena ryzyka i pilności sprawy. Nie stanowi porady prawnej, opinii prawnej ani ostatecznej rekomendacji procesowej.</t>
+        </is>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>OK_DO_TESTÓW</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Nowy scenariusz 06.07.2026 — przedsądowe wezwanie do zapłaty (członek zarządu, art. 299 KSH).</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
         <is>
           <t>K3–K6 nie są warunkami wyboru scenariusza bazowego; ich teksty pobieraj z arkusza 6A_Moduly_K3_K6.</t>
         </is>
@@ -41173,7 +42389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="5.625" customWidth="1" style="4" min="1" max="1"/>
@@ -43036,6 +44252,53 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rodzaj pisma</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Wezwanie przedsądowe (członek zarządu)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Brak</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Nowa kategoria 06.07.2026: przedsądowe wezwanie do zapłaty powołujące się na art. 299 KSH i/lub bezskuteczność egzekucji wobec spółki, skierowane do członka zarządu — poważny sygnał, ale to jeszcze nie dokument sądowy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
@@ -43050,7 +44313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" style="4" min="1" max="1"/>
@@ -43461,48 +44724,48 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_0_3</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>0–3 dni kalendarzowe</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>K2_urgency</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Wezwanie przedsądowe (członek zarządu)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>K1_document_weight</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Najwyższa pilność. Bardzo krótki czas na reakcję.</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki — poważnie wymierzone bezpośrednio w członka zarządu, ale to jeszcze nie dokument sądowy (analogicznie do wezwania sądowego skierowanego do członka zarządu).</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>4–7 dni kalendarzowych</t>
+          <t>0–3 dni kalendarzowe</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -43514,14 +44777,14 @@
         <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Wysoka pilność. Jest jeszcze czas, ale sprawa wymaga szybkiego działania.</t>
+          <t>Najwyższa pilność. Bardzo krótki czas na reakcję.</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -43531,12 +44794,12 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>8–14 dni kalendarzowych</t>
+          <t>4–7 dni kalendarzowych</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -43548,14 +44811,14 @@
         <v>0</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Umiarkowana pilność. Termin wymaga kontroli, ale nie jest jeszcze krytyczny.</t>
+          <t>Wysoka pilność. Jest jeszcze czas, ale sprawa wymaga szybkiego działania.</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -43565,12 +44828,12 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Ponad 14 dni kalendarzowych</t>
+          <t>8–14 dni kalendarzowych</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -43582,14 +44845,14 @@
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Niska pilność czasowa, choć ryzyko może wynikać z rodzaju dokumentu.</t>
+          <t>Umiarkowana pilność. Termin wymaga kontroli, ale nie jest jeszcze krytyczny.</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -43599,12 +44862,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem / nie udało się ustalić</t>
+          <t>Ponad 14 dni kalendarzowych</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -43616,14 +44879,14 @@
         <v>0</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Brak wiedzy o terminie jest ryzykiem samym w sobie. Dlatego przyznajemy 1 punkt za pilność i 1 punkt za niepewność.</t>
+          <t>Niska pilność czasowa, choć ryzyko może wynikać z rodzaju dokumentu.</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -43633,31 +44896,31 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>K2A_DELIVERY_DATE_KNOWN</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Tak, znam datę doręczenia</t>
+          <t>Nie wiem / nie udało się ustalić</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>K2A_auxiliary</t>
+          <t>K2_urgency</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Dane pomocnicze. Nie punktować samodzielnie. Służy do obliczenia K2.</t>
+          <t>Brak wiedzy o terminie jest ryzykiem samym w sobie. Dlatego przyznajemy 1 punkt za pilność i 1 punkt za niepewność.</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -43667,12 +44930,12 @@
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>K2A_DELIVERY_DATE_UNKNOWN</t>
+          <t>K2A_DELIVERY_DATE_KNOWN</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Nie znam daty doręczenia</t>
+          <t>Tak, znam datę doręczenia</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -43687,11 +44950,11 @@
         <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Brak daty doręczenia zwiększa niepewność.</t>
+          <t>Dane pomocnicze. Nie punktować samodzielnie. Służy do obliczenia K2.</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -43701,17 +44964,17 @@
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>K3_SUPPORT_BASIC_NO_DOCS</t>
+          <t>K2A_DELIVERY_DATE_UNKNOWN</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Tylko wstępna ocena bez wysyłki dokumentów</t>
+          <t>Nie znam daty doręczenia</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>K3_support_needed</t>
+          <t>K2A_auxiliary</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -43721,11 +44984,11 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Ocena bez pełnych dokumentów jest bardziej niepewna.</t>
+          <t>Brak daty doręczenia zwiększa niepewność.</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -43735,12 +44998,12 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>K3_SUPPORT_NOW_DOCS_LATER</t>
+          <t>K3_SUPPORT_BASIC_NO_DOCS</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Wstępna ocena teraz + dokumenty dosyłam później</t>
+          <t>Tylko wstępna ocena bez wysyłki dokumentów</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -43755,11 +45018,11 @@
         <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Częściowa gotowość do uporządkowania sprawy.</t>
+          <t>Ocena bez pełnych dokumentów jest bardziej niepewna.</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -43769,12 +45032,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>K3_READY_FOR_AUDIT_48H</t>
+          <t>K3_SUPPORT_NOW_DOCS_LATER</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Jestem gotowy wysłać dokumenty i wejść w Audyt 48h</t>
+          <t>Wstępna ocena teraz + dokumenty dosyłam później</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -43789,11 +45052,11 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Najmniejsza niepewność organizacyjna, użytkownik jest gotowy do pełniejszej analizy.</t>
+          <t>Częściowa gotowość do uporządkowania sprawy.</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -43803,17 +45066,17 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_ACTIVE</t>
+          <t>K3_READY_FOR_AUDIT_48H</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Nadal pełnię funkcję</t>
+          <t>Jestem gotowy wysłać dokumenty i wejść w Audyt 48h</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>K4_board_status</t>
+          <t>K3_support_needed</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -43823,11 +45086,11 @@
         <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Nadal pełniona funkcja może wymagać uporządkowania sytuacji, ale sama w sobie nie oznacza najwyższego chaosu.</t>
+          <t>Najmniejsza niepewność organizacyjna, użytkownik jest gotowy do pełniejszej analizy.</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -43837,12 +45100,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_RESIGNED</t>
+          <t>K4_BOARD_ACTIVE</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Była rezygnacja / odwołanie</t>
+          <t>Nadal pełnię funkcję</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -43861,7 +45124,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Rezygnacja/odwołanie wymaga sprawdzenia dat i wpisu w KRS.</t>
+          <t>Nadal pełniona funkcja może wymagać uporządkowania sytuacji, ale sama w sobie nie oznacza najwyższego chaosu.</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -43871,12 +45134,12 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_UNKNOWN</t>
+          <t>K4_BOARD_RESIGNED</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem / trudno powiedzieć</t>
+          <t>Była rezygnacja / odwołanie</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -43891,11 +45154,11 @@
         <v>0</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Niepewność co do statusu w zarządzie istotnie zwiększa chaos informacyjny.</t>
+          <t>Rezygnacja/odwołanie wymaga sprawdzenia dat i wpisu w KRS.</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -43905,17 +45168,17 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_UPDATED</t>
+          <t>K4_BOARD_UNKNOWN</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Tak — wpis w KRS widnieje</t>
+          <t>Nie wiem / trudno powiedzieć</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>K5_krs_status</t>
+          <t>K4_board_status</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -43925,11 +45188,11 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Najniższa niepewność formalna w zakresie wpisu KRS.</t>
+          <t>Niepewność co do statusu w zarządzie istotnie zwiększa chaos informacyjny.</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -43939,12 +45202,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_NOT_UPDATED</t>
+          <t>K5_KRS_UPDATED</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Nie — brak aktualnego wpisu w KRS</t>
+          <t>Tak — wpis w KRS widnieje</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -43959,11 +45222,11 @@
         <v>0</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Brak aktualnego wpisu może zwiększać chaos formalny i ryzyko nieporozumień.</t>
+          <t>Najniższa niepewność formalna w zakresie wpisu KRS.</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -43973,12 +45236,12 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_UNKNOWN</t>
+          <t>K5_KRS_NOT_UPDATED</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem</t>
+          <t>Nie — brak aktualnego wpisu w KRS</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -43997,7 +45260,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Brak wiedzy o wpisie w KRS wymaga weryfikacji.</t>
+          <t>Brak aktualnego wpisu może zwiększać chaos formalny i ryzyko nieporozumień.</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -44007,12 +45270,12 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>K5_NOT_APPLICABLE</t>
+          <t>K5_KRS_UNKNOWN</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Nie dotyczy</t>
+          <t>Nie wiem</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -44027,11 +45290,11 @@
         <v>0</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Stosować automatycznie, gdy użytkownik nadal pełni funkcję.</t>
+          <t>Brak wiedzy o wpisie w KRS wymaga weryfikacji.</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -44041,17 +45304,17 @@
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_DEFENSE</t>
+          <t>K5_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Chcę ocenić, czy mam realne podstawy obrony</t>
+          <t>Nie dotyczy</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>K6_goal</t>
+          <t>K5_krs_status</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
@@ -44065,7 +45328,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Cel dotyczy merytorycznej oceny podstaw obrony i możliwych zarzutów.</t>
+          <t>Stosować automatycznie, gdy użytkownik nadal pełni funkcję.</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -44075,12 +45338,12 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_BUY_TIME</t>
+          <t>K6_GOAL_DEFENSE</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Chcę zyskać czas na przygotowanie obrony</t>
+          <t>Chcę ocenić, czy mam realne podstawy obrony</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -44099,7 +45362,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Cel wymaga bezpiecznego języka: tylko legalne środki procesowe i faktyczna dokumentacja.</t>
+          <t>Cel dotyczy merytorycznej oceny podstaw obrony i możliwych zarzutów.</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -44109,12 +45372,12 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_PROCEDURAL_LETTER</t>
+          <t>K6_GOAL_BUY_TIME</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Chcę przygotować odpowiednie pismo procesowe</t>
+          <t>Chcę zyskać czas na przygotowanie obrony</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -44133,7 +45396,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Cel praktyczny: dobór właściwego pisma zależnie od dokumentu.</t>
+          <t>Cel wymaga bezpiecznego języka: tylko legalne środki procesowe i faktyczna dokumentacja.</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -44143,12 +45406,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_PLAN</t>
+          <t>K6_GOAL_PROCEDURAL_LETTER</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Potrzebuję planu działania i oceny szans</t>
+          <t>Chcę przygotować odpowiednie pismo procesowe</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -44167,7 +45430,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Cel dotyczy planu kolejnych kroków oraz oceny szans po weryfikacji dokumentów.</t>
+          <t>Cel praktyczny: dobór właściwego pisma zależnie od dokumentu.</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -44177,12 +45440,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_UNKNOWN</t>
+          <t>K6_GOAL_PLAN</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem — potrzebuję uporządkowania sytuacji</t>
+          <t>Potrzebuję planu działania i oceny szans</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -44197,11 +45460,11 @@
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Niepewność celu zwiększa potrzebę uporządkowania sprawy.</t>
+          <t>Cel dotyczy planu kolejnych kroków oraz oceny szans po weryfikacji dokumentów.</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -44209,26 +45472,42 @@
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>K6_GOAL_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Nie wiem — potrzebuję uporządkowania sytuacji</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>K6_goal</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Niepewność celu zwiększa potrzebę uporządkowania sprawy.</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>Treść</t>
-        </is>
-      </c>
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="n"/>
       <c r="D36" s="5" t="n"/>
       <c r="E36" s="5" t="n"/>
@@ -44237,48 +45516,32 @@
       <c r="H36" s="5" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>K7_AMOUNT_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Nie wiem / nie widzę kwoty</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>K7_claim_amount</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Brak kwoty ogranicza pewność oceny; dodać H=1 i W=1.</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>Treść</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_UP_TO_10K</t>
+          <t>K7_AMOUNT_UNKNOWN</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Do 10 000 zł</t>
+          <t>Nie wiem / nie widzę kwoty</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -44293,26 +45556,26 @@
         <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Niska kwota nie podnosi samodzielnie ciężaru sprawy.</t>
+          <t>Brak kwoty ogranicza pewność oceny; dodać H=1 i W=1.</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_10K_50K</t>
+          <t>K7_AMOUNT_UP_TO_10K</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>10 001 – 50 000 zł</t>
+          <t>Do 10 000 zł</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -44331,22 +45594,22 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Kwota umiarkowana — niewielkie podniesienie ciężaru finansowego.</t>
+          <t>Niska kwota nie podnosi samodzielnie ciężaru sprawy.</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_50K_150K</t>
+          <t>K7_AMOUNT_10K_50K</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>50 001 – 150 000 zł</t>
+          <t>10 001 – 50 000 zł</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -44365,22 +45628,22 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Kwota istotna — podnosi ciężar sprawy.</t>
+          <t>Kwota umiarkowana — niewielkie podniesienie ciężaru finansowego.</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_150K_500K</t>
+          <t>K7_AMOUNT_50K_150K</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>150 001 – 500 000 zł</t>
+          <t>50 001 – 150 000 zł</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -44399,22 +45662,22 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Wysoka kwota — istotne konsekwencje finansowe.</t>
+          <t>Kwota istotna — podnosi ciężar sprawy.</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_ABOVE_500K</t>
+          <t>K7_AMOUNT_150K_500K</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Powyżej 500 000 zł</t>
+          <t>150 001 – 500 000 zł</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -44433,44 +45696,60 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
+          <t>Wysoka kwota — istotne konsekwencje finansowe.</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>K7_AMOUNT_ABOVE_500K</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Powyżej 500 000 zł</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>K7_claim_amount</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
           <t>Bardzo wysoka kwota — znacząco podnosi ciężar sprawy.</t>
         </is>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="H43" s="5" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="n"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="11" t="n"/>
-    </row>
     <row r="44" ht="45" customHeight="1">
-      <c r="A44" s="25" t="n"/>
-      <c r="B44" s="25" t="n"/>
-      <c r="C44" s="25" t="n"/>
-      <c r="D44" s="25" t="n"/>
-      <c r="E44" s="25" t="n"/>
-      <c r="F44" s="25" t="n"/>
-      <c r="G44" s="25" t="n"/>
-      <c r="H44" s="25" t="n"/>
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="11" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>Treść</t>
-        </is>
-      </c>
+      <c r="A45" s="25" t="n"/>
+      <c r="B45" s="25" t="n"/>
       <c r="C45" s="25" t="n"/>
       <c r="D45" s="25" t="n"/>
       <c r="E45" s="25" t="n"/>
@@ -44479,14 +45758,14 @@
       <c r="H45" s="25" t="n"/>
     </row>
     <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Zasada liczenia C</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>C liczymy z rodzaju dokumentu i jego ciężaru procesowego.</t>
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Treść</t>
         </is>
       </c>
       <c r="C46" s="25" t="n"/>
@@ -44499,12 +45778,12 @@
     <row r="47" ht="90" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Zasada liczenia P</t>
+          <t>Zasada liczenia C</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>P liczymy przede wszystkim z czasu na reakcję.</t>
+          <t>C liczymy z rodzaju dokumentu i jego ciężaru procesowego.</t>
         </is>
       </c>
       <c r="C47" s="25" t="n"/>
@@ -44517,12 +45796,12 @@
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Zasada liczenia H</t>
+          <t>Zasada liczenia P</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>H liczymy z niepewności danych, statusu zarządu/KRS i organizacyjnej gotowości.</t>
+          <t>P liczymy przede wszystkim z czasu na reakcję.</t>
         </is>
       </c>
       <c r="C48" s="25" t="n"/>
@@ -44535,12 +45814,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Zasada liczenia W</t>
+          <t>Zasada liczenia H</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>W liczymy z przedziału kwoty roszczenia; W wpływa na ciężar finansowy, ale nie zastępuje oceny terminu i dokumentu.</t>
+          <t>H liczymy z niepewności danych, statusu zarządu/KRS i organizacyjnej gotowości.</t>
         </is>
       </c>
       <c r="C49" s="25" t="n"/>
@@ -44551,14 +45830,14 @@
       <c r="H49" s="25" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="inlineStr">
-        <is>
-          <t>Wynik końcowy</t>
-        </is>
-      </c>
-      <c r="B50" s="22" t="inlineStr">
-        <is>
-          <t>S = C + P + H + W.</t>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Zasada liczenia W</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>W liczymy z przedziału kwoty roszczenia; W wpływa na ciężar finansowy, ale nie zastępuje oceny terminu i dokumentu.</t>
         </is>
       </c>
       <c r="C50" s="25" t="n"/>
@@ -44569,14 +45848,32 @@
       <c r="H50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="25" t="n"/>
-      <c r="B51" s="25" t="n"/>
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>Wynik końcowy</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>S = C + P + H + W.</t>
+        </is>
+      </c>
       <c r="C51" s="25" t="n"/>
       <c r="D51" s="25" t="n"/>
       <c r="E51" s="25" t="n"/>
       <c r="F51" s="25" t="n"/>
       <c r="G51" s="25" t="n"/>
       <c r="H51" s="25" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="n"/>
+      <c r="B52" s="25" t="n"/>
+      <c r="C52" s="25" t="n"/>
+      <c r="D52" s="25" t="n"/>
+      <c r="E52" s="25" t="n"/>
+      <c r="F52" s="25" t="n"/>
+      <c r="G52" s="25" t="n"/>
+      <c r="H52" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -41076,7 +41076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="23.5" customWidth="1" style="4" min="1" max="1"/>
@@ -42372,6 +42372,100 @@
       <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Odrębna ścieżka od pozwu/nakazu. Nie generować sprzeciwu ani odpowiedzi na pozew; priorytetem są wyjaśnienia, dowody, okres pełnienia funkcji i przesłanki wyłączające odpowiedzialność.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WYROK_ZAOCZNY_SPOLKA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Wyrok zaoczny przeciwko spółce</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sąd</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>spółka</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>wyrok zaoczny; w imieniu rzeczypospolitej polskiej; zasądza; rygor natychmiastowej wykonalności; sprzeciw; spółka z o.o.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>w imieniu rzeczypospolitej polskiej</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>termin na sprzeciw od wyroku zaocznego, zwykle 2 tygodnie od doręczenia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>07.07.2026: wyrok zaoczny to już rozstrzygnięcie sądu (z rygorem natychmiastowej wykonalności), nie preliminaryjny nakaz zapłaty — jedyna ścieżka zaskarżenia to sprzeciw (bez alternatywy zarzuty, która dotyczy tylko nakazu w postępowaniu nakazowym). Lekka integracja: kod K1 i scenariusz bazowy są reużyte z NAKAZ_SPOLKA (patrz doc_processor.py _DOC_TYPE_TO_K1) — bez własnych wierszy w CSV 12; app.py nadpisuje fragmenty tekstu scenariusza (user_summary_base/user_risk_explanation_base/user_practical_meaning_base), żeby poprawnie opisywały wyrok zaoczny, nie nakaz zapłaty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WYROK_ZAOCZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Wyrok zaoczny przeciwko członkowi zarządu</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sąd</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>członek zarządu</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>wyrok zaoczny; w imieniu rzeczypospolitej polskiej; zasądza; rygor natychmiastowej wykonalności; sprzeciw; art. 299 KSH</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>w imieniu rzeczypospolitej polskiej</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>termin na sprzeciw od wyroku zaocznego, zwykle 2 tygodnie od doręczenia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>07.07.2026: jak WYROK_ZAOCZNY_SPOLKA, ale pozwanym jest osoba fizyczna (członek zarządu) — jeden z najwyższych priorytetów. Lekka integracja: kod K1 i scenariusz bazowy reużyte z NAKAZ_CZLONEK_ZARZADU (patrz doc_processor.py _DOC_TYPE_TO_K1), bez własnych wierszy w CSV 12; app.py nadpisuje fragmenty tekstu scenariusza tak, by poprawnie opisywały wyrok zaoczny.</t>
         </is>
       </c>
     </row>

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B4" s="46" t="inlineStr">
         <is>
-          <t>K1 = K1_NAKAZ_CZLONEK_ZARZADU AND K2 = K2_DAYS_LEFT_0_3</t>
+          <t>K1 ∈ {K1_NAKAZ_CZLONEK_ZARZADU, K1_WYROK_ZAOCZNY_CZLONEK_ZARZADU} AND K2 = K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="C4" s="46" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F4" s="46" t="inlineStr">
         <is>
-          <t>Nakaz przeciwko członkowi zarządu z terminem 0–3 dni jest krytyczny.</t>
+          <t>Nakaz (lub wyrok zaoczny, ta sama pilność) przeciwko członkowi zarządu z terminem 0–3 dni jest krytyczny.</t>
         </is>
       </c>
       <c r="G4" s="46" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B6" s="46" t="inlineStr">
         <is>
-          <t>K1 = K1_NAKAZ_CZLONEK_ZARZADU AND K2 = K2_DAYS_LEFT_4_7</t>
+          <t>K1 ∈ {K1_NAKAZ_CZLONEK_ZARZADU, K1_WYROK_ZAOCZNY_CZLONEK_ZARZADU} AND K2 = K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="C6" s="46" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F6" s="46" t="inlineStr">
         <is>
-          <t>Nakaz przeciwko członkowi zarządu i termin 4–7 dni oznaczają co najmniej wysokie ryzyko.</t>
+          <t>Nakaz (lub wyrok zaoczny, ta sama pilność) przeciwko członkowi zarządu i termin 4–7 dni oznaczają co najmniej wysokie ryzyko.</t>
         </is>
       </c>
       <c r="G6" s="46" t="inlineStr">
@@ -42483,7 +42483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="5.625" customWidth="1" style="4" min="1" max="1"/>
@@ -42749,96 +42749,96 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Rodzaj pisma</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Rodzaj pisma, którego dotyczy sprawa</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Wezwanie sądowe (spółka)</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Wyrok zaoczny (spółka)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>K1_WYROK_ZAOCZNY_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>TAK</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Brak</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Ważne, ale niżej niż wezwanie skierowane do członka zarządu.</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Traktowany jak nakaz zapłaty przeciwko spółce (ten sam dwutygodniowy termin na sprzeciw), ale z rygorem natychmiastowej wykonalności.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Rodzaj pisma</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Rodzaj pisma, którego dotyczy sprawa</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Wezwanie sądowe (członek zarządu)</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Wyrok zaoczny (członek zarządu)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>K1_WYROK_ZAOCZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>TAK</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Brak</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Wysoki priorytet, jeżeli zawiera termin reakcji.</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Traktowany jak nakaz zapłaty przeciwko członkowi zarządu (jeden z najwyższych priorytetów), z rygorem natychmiastowej wykonalności.</t>
         </is>
       </c>
     </row>
@@ -42860,12 +42860,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Inne / nie wiem</t>
+          <t>Wezwanie sądowe (spółka)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -42885,34 +42885,34 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Użytkownik może wybrać, gdy nie rozumie dokumentu albo OCR nie pozwala na rozpoznanie.</t>
+          <t>Ważne, ale niżej niż wezwanie skierowane do członka zarządu.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="51.75" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Czas na reakcję</t>
+          <t>Rodzaj pisma</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Ile czasu zostało na reakcję?</t>
+          <t>Rodzaj pisma, którego dotyczy sprawa</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>0–3 dni kalendarzowe</t>
+          <t>Wezwanie sądowe (członek zarządu)</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_0_3</t>
+          <t>K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -42922,44 +42922,44 @@
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>Może być automatycznie wyliczone z daty doręczenia i terminu formalnego.</t>
+          <t>Brak</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Najczęściej o wyniku decyduje czas — nawet dobra obrona nie zadziała, jeśli termin ucieknie.</t>
+          <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Najwyższa pilność.</t>
+          <t>Wysoki priorytet, jeżeli zawiera termin reakcji.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46.5" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Czas na reakcję</t>
+          <t>Rodzaj pisma</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Ile czasu zostało na reakcję?</t>
+          <t>Rodzaj pisma, którego dotyczy sprawa</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>4–7 dni kalendarzowych</t>
+          <t>Inne / nie wiem</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_4_7</t>
+          <t>K1_INNE_NIE_WIEM</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -42969,17 +42969,17 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Może być automatycznie wyliczone z daty doręczenia i terminu formalnego.</t>
+          <t>Brak</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Najczęściej o wyniku decyduje czas — nawet dobra obrona nie zadziała, jeśli termin ucieknie.</t>
+          <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Wysoka pilność.</t>
+          <t>Użytkownik może wybrać, gdy nie rozumie dokumentu albo OCR nie pozwala na rozpoznanie.</t>
         </is>
       </c>
     </row>
@@ -43001,12 +43001,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>8–14 dni kalendarzowych</t>
+          <t>0–3 dni kalendarzowe</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -43026,7 +43026,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Umiarkowana pilność.</t>
+          <t>Najwyższa pilność.</t>
         </is>
       </c>
     </row>
@@ -43048,12 +43048,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Ponad 14 dni kalendarzowych</t>
+          <t>4–7 dni kalendarzowych</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -43073,7 +43073,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Niska pilność, ale zależna od typu dokumentu.</t>
+          <t>Wysoka pilność.</t>
         </is>
       </c>
     </row>
@@ -43095,12 +43095,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem / nie udało się ustalić</t>
+          <t>8–14 dni kalendarzowych</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -43110,7 +43110,7 @@
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Stosować, gdy brak daty doręczenia, brak terminu albo OCR nie pozwala ustalić danych.</t>
+          <t>Może być automatycznie wyliczone z daty doręczenia i terminu formalnego.</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -43120,195 +43120,195 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Brak wiedzy o terminie zwiększa ostrożność oceny.</t>
+          <t>Umiarkowana pilność.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46.5" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>K2A</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Data doręczenia</t>
+          <t>Czas na reakcję</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Znam datę doręczenia — policz, ile czasu zostało</t>
+          <t>Ile czasu zostało na reakcję?</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Tak, znam datę doręczenia</t>
+          <t>Ponad 14 dni kalendarzowych</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>K2A_DELIVERY_DATE_KNOWN</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>Jeżeli użytkownik zaznaczy, pokaż kalendarz daty doręczenia.</t>
+          <t>Może być automatycznie wyliczone z daty doręczenia i terminu formalnego.</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Data doręczenia pozwala obliczyć faktyczny czas pozostały na reakcję.</t>
+          <t>Najczęściej o wyniku decyduje czas — nawet dobra obrona nie zadziała, jeśli termin ucieknie.</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>To nie jest osobna punktowana odpowiedź, tylko dane pomocnicze do K2.</t>
+          <t>Niska pilność, ale zależna od typu dokumentu.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="47.25" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>K2A</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Data doręczenia</t>
+          <t>Czas na reakcję</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Znam datę doręczenia — policz, ile czasu zostało</t>
+          <t>Ile czasu zostało na reakcję?</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Nie znam daty doręczenia</t>
+          <t>Nie wiem / nie udało się ustalić</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>K2A_DELIVERY_DATE_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>Jeżeli użytkownik nie zna daty, K2 może pozostać jako „nie wiem”.</t>
+          <t>Stosować, gdy brak daty doręczenia, brak terminu albo OCR nie pozwala ustalić danych.</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Data doręczenia pozwala obliczyć faktyczny czas pozostały na reakcję.</t>
+          <t>Najczęściej o wyniku decyduje czas — nawet dobra obrona nie zadziała, jeśli termin ucieknie.</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Brak daty doręczenia powinien zwiększyć ostrożność oceny.</t>
+          <t>Brak wiedzy o terminie zwiększa ostrożność oceny.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2A</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Potrzebne wsparcie</t>
+          <t>Data doręczenia</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Jakiego wsparcia teraz potrzebujesz?</t>
+          <t>Znam datę doręczenia — policz, ile czasu zostało</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Tylko wstępna ocena bez wysyłki dokumentów</t>
+          <t>Tak, znam datę doręczenia</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>K3_SUPPORT_BASIC_NO_DOCS</t>
+          <t>K2A_DELIVERY_DATE_KNOWN</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>Brak</t>
+          <t>Jeżeli użytkownik zaznaczy, pokaż kalendarz daty doręczenia.</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Ocena bez dokumentów może być tylko orientacyjna. Audyt 48h daje większą pewność, ale wymaga przesłania kompletu dokumentów.</t>
+          <t>Data doręczenia pozwala obliczyć faktyczny czas pozostały na reakcję.</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Użytkownik jest jeszcze daleko od Audytu 48h.</t>
+          <t>To nie jest osobna punktowana odpowiedź, tylko dane pomocnicze do K2.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2A</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Potrzebne wsparcie</t>
+          <t>Data doręczenia</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Jakiego wsparcia teraz potrzebujesz?</t>
+          <t>Znam datę doręczenia — policz, ile czasu zostało</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Wstępna ocena teraz + dokumenty dosyłam później</t>
+          <t>Nie znam daty doręczenia</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>K3_SUPPORT_NOW_DOCS_LATER</t>
+          <t>K2A_DELIVERY_DATE_UNKNOWN</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>Brak</t>
+          <t>Jeżeli użytkownik nie zna daty, K2 może pozostać jako „nie wiem”.</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Ocena bez dokumentów może być tylko orientacyjna. Audyt 48h daje większą pewność, ale wymaga przesłania kompletu dokumentów.</t>
+          <t>Data doręczenia pozwala obliczyć faktyczny czas pozostały na reakcję.</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Dobry moment na CTA do Audytu 48h.</t>
+          <t>Brak daty doręczenia powinien zwiększyć ostrożność oceny.</t>
         </is>
       </c>
     </row>
@@ -43330,12 +43330,12 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Jestem gotowy wysłać dokumenty i wejść w Audyt 48h</t>
+          <t>Tylko wstępna ocena bez wysyłki dokumentów</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>K3_READY_FOR_AUDIT_48H</t>
+          <t>K3_SUPPORT_BASIC_NO_DOCS</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -43355,34 +43355,34 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Użytkownik jest najbliżej konwersji.</t>
+          <t>Użytkownik jest jeszcze daleko od Audytu 48h.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="38.25" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Status w zarządzie</t>
+          <t>Potrzebne wsparcie</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Status w zarządzie w okresie sprawy</t>
+          <t>Jakiego wsparcia teraz potrzebujesz?</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Nadal pełnię funkcję</t>
+          <t>Wstępna ocena teraz + dokumenty dosyłam później</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_ACTIVE</t>
+          <t>K3_SUPPORT_NOW_DOCS_LATER</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -43392,44 +43392,44 @@
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>Jeżeli wybrane, K5 ustaw jako „Nie dotyczy”.</t>
+          <t>Brak</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Status i daty pełnienia funkcji wpływają na ryzyka oraz na to, co warto zabezpieczyć dowodowo.</t>
+          <t>Ocena bez dokumentów może być tylko orientacyjna. Audyt 48h daje większą pewność, ale wymaga przesłania kompletu dokumentów.</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>K5 nie powinien być wymagany.</t>
+          <t>Dobry moment na CTA do Audytu 48h.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Status w zarządzie</t>
+          <t>Potrzebne wsparcie</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Status w zarządzie w okresie sprawy</t>
+          <t>Jakiego wsparcia teraz potrzebujesz?</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Była rezygnacja / odwołanie</t>
+          <t>Jestem gotowy wysłać dokumenty i wejść w Audyt 48h</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_RESIGNED</t>
+          <t>K3_READY_FOR_AUDIT_48H</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -43439,17 +43439,17 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Jeżeli wybrane, pokaż K5.</t>
+          <t>Brak</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Status i daty pełnienia funkcji wpływają na ryzyka oraz na to, co warto zabezpieczyć dowodowo.</t>
+          <t>Ocena bez dokumentów może być tylko orientacyjna. Audyt 48h daje większą pewność, ale wymaga przesłania kompletu dokumentów.</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>K5 powinien być obowiązkowy.</t>
+          <t>Użytkownik jest najbliżej konwersji.</t>
         </is>
       </c>
     </row>
@@ -43471,12 +43471,12 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem / trudno powiedzieć</t>
+          <t>Nadal pełnię funkcję</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_UNKNOWN</t>
+          <t>K4_BOARD_ACTIVE</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -43486,7 +43486,7 @@
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
-          <t>Można pokazać K5 jako opcjonalny albo ustawić K5_UNKNOWN.</t>
+          <t>Jeżeli wybrane, K5 ustaw jako „Nie dotyczy”.</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -43496,101 +43496,101 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Niepewność statusu zwiększa chaos informacyjny.</t>
+          <t>K5 nie powinien być wymagany.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="51" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Status wpisu w KRS</t>
+          <t>Status w zarządzie</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Czy zmiana została ujawniona w KRS?</t>
+          <t>Status w zarządzie w okresie sprawy</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Tak — wpis w KRS widnieje</t>
+          <t>Była rezygnacja / odwołanie</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_UPDATED</t>
+          <t>K4_BOARD_RESIGNED</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>WARUNKOWO</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>Obowiązkowe tylko, gdy K4 = K4_BOARD_RESIGNED.</t>
+          <t>Jeżeli wybrane, pokaż K5.</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>W praktyce wiele sytuacji opiera się o wpis w KRS — brak aktualizacji potrafi zwiększać chaos formalny.</t>
+          <t>Status i daty pełnienia funkcji wpływają na ryzyka oraz na to, co warto zabezpieczyć dowodowo.</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Najniższy poziom chaosu w tym kroku.</t>
+          <t>K5 powinien być obowiązkowy.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="51" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Status wpisu w KRS</t>
+          <t>Status w zarządzie</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Czy zmiana została ujawniona w KRS?</t>
+          <t>Status w zarządzie w okresie sprawy</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Nie — brak aktualnego wpisu w KRS</t>
+          <t>Nie wiem / trudno powiedzieć</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_NOT_UPDATED</t>
+          <t>K4_BOARD_UNKNOWN</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>WARUNKOWO</t>
+          <t>TAK</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>Obowiązkowe tylko, gdy K4 = K4_BOARD_RESIGNED.</t>
+          <t>Można pokazać K5 jako opcjonalny albo ustawić K5_UNKNOWN.</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>W praktyce wiele sytuacji opiera się o wpis w KRS — brak aktualizacji potrafi zwiększać chaos formalny.</t>
+          <t>Status i daty pełnienia funkcji wpływają na ryzyka oraz na to, co warto zabezpieczyć dowodowo.</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Podwyższa chaos i niepewność formalną.</t>
+          <t>Niepewność statusu zwiększa chaos informacyjny.</t>
         </is>
       </c>
     </row>
@@ -43612,12 +43612,12 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem</t>
+          <t>Tak — wpis w KRS widnieje</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_UNKNOWN</t>
+          <t>K5_KRS_UPDATED</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -43627,7 +43627,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>Obowiązkowe tylko, gdy K4 = K4_BOARD_RESIGNED albo gdy użytkownik chce uzupełnić informację.</t>
+          <t>Obowiązkowe tylko, gdy K4 = K4_BOARD_RESIGNED.</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -43637,7 +43637,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Zwiększa ostrożność oceny.</t>
+          <t>Najniższy poziom chaosu w tym kroku.</t>
         </is>
       </c>
     </row>
@@ -43659,22 +43659,22 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Nie dotyczy</t>
+          <t>Nie — brak aktualnego wpisu w KRS</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>K5_NOT_APPLICABLE</t>
+          <t>K5_KRS_NOT_UPDATED</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>WARUNKOWO</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Automatycznie ustaw, gdy K4 = K4_BOARD_ACTIVE.</t>
+          <t>Obowiązkowe tylko, gdy K4 = K4_BOARD_RESIGNED.</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -43684,101 +43684,101 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Wartość techniczna potrzebna do scenariuszy.</t>
+          <t>Podwyższa chaos i niepewność formalną.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Cel klienta</t>
+          <t>Status wpisu w KRS</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Jaki jest Twój główny cel?</t>
+          <t>Czy zmiana została ujawniona w KRS?</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Chcę ocenić, czy mam realne podstawy obrony</t>
+          <t>Nie wiem</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_DEFENSE</t>
+          <t>K5_KRS_UNKNOWN</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>WARUNKOWO</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>Brak</t>
+          <t>Obowiązkowe tylko, gdy K4 = K4_BOARD_RESIGNED albo gdy użytkownik chce uzupełnić informację.</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Cel pomaga dobrać charakter komunikatu: ocena szans, bezpieczne przygotowanie obrony, konkretne pismo procesowe albo uporządkowanie sytuacji.</t>
+          <t>W praktyce wiele sytuacji opiera się o wpis w KRS — brak aktualizacji potrafi zwiększać chaos formalny.</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Analiza szans i możliwych argumentów obrony.</t>
+          <t>Zwiększa ostrożność oceny.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Cel klienta</t>
+          <t>Status wpisu w KRS</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Jaki jest Twój główny cel?</t>
+          <t>Czy zmiana została ujawniona w KRS?</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Chcę zyskać czas na przygotowanie obrony</t>
+          <t>Nie dotyczy</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_BUY_TIME</t>
+          <t>K5_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>TAK</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>Brak</t>
+          <t>Automatycznie ustaw, gdy K4 = K4_BOARD_ACTIVE.</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Cel pomaga dobrać charakter komunikatu: ocena szans, bezpieczne przygotowanie obrony, konkretne pismo procesowe albo uporządkowanie sytuacji.</t>
+          <t>W praktyce wiele sytuacji opiera się o wpis w KRS — brak aktualizacji potrafi zwiększać chaos formalny.</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Chodzi o legalne wykorzystanie dostępnych środków procesowych, aby zebrać dokumenty i przygotować obronę — nie o nadużycie prawa.</t>
+          <t>Wartość techniczna potrzebna do scenariuszy.</t>
         </is>
       </c>
     </row>
@@ -43800,12 +43800,12 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Chcę przygotować odpowiednie pismo procesowe</t>
+          <t>Chcę ocenić, czy mam realne podstawy obrony</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_PROCEDURAL_LETTER</t>
+          <t>K6_GOAL_DEFENSE</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -43825,7 +43825,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Cel praktyczny: sprzeciw, odpowiedź na pozew albo inne właściwe pismo zależnie od dokumentu.</t>
+          <t>Analiza szans i możliwych argumentów obrony.</t>
         </is>
       </c>
     </row>
@@ -43847,12 +43847,12 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Potrzebuję planu działania i oceny szans</t>
+          <t>Chcę zyskać czas na przygotowanie obrony</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_PLAN</t>
+          <t>K6_GOAL_BUY_TIME</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -43872,7 +43872,7 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Plan działania i ocena szans po uporządkowaniu dokumentów, terminu oraz możliwych zarzutów.</t>
+          <t>Chodzi o legalne wykorzystanie dostępnych środków procesowych, aby zebrać dokumenty i przygotować obronę — nie o nadużycie prawa.</t>
         </is>
       </c>
     </row>
@@ -43894,12 +43894,12 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem — potrzebuję uporządkowania sytuacji</t>
+          <t>Chcę przygotować odpowiednie pismo procesowe</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_UNKNOWN</t>
+          <t>K6_GOAL_PROCEDURAL_LETTER</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -43919,34 +43919,34 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Opcja dla osoby, która nie potrafi jeszcze wybrać strategii.</t>
+          <t>Cel praktyczny: sprzeciw, odpowiedź na pozew albo inne właściwe pismo zależnie od dokumentu.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36.75" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Kwota roszczenia</t>
+          <t>Cel klienta</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Jaka jest kwota roszczenia wskazana w dokumencie?</t>
+          <t>Jaki jest Twój główny cel?</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem / nie widzę kwoty</t>
+          <t>Potrzebuję planu działania i oceny szans</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_UNKNOWN</t>
+          <t>K6_GOAL_PLAN</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -43961,39 +43961,39 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Kwota wpływa na ciężar gatunkowy sprawy, skalę ryzyka finansowego i priorytet działań.</t>
+          <t>Cel pomaga dobrać charakter komunikatu: ocena szans, bezpieczne przygotowanie obrony, konkretne pismo procesowe albo uporządkowanie sytuacji.</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Zwiększa niepewność i ostrożność oceny.</t>
+          <t>Plan działania i ocena szans po uporządkowaniu dokumentów, terminu oraz możliwych zarzutów.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36.75" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>K7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Kwota roszczenia</t>
+          <t>Cel klienta</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Jaka jest kwota roszczenia wskazana w dokumencie?</t>
+          <t>Jaki jest Twój główny cel?</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Do 10 000 zł</t>
+          <t>Nie wiem — potrzebuję uporządkowania sytuacji</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_UP_TO_10K</t>
+          <t>K6_GOAL_UNKNOWN</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -44008,12 +44008,12 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Kwota wpływa na ciężar gatunkowy sprawy, skalę ryzyka finansowego i priorytet działań.</t>
+          <t>Cel pomaga dobrać charakter komunikatu: ocena szans, bezpieczne przygotowanie obrony, konkretne pismo procesowe albo uporządkowanie sytuacji.</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Niska wartość roszczenia, ale nadal oceniać termin i typ dokumentu.</t>
+          <t>Opcja dla osoby, która nie potrafi jeszcze wybrać strategii.</t>
         </is>
       </c>
     </row>
@@ -44035,12 +44035,12 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>10 001 – 50 000 zł</t>
+          <t>Nie wiem / nie widzę kwoty</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_10K_50K</t>
+          <t>K7_AMOUNT_UNKNOWN</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -44060,7 +44060,7 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Umiarkowana wartość roszczenia.</t>
+          <t>Zwiększa niepewność i ostrożność oceny.</t>
         </is>
       </c>
     </row>
@@ -44082,12 +44082,12 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>50 001 – 150 000 zł</t>
+          <t>Do 10 000 zł</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_50K_150K</t>
+          <t>K7_AMOUNT_UP_TO_10K</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -44107,7 +44107,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Istotna wartość roszczenia.</t>
+          <t>Niska wartość roszczenia, ale nadal oceniać termin i typ dokumentu.</t>
         </is>
       </c>
     </row>
@@ -44129,12 +44129,12 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>150 001 – 500 000 zł</t>
+          <t>10 001 – 50 000 zł</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_150K_500K</t>
+          <t>K7_AMOUNT_10K_50K</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -44154,7 +44154,7 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Wysoka wartość roszczenia — podnosi ciężar sprawy.</t>
+          <t>Umiarkowana wartość roszczenia.</t>
         </is>
       </c>
     </row>
@@ -44176,12 +44176,12 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Powyżej 500 000 zł</t>
+          <t>50 001 – 150 000 zł</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_ABOVE_500K</t>
+          <t>K7_AMOUNT_50K_150K</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -44201,148 +44201,148 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Bardzo wysoka wartość roszczenia — znacząco podnosi ciężar sprawy.</t>
+          <t>Istotna wartość roszczenia.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="64.5" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Kwota roszczenia</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Jaka jest kwota roszczenia wskazana w dokumencie?</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>150 001 – 500 000 zł</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>K7_AMOUNT_150K_500K</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>Brak</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Kwota wpływa na ciężar gatunkowy sprawy, skalę ryzyka finansowego i priorytet działań.</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Wysoka wartość roszczenia — podnosi ciężar sprawy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Kwota roszczenia</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Jaka jest kwota roszczenia wskazana w dokumencie?</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Powyżej 500 000 zł</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>K7_AMOUNT_ABOVE_500K</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>Brak</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Kwota wpływa na ciężar gatunkowy sprawy, skalę ryzyka finansowego i priorytet działań.</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Bardzo wysoka wartość roszczenia — znacząco podnosi ciężar sprawy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Rodzaj pisma</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Rodzaj pisma, którego dotyczy sprawa</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Pismo z ZUS / urzędu dotyczące odpowiedzialności członka zarządu</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>TAK</t>
         </is>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G40" s="15" t="inlineStr">
         <is>
           <t>Brak</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Pisma organów publicznych dotyczące odpowiedzialności członka zarządu wymagają innej ścieżki niż pozew/nakaz sądowy.</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>Nowa kategoria v35: zawiadomienie/wezwanie/decyzja ZUS lub urzędu skarbowego dotyczące zaległości spółki i odpowiedzialności członka zarządu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Rodzaj pisma</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Pismo komornicze (spółka)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Brak</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Nowa kategoria 05.07.2026: pismo komornika w egzekucji przeciwko spółce (zawiadomienie o wszczęciu egzekucji, zajęcie rachunku, wezwanie do wykazu majątku itp.). Egzekucja przeciwko spółce to przedpole odpowiedzialności z art. 299 KSH — jeżeli okaże się bezskuteczna, wierzyciel może dochodzić zapłaty od członków zarządu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Rodzaj pisma</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Pismo komornicze (członek zarządu)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Brak</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Nowa kategoria 05.07.2026: pismo komornika w egzekucji z majątku osobistego członka zarządu — najpóźniejszy etap sprawy, istnieje tytuł wykonawczy przeciwko osobie fizycznej. Jeden z najwyższych ciężarów gatunkowych.</t>
         </is>
       </c>
     </row>
@@ -44364,30 +44364,124 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>Pismo komornicze (spółka)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Brak</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Nowa kategoria 05.07.2026: pismo komornika w egzekucji przeciwko spółce (zawiadomienie o wszczęciu egzekucji, zajęcie rachunku, wezwanie do wykazu majątku itp.). Egzekucja przeciwko spółce to przedpole odpowiedzialności z art. 299 KSH — jeżeli okaże się bezskuteczna, wierzyciel może dochodzić zapłaty od członków zarządu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rodzaj pisma</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pismo komornicze (członek zarządu)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Brak</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Nowa kategoria 05.07.2026: pismo komornika w egzekucji z majątku osobistego członka zarządu — najpóźniejszy etap sprawy, istnieje tytuł wykonawczy przeciwko osobie fizycznej. Jeden z najwyższych ciężarów gatunkowych.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rodzaj pisma</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>Wezwanie przedsądowe (członek zarządu)</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>TAK</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Brak</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Nowa kategoria 06.07.2026: przedsądowe wezwanie do zapłaty powołujące się na art. 299 KSH i/lub bezskuteczność egzekucji wobec spółki, skierowane do członka zarządu — poważny sygnał, ale to jeszcze nie dokument sądowy.</t>
         </is>
@@ -44407,7 +44501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="27.5" customWidth="1" style="4" min="1" max="1"/>
@@ -44614,82 +44708,82 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Wezwanie sądowe (spółka)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>K1_WYROK_ZAOCZNY_SPOLKA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Wyrok zaoczny (spółka)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>K1_document_weight</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5" t="n">
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Ważne jako dokument procesowy, ale zwykle niżej niż dokument skierowany do członka zarządu.</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Traktowany jak nakaz przeciwko spółce — może mieć znaczenie dla późniejszej odpowiedzialności z art. 299 KSH, ale nie jest tak pilny jak wobec członka zarządu.</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Wezwanie sądowe (członek zarządu)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>K1_WYROK_ZAOCZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wyrok zaoczny (członek zarządu)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>K1_document_weight</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="5" t="n">
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Dokument skierowany bezpośrednio do członka zarządu, często wymagający reakcji.</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Jeden z najwyższych ciężarów gatunkowych — rygor natychmiastowej wykonalności, biegnie termin na sprzeciw.</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+          <t>K1_WEZWANIE_SADOWE_SPOLKA</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Pismo z ZUS / urzędu dotyczące odpowiedzialności członka zarządu</t>
+          <t>Wezwanie sądowe (spółka)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -44698,7 +44792,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
@@ -44708,7 +44802,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Pismo organu publicznego dotyczące możliwej osobistej odpowiedzialności członka zarządu ma wysoki ciężar gatunkowy i odrębną ścieżkę oceny; nie traktować jak pozew ani nakaz zapłaty.</t>
+          <t>Ważne jako dokument procesowy, ale zwykle niżej niż dokument skierowany do członka zarządu.</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -44718,12 +44812,12 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>K1_INNE_NIE_WIEM</t>
+          <t>K1_WEZWANIE_SADOWE_CZLONEK_ZARZADU</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Inne / nie wiem</t>
+          <t>Wezwanie sądowe (członek zarządu)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -44732,7 +44826,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>0</v>
@@ -44742,7 +44836,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Niepewność co do rodzaju dokumentu powinna zwiększyć ostrożność, ale nie przesądza wysokiego ciężaru dokumentu.</t>
+          <t>Dokument skierowany bezpośrednio do członka zarządu, często wymagający reakcji.</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -44750,82 +44844,82 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pismo komornicze (spółka)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>K1_ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Pismo z ZUS / urzędu dotyczące odpowiedzialności członka zarządu</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>K1_document_weight</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Pismo komornicze w egzekucji przeciwko spółce — zaawansowany etap sprawy i przedpole odpowiedzialności z art. 299 KSH, ale bez bezpośredniego roszczenia wobec członka zarządu (analogicznie do nakazu przeciwko spółce).</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Pismo organu publicznego dotyczące możliwej osobistej odpowiedzialności członka zarządu ma wysoki ciężar gatunkowy i odrębną ścieżkę oceny; nie traktować jak pozew ani nakaz zapłaty.</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pismo komornicze (członek zarządu)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>K1_INNE_NIE_WIEM</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Inne / nie wiem</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>K1_document_weight</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Egzekucja z majątku osobistego członka zarządu na podstawie tytułu wykonawczego — jeden z najwyższych ciężarów gatunkowych.</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Niepewność co do rodzaju dokumentu powinna zwiększyć ostrożność, ale nie przesądza wysokiego ciężaru dokumentu.</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+          <t>K1_PISMO_KOMORNIK_SPOLKA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wezwanie przedsądowe (członek zarządu)</t>
+          <t>Pismo komornicze (spółka)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -44844,7 +44938,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Przedsądowe wezwanie powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki — poważnie wymierzone bezpośrednio w członka zarządu, ale to jeszcze nie dokument sądowy (analogicznie do wezwania sądowego skierowanego do członka zarządu).</t>
+          <t>Pismo komornicze w egzekucji przeciwko spółce — zaawansowany etap sprawy i przedpole odpowiedzialności z art. 299 KSH, ale bez bezpośredniego roszczenia wobec członka zarządu (analogicznie do nakazu przeciwko spółce).</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -44852,82 +44946,82 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_0_3</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>0–3 dni kalendarzowe</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>K2_urgency</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>K1_PISMO_KOMORNIK_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pismo komornicze (członek zarządu)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>K1_document_weight</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Najwyższa pilność. Bardzo krótki czas na reakcję.</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Egzekucja z majątku osobistego członka zarządu na podstawie tytułu wykonawczego — jeden z najwyższych ciężarów gatunkowych.</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>K2_DAYS_LEFT_4_7</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>4–7 dni kalendarzowych</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>K2_urgency</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>K1_WEZWANIE_PRZEDSADOWE_CZLONEK_ZARZADU</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wezwanie przedsądowe (członek zarządu)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>K1_document_weight</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Wysoka pilność. Jest jeszcze czas, ale sprawa wymaga szybkiego działania.</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Przedsądowe wezwanie powołujące się na art. 299 KSH i bezskuteczność egzekucji wobec spółki — poważnie wymierzone bezpośrednio w członka zarządu, ale to jeszcze nie dokument sądowy (analogicznie do wezwania sądowego skierowanego do członka zarządu).</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_8_14</t>
+          <t>K2_DAYS_LEFT_0_3</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>8–14 dni kalendarzowych</t>
+          <t>0–3 dni kalendarzowe</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -44939,14 +45033,14 @@
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Umiarkowana pilność. Termin wymaga kontroli, ale nie jest jeszcze krytyczny.</t>
+          <t>Najwyższa pilność. Bardzo krótki czas na reakcję.</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -44956,12 +45050,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_ABOVE_14</t>
+          <t>K2_DAYS_LEFT_4_7</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Ponad 14 dni kalendarzowych</t>
+          <t>4–7 dni kalendarzowych</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -44973,14 +45067,14 @@
         <v>0</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Niska pilność czasowa, choć ryzyko może wynikać z rodzaju dokumentu.</t>
+          <t>Wysoka pilność. Jest jeszcze czas, ale sprawa wymaga szybkiego działania.</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -44990,12 +45084,12 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>K2_DAYS_LEFT_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_8_14</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem / nie udało się ustalić</t>
+          <t>8–14 dni kalendarzowych</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -45010,11 +45104,11 @@
         <v>1</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Brak wiedzy o terminie jest ryzykiem samym w sobie. Dlatego przyznajemy 1 punkt za pilność i 1 punkt za niepewność.</t>
+          <t>Umiarkowana pilność. Termin wymaga kontroli, ale nie jest jeszcze krytyczny.</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -45024,17 +45118,17 @@
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>K2A_DELIVERY_DATE_KNOWN</t>
+          <t>K2_DAYS_LEFT_ABOVE_14</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Tak, znam datę doręczenia</t>
+          <t>Ponad 14 dni kalendarzowych</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>K2A_auxiliary</t>
+          <t>K2_urgency</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -45048,7 +45142,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Dane pomocnicze. Nie punktować samodzielnie. Służy do obliczenia K2.</t>
+          <t>Niska pilność czasowa, choć ryzyko może wynikać z rodzaju dokumentu.</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -45058,31 +45152,31 @@
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>K2A_DELIVERY_DATE_UNKNOWN</t>
+          <t>K2_DAYS_LEFT_UNKNOWN</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Nie znam daty doręczenia</t>
+          <t>Nie wiem / nie udało się ustalić</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>K2A_auxiliary</t>
+          <t>K2_urgency</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Brak daty doręczenia zwiększa niepewność.</t>
+          <t>Brak wiedzy o terminie jest ryzykiem samym w sobie. Dlatego przyznajemy 1 punkt za pilność i 1 punkt za niepewność.</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -45092,17 +45186,17 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>K3_SUPPORT_BASIC_NO_DOCS</t>
+          <t>K2A_DELIVERY_DATE_KNOWN</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Tylko wstępna ocena bez wysyłki dokumentów</t>
+          <t>Tak, znam datę doręczenia</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>K3_support_needed</t>
+          <t>K2A_auxiliary</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -45112,11 +45206,11 @@
         <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Ocena bez pełnych dokumentów jest bardziej niepewna.</t>
+          <t>Dane pomocnicze. Nie punktować samodzielnie. Służy do obliczenia K2.</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -45126,17 +45220,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>K3_SUPPORT_NOW_DOCS_LATER</t>
+          <t>K2A_DELIVERY_DATE_UNKNOWN</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Wstępna ocena teraz + dokumenty dosyłam później</t>
+          <t>Nie znam daty doręczenia</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>K3_support_needed</t>
+          <t>K2A_auxiliary</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -45150,7 +45244,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Częściowa gotowość do uporządkowania sprawy.</t>
+          <t>Brak daty doręczenia zwiększa niepewność.</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -45160,12 +45254,12 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>K3_READY_FOR_AUDIT_48H</t>
+          <t>K3_SUPPORT_BASIC_NO_DOCS</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Jestem gotowy wysłać dokumenty i wejść w Audyt 48h</t>
+          <t>Tylko wstępna ocena bez wysyłki dokumentów</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -45180,11 +45274,11 @@
         <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Najmniejsza niepewność organizacyjna, użytkownik jest gotowy do pełniejszej analizy.</t>
+          <t>Ocena bez pełnych dokumentów jest bardziej niepewna.</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -45194,17 +45288,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_ACTIVE</t>
+          <t>K3_SUPPORT_NOW_DOCS_LATER</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Nadal pełnię funkcję</t>
+          <t>Wstępna ocena teraz + dokumenty dosyłam później</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>K4_board_status</t>
+          <t>K3_support_needed</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -45218,7 +45312,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Nadal pełniona funkcja może wymagać uporządkowania sytuacji, ale sama w sobie nie oznacza najwyższego chaosu.</t>
+          <t>Częściowa gotowość do uporządkowania sprawy.</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -45228,17 +45322,17 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_RESIGNED</t>
+          <t>K3_READY_FOR_AUDIT_48H</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Była rezygnacja / odwołanie</t>
+          <t>Jestem gotowy wysłać dokumenty i wejść w Audyt 48h</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>K4_board_status</t>
+          <t>K3_support_needed</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -45248,11 +45342,11 @@
         <v>0</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Rezygnacja/odwołanie wymaga sprawdzenia dat i wpisu w KRS.</t>
+          <t>Najmniejsza niepewność organizacyjna, użytkownik jest gotowy do pełniejszej analizy.</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -45262,12 +45356,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>K4_BOARD_UNKNOWN</t>
+          <t>K4_BOARD_ACTIVE</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem / trudno powiedzieć</t>
+          <t>Nadal pełnię funkcję</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -45282,11 +45376,11 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Niepewność co do statusu w zarządzie istotnie zwiększa chaos informacyjny.</t>
+          <t>Nadal pełniona funkcja może wymagać uporządkowania sytuacji, ale sama w sobie nie oznacza najwyższego chaosu.</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -45296,17 +45390,17 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_UPDATED</t>
+          <t>K4_BOARD_RESIGNED</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Tak — wpis w KRS widnieje</t>
+          <t>Była rezygnacja / odwołanie</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>K5_krs_status</t>
+          <t>K4_board_status</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -45316,11 +45410,11 @@
         <v>0</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Najniższa niepewność formalna w zakresie wpisu KRS.</t>
+          <t>Rezygnacja/odwołanie wymaga sprawdzenia dat i wpisu w KRS.</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -45330,17 +45424,17 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_NOT_UPDATED</t>
+          <t>K4_BOARD_UNKNOWN</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Nie — brak aktualnego wpisu w KRS</t>
+          <t>Nie wiem / trudno powiedzieć</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>K5_krs_status</t>
+          <t>K4_board_status</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -45354,7 +45448,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Brak aktualnego wpisu może zwiększać chaos formalny i ryzyko nieporozumień.</t>
+          <t>Niepewność co do statusu w zarządzie istotnie zwiększa chaos informacyjny.</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -45364,12 +45458,12 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>K5_KRS_UNKNOWN</t>
+          <t>K5_KRS_UPDATED</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem</t>
+          <t>Tak — wpis w KRS widnieje</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -45384,11 +45478,11 @@
         <v>0</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Brak wiedzy o wpisie w KRS wymaga weryfikacji.</t>
+          <t>Najniższa niepewność formalna w zakresie wpisu KRS.</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -45398,12 +45492,12 @@
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>K5_NOT_APPLICABLE</t>
+          <t>K5_KRS_NOT_UPDATED</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Nie dotyczy</t>
+          <t>Nie — brak aktualnego wpisu w KRS</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -45418,11 +45512,11 @@
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Stosować automatycznie, gdy użytkownik nadal pełni funkcję.</t>
+          <t>Brak aktualnego wpisu może zwiększać chaos formalny i ryzyko nieporozumień.</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -45432,17 +45526,17 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_DEFENSE</t>
+          <t>K5_KRS_UNKNOWN</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Chcę ocenić, czy mam realne podstawy obrony</t>
+          <t>Nie wiem</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>K6_goal</t>
+          <t>K5_krs_status</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
@@ -45452,11 +45546,11 @@
         <v>0</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Cel dotyczy merytorycznej oceny podstaw obrony i możliwych zarzutów.</t>
+          <t>Brak wiedzy o wpisie w KRS wymaga weryfikacji.</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -45466,17 +45560,17 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_BUY_TIME</t>
+          <t>K5_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Chcę zyskać czas na przygotowanie obrony</t>
+          <t>Nie dotyczy</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>K6_goal</t>
+          <t>K5_krs_status</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -45490,7 +45584,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Cel wymaga bezpiecznego języka: tylko legalne środki procesowe i faktyczna dokumentacja.</t>
+          <t>Stosować automatycznie, gdy użytkownik nadal pełni funkcję.</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -45500,12 +45594,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_PROCEDURAL_LETTER</t>
+          <t>K6_GOAL_DEFENSE</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Chcę przygotować odpowiednie pismo procesowe</t>
+          <t>Chcę ocenić, czy mam realne podstawy obrony</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -45524,7 +45618,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Cel praktyczny: dobór właściwego pisma zależnie od dokumentu.</t>
+          <t>Cel dotyczy merytorycznej oceny podstaw obrony i możliwych zarzutów.</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -45534,12 +45628,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_PLAN</t>
+          <t>K6_GOAL_BUY_TIME</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Potrzebuję planu działania i oceny szans</t>
+          <t>Chcę zyskać czas na przygotowanie obrony</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -45558,7 +45652,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Cel dotyczy planu kolejnych kroków oraz oceny szans po weryfikacji dokumentów.</t>
+          <t>Cel wymaga bezpiecznego języka: tylko legalne środki procesowe i faktyczna dokumentacja.</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -45568,12 +45662,12 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>K6_GOAL_UNKNOWN</t>
+          <t>K6_GOAL_PROCEDURAL_LETTER</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Nie wiem — potrzebuję uporządkowania sytuacji</t>
+          <t>Chcę przygotować odpowiednie pismo procesowe</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -45588,11 +45682,11 @@
         <v>0</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Niepewność celu zwiększa potrzebę uporządkowania sprawy.</t>
+          <t>Cel praktyczny: dobór właściwego pisma zależnie od dokumentu.</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -45600,110 +45694,110 @@
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>K6_GOAL_PLAN</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Potrzebuję planu działania i oceny szans</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>K6_goal</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Cel dotyczy planu kolejnych kroków oraz oceny szans po weryfikacji dokumentów.</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>K6_GOAL_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Nie wiem — potrzebuję uporządkowania sytuacji</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>K6_goal</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Niepewność celu zwiększa potrzebę uporządkowania sprawy.</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>Treść</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>K7_AMOUNT_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Nie wiem / nie widzę kwoty</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>K7_claim_amount</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Brak kwoty ogranicza pewność oceny; dodać H=1 i W=1.</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>K7_AMOUNT_UP_TO_10K</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Do 10 000 zł</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>K7_claim_amount</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>Niska kwota nie podnosi samodzielnie ciężaru sprawy.</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_10K_50K</t>
+          <t>K7_AMOUNT_UNKNOWN</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>10 001 – 50 000 zł</t>
+          <t>Nie wiem / nie widzę kwoty</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -45718,11 +45812,11 @@
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Kwota umiarkowana — niewielkie podniesienie ciężaru finansowego.</t>
+          <t>Brak kwoty ogranicza pewność oceny; dodać H=1 i W=1.</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -45732,12 +45826,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_50K_150K</t>
+          <t>K7_AMOUNT_UP_TO_10K</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>50 001 – 150 000 zł</t>
+          <t>Do 10 000 zł</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -45756,22 +45850,22 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Kwota istotna — podnosi ciężar sprawy.</t>
+          <t>Niska kwota nie podnosi samodzielnie ciężaru sprawy.</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_150K_500K</t>
+          <t>K7_AMOUNT_10K_50K</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>150 001 – 500 000 zł</t>
+          <t>10 001 – 50 000 zł</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -45790,22 +45884,22 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Wysoka kwota — istotne konsekwencje finansowe.</t>
+          <t>Kwota umiarkowana — niewielkie podniesienie ciężaru finansowego.</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>K7_AMOUNT_ABOVE_500K</t>
+          <t>K7_AMOUNT_50K_150K</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Powyżej 500 000 zł</t>
+          <t>50 001 – 150 000 zł</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -45824,62 +45918,94 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
+          <t>Kwota istotna — podnosi ciężar sprawy.</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>K7_AMOUNT_150K_500K</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>150 001 – 500 000 zł</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>K7_claim_amount</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Wysoka kwota — istotne konsekwencje finansowe.</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>K7_AMOUNT_ABOVE_500K</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Powyżej 500 000 zł</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>K7_claim_amount</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
           <t>Bardzo wysoka kwota — znacząco podnosi ciężar sprawy.</t>
         </is>
       </c>
-      <c r="H43" s="5" t="n">
+      <c r="H45" s="5" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="44" ht="45" customHeight="1">
-      <c r="A44" s="11" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="11" t="n"/>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="25" t="n"/>
-      <c r="B45" s="25" t="n"/>
-      <c r="C45" s="25" t="n"/>
-      <c r="D45" s="25" t="n"/>
-      <c r="E45" s="25" t="n"/>
-      <c r="F45" s="25" t="n"/>
-      <c r="G45" s="25" t="n"/>
-      <c r="H45" s="25" t="n"/>
-    </row>
     <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>Treść</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="n"/>
-      <c r="D46" s="25" t="n"/>
-      <c r="E46" s="25" t="n"/>
-      <c r="F46" s="25" t="n"/>
-      <c r="G46" s="25" t="n"/>
-      <c r="H46" s="25" t="n"/>
+      <c r="A46" s="11" t="n"/>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="11" t="n"/>
     </row>
     <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Zasada liczenia C</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>C liczymy z rodzaju dokumentu i jego ciężaru procesowego.</t>
-        </is>
-      </c>
+      <c r="A47" s="25" t="n"/>
+      <c r="B47" s="25" t="n"/>
       <c r="C47" s="25" t="n"/>
       <c r="D47" s="25" t="n"/>
       <c r="E47" s="25" t="n"/>
@@ -45888,14 +46014,14 @@
       <c r="H47" s="25" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Zasada liczenia P</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>P liczymy przede wszystkim z czasu na reakcję.</t>
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Treść</t>
         </is>
       </c>
       <c r="C48" s="25" t="n"/>
@@ -45908,12 +46034,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Zasada liczenia H</t>
+          <t>Zasada liczenia C</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>H liczymy z niepewności danych, statusu zarządu/KRS i organizacyjnej gotowości.</t>
+          <t>C liczymy z rodzaju dokumentu i jego ciężaru procesowego.</t>
         </is>
       </c>
       <c r="C49" s="25" t="n"/>
@@ -45926,12 +46052,12 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Zasada liczenia W</t>
+          <t>Zasada liczenia P</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>W liczymy z przedziału kwoty roszczenia; W wpływa na ciężar finansowy, ale nie zastępuje oceny terminu i dokumentu.</t>
+          <t>P liczymy przede wszystkim z czasu na reakcję.</t>
         </is>
       </c>
       <c r="C50" s="25" t="n"/>
@@ -45942,14 +46068,14 @@
       <c r="H50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="inlineStr">
-        <is>
-          <t>Wynik końcowy</t>
-        </is>
-      </c>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>S = C + P + H + W.</t>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Zasada liczenia H</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>H liczymy z niepewności danych, statusu zarządu/KRS i organizacyjnej gotowości.</t>
         </is>
       </c>
       <c r="C51" s="25" t="n"/>
@@ -45960,14 +46086,50 @@
       <c r="H51" s="25" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="25" t="n"/>
-      <c r="B52" s="25" t="n"/>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Zasada liczenia W</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>W liczymy z przedziału kwoty roszczenia; W wpływa na ciężar finansowy, ale nie zastępuje oceny terminu i dokumentu.</t>
+        </is>
+      </c>
       <c r="C52" s="25" t="n"/>
       <c r="D52" s="25" t="n"/>
       <c r="E52" s="25" t="n"/>
       <c r="F52" s="25" t="n"/>
       <c r="G52" s="25" t="n"/>
       <c r="H52" s="25" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>Wynik końcowy</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>S = C + P + H + W.</t>
+        </is>
+      </c>
+      <c r="C53" s="25" t="n"/>
+      <c r="D53" s="25" t="n"/>
+      <c r="E53" s="25" t="n"/>
+      <c r="F53" s="25" t="n"/>
+      <c r="G53" s="25" t="n"/>
+      <c r="H53" s="25" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="n"/>
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="25" t="n"/>
+      <c r="D54" s="25" t="n"/>
+      <c r="E54" s="25" t="n"/>
+      <c r="F54" s="25" t="n"/>
+      <c r="G54" s="25" t="n"/>
+      <c r="H54" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -41076,7 +41076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="23.5" customWidth="1" style="4" min="1" max="1"/>
@@ -42141,66 +42141,66 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>UMOWA_FAKTURA_KORESPONDENCJA</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Umowa, faktura lub korespondencja handlowa</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>pomocniczy</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>nieustalony</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>faktura; umowa; zamówienie; protokół; e-mail; nota księgowa; potwierdzenie przelewu</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>dokument gospodarczy, nie procesowy</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>nie dotyczy</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>POSTANOWIENIE_KRS_Z_URZEDU</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Postanowienie sądu rejestrowego KRS (z urzędu)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>nieistotny</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>spółka</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>rozwiązanie podmiotu bez likwidacji; art. 25a; art. 25b; ustawy o Krajowym Rejestrze Sądowym; postępowanie z urzędu; wykreślenie z rejestru; sąd rejestrowy</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>sprawy z urzędu przy uczestnictwie, brak powoda — sąd rejestrowy KRS orzeka bez sporu dwustronnego</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>14 dni na wykazanie majątku/działalności, ale to nie jest termin na odpowiedź na roszczenie</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>NIE</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>Dokument pomocniczy. Może mieć znaczenie w Audycie 48h, ale nie powinien być dokumentem głównym.</t>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>14.07.2026: postępowanie rejestrowe KRS o wykreślenie nieaktywnej/bezmajątkowej spółki z urzędu — NIE jest sporem o zapłatę (brak powoda, brak kwoty roszczenia). Wykrywane głównie strukturalnie w doc_classifier.py (sad_organ zawiera "Rejestru Sądowego"/"rejestrowy" + powod=None + "z urzędu"/tytuł POSTANOWIENIE), słowa kluczowe tu są fallbackiem gdy ekstrakcja AI zawiedzie. app.py pokazuje dedykowany baner zamiast tabeli/analizy — dokument dotyczy spółki, ale samo wykreślenie bez majątku może być kontekstem dla przyszłego art. 299 KSH, gdyby pojawił się wierzyciel.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>DOKUMENT_NIEPRAWNY</t>
+          <t>UMOWA_FAKTURA_KORESPONDENCJA</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Dokument nieprawny albo obcy tematycznie</t>
+          <t>Umowa, faktura lub korespondencja handlowa</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>nieistotny</t>
+          <t>pomocniczy</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -42210,12 +42210,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>bilet; paragon; reklama; artykuł; notatka; dokument niezwiązany ze sprawą</t>
+          <t>faktura; umowa; zamówienie; protokół; e-mail; nota księgowa; potwierdzenie przelewu</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>brak cech dokumentu prawnego lub sprawy zarządu/spółki</t>
+          <t>dokument gospodarczy, nie procesowy</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -42228,242 +42228,289 @@
           <t>NIE</t>
         </is>
       </c>
-      <c r="I25" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Dokument pomocniczy. Może mieć znaczenie w Audycie 48h, ale nie powinien być dokumentem głównym.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="140.4499969482422" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>DOKUMENT_NIEPRAWNY</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Dokument nieprawny albo obcy tematycznie</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>nieistotny</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>nieustalony</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>bilet; paragon; reklama; artykuł; notatka; dokument niezwiązany ze sprawą</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>brak cech dokumentu prawnego lub sprawy zarządu/spółki</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>nie dotyczy</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
+      <c r="I26" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>DOKUMENT_NIECZYTELNY</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Dokument nieczytelny</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>techniczny</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>nieustalony</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>brak odczytu; OCR niepewny; tekst nieczytelny; skan bardzo słabej jakości</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>bardzo niska jakość odczytu</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>nieustalony</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>NIE</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Kalkulator powinien poprosić o lepszy skan albo umożliwić ręczne uzupełnienie danych.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>PISMO_PROCESOWE_SADOWE</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Pismo procesowe w toczącym się postępowaniu sądowym</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>sąd</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>członek zarządu / spółka</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>pismo przygotowawcze; odpowiedź na sprzeciw; w odpowiedzi na sprzeciw; replika; podtrzymuję; wnoszę o oddalenie; postępowanie w toku; sprawa w toku; dalsze pisma</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>pismo przygotowawcze; odpowiedź na sprzeciw; w odpowiedzi na sprzeciw</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>termin wskazany w wezwaniu sądu jeśli dotyczy</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>WARUNKOWO</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Dokument wskazuje na kontynuację sporu sądowego. Bez kompletnej dokumentacji (pozwu, sprzeciwu, wcześniejszych pism) rzetelna ocena jest niemożliwa. Jeżeli jest dokumentem głównym — przekierować do Audytu 48h z pełną dokumentacją.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>ORGAN_PUBLICZNY_CZLONEK_ZARZADU</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Pismo z ZUS / urzędu dotyczące odpowiedzialności członka zarządu</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>organ publiczny</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>członek zarządu</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>ZUS; Zakład Ubezpieczeń Społecznych; urząd skarbowy; naczelnik urzędu skarbowego; odpowiedzialność osoby trzeciej; odpowiedzialność członka zarządu; zaległości składkowe; zaległości podatkowe; Ordynacja podatkowa; ustawa o systemie ubezpieczeń społecznych; wezwanie do wyjaśnień; zawiadomienie o wszczęciu postępowania; decyzja</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>organ publiczny informuje o wszczęciu postępowania albo wzywa członka zarządu do wyjaśnień w sprawie odpowiedzialności za zobowiązania spółki</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>termin wskazany w piśmie organu, często na złożenie wyjaśnień albo dokumentów</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>TAK</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>Odrębna ścieżka od pozwu/nakazu. Nie generować sprzeciwu ani odpowiedzi na pozew; priorytetem są wyjaśnienia, dowody, okres pełnienia funkcji i przesłanki wyłączające odpowiedzialność.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>WYROK_ZAOCZNY_SPOLKA</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Wyrok zaoczny przeciwko spółce</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>sąd</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>spółka</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>wyrok zaoczny; w imieniu rzeczypospolitej polskiej; zasądza; rygor natychmiastowej wykonalności; sprzeciw; spółka z o.o.</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>w imieniu rzeczypospolitej polskiej</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>termin na sprzeciw od wyroku zaocznego, zwykle 2 tygodnie od doręczenia</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>TAK</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>07.07.2026: wyrok zaoczny to już rozstrzygnięcie sądu (z rygorem natychmiastowej wykonalności), nie preliminaryjny nakaz zapłaty — jedyna ścieżka zaskarżenia to sprzeciw (bez alternatywy zarzuty, która dotyczy tylko nakazu w postępowaniu nakazowym). Lekka integracja: kod K1 i scenariusz bazowy są reużyte z NAKAZ_SPOLKA (patrz doc_processor.py _DOC_TYPE_TO_K1) — bez własnych wierszy w CSV 12; app.py nadpisuje fragmenty tekstu scenariusza (user_summary_base/user_risk_explanation_base/user_practical_meaning_base), żeby poprawnie opisywały wyrok zaoczny, nie nakaz zapłaty.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>WYROK_ZAOCZNY_SPOLKA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Wyrok zaoczny przeciwko spółce</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sąd</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>spółka</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>wyrok zaoczny; w imieniu rzeczypospolitej polskiej; zasądza; rygor natychmiastowej wykonalności; sprzeciw; spółka z o.o.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>w imieniu rzeczypospolitej polskiej</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>termin na sprzeciw od wyroku zaocznego, zwykle 2 tygodnie od doręczenia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>07.07.2026: wyrok zaoczny to już rozstrzygnięcie sądu (z rygorem natychmiastowej wykonalności), nie preliminaryjny nakaz zapłaty — jedyna ścieżka zaskarżenia to sprzeciw (bez alternatywy zarzuty, która dotyczy tylko nakazu w postępowaniu nakazowym). Lekka integracja: kod K1 i scenariusz bazowy są reużyte z NAKAZ_SPOLKA (patrz doc_processor.py _DOC_TYPE_TO_K1) — bez własnych wierszy w CSV 12; app.py nadpisuje fragmenty tekstu scenariusza (user_summary_base/user_risk_explanation_base/user_practical_meaning_base), żeby poprawnie opisywały wyrok zaoczny, nie nakaz zapłaty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>WYROK_ZAOCZNY_CZLONEK_ZARZADU</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Wyrok zaoczny przeciwko członkowi zarządu</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>sąd</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>członek zarządu</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>wyrok zaoczny; w imieniu rzeczypospolitej polskiej; zasądza; rygor natychmiastowej wykonalności; sprzeciw; art. 299 KSH</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>w imieniu rzeczypospolitej polskiej</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>termin na sprzeciw od wyroku zaocznego, zwykle 2 tygodnie od doręczenia</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>TAK</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>07.07.2026: jak WYROK_ZAOCZNY_SPOLKA, ale pozwanym jest osoba fizyczna (członek zarządu) — jeden z najwyższych priorytetów. Lekka integracja: kod K1 i scenariusz bazowy reużyte z NAKAZ_CZLONEK_ZARZADU (patrz doc_processor.py _DOC_TYPE_TO_K1), bez własnych wierszy w CSV 12; app.py nadpisuje fragmenty tekstu scenariusza tak, by poprawnie opisywały wyrok zaoczny.</t>
         </is>

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -44384,7 +44384,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>Pisma organów publicznych dotyczące odpowiedzialności członka zarządu wymagają innej ścieżki niż pozew/nakaz sądowy.</t>
+          <t>Różne pisma mają różną wagę — to wpływa na pilność i końcową ocenę ryzyka.</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">

--- a/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
+++ b/dane_wejściowe/KRS_Guard_reguly_i_zasady_funkcjonowania.xlsx
@@ -42620,7 +42620,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -42667,7 +42667,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -42761,7 +42761,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -42808,7 +42808,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -42855,7 +42855,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -42902,7 +42902,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -42949,7 +42949,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -42996,7 +42996,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -43513,7 +43513,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Status w zarządzie w okresie sprawy</t>
+          <t>Jaki jest Twój status w zarządzie?</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -43560,7 +43560,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Status w zarządzie w okresie sprawy</t>
+          <t>Jaki jest Twój status w zarządzie?</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -43607,7 +43607,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Status w zarządzie w okresie sprawy</t>
+          <t>Jaki jest Twój status w zarządzie?</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -43654,7 +43654,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Czy zmiana została ujawniona w KRS?</t>
+          <t>Czy zmiana w zarządzie została ujawniona w KRS?</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -43701,7 +43701,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Czy zmiana została ujawniona w KRS?</t>
+          <t>Czy zmiana w zarządzie została ujawniona w KRS?</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -43748,7 +43748,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Czy zmiana została ujawniona w KRS?</t>
+          <t>Czy zmiana w zarządzie została ujawniona w KRS?</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -43795,7 +43795,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Czy zmiana została ujawniona w KRS?</t>
+          <t>Czy zmiana w zarządzie została ujawniona w KRS?</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -44077,7 +44077,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Jaka jest kwota roszczenia wskazana w dokumencie?</t>
+          <t>Jaka kwota roszczenia jest wskazana w dokumencie?</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -44124,7 +44124,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Jaka jest kwota roszczenia wskazana w dokumencie?</t>
+          <t>Jaka kwota roszczenia jest wskazana w dokumencie?</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -44171,7 +44171,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Jaka jest kwota roszczenia wskazana w dokumencie?</t>
+          <t>Jaka kwota roszczenia jest wskazana w dokumencie?</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -44218,7 +44218,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Jaka jest kwota roszczenia wskazana w dokumencie?</t>
+          <t>Jaka kwota roszczenia jest wskazana w dokumencie?</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -44265,7 +44265,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Jaka jest kwota roszczenia wskazana w dokumencie?</t>
+          <t>Jaka kwota roszczenia jest wskazana w dokumencie?</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -44312,7 +44312,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Jaka jest kwota roszczenia wskazana w dokumencie?</t>
+          <t>Jaka kwota roszczenia jest wskazana w dokumencie?</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -44359,7 +44359,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -44406,7 +44406,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -44500,7 +44500,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rodzaj pisma, którego dotyczy sprawa</t>
+          <t>Jakie pismo lub dokument dotyczy Twojej sprawy?</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
